--- a/data/Data_Mix.xlsx
+++ b/data/Data_Mix.xlsx
@@ -5,26 +5,28 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/ew-mix-epximd/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796F4842-0CF8-DF4A-A24A-7E46A3DEB735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E78B1C-711E-F24D-A23F-6FCAF4F9D7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="3" xr2:uid="{151B9EC8-58A5-074E-9B57-F0DD5BB2A4DA}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="14700" windowHeight="18380" activeTab="2" xr2:uid="{151B9EC8-58A5-074E-9B57-F0DD5BB2A4DA}"/>
   </bookViews>
   <sheets>
     <sheet name="ReproAutumn2024" sheetId="1" r:id="rId1"/>
     <sheet name="ReproSpring2025weight" sheetId="10" r:id="rId2"/>
-    <sheet name="ReproSpring2025hatchlingsLotD" sheetId="11" r:id="rId3"/>
-    <sheet name="ReproSpring2025hatchlingsLotE" sheetId="12" r:id="rId4"/>
-    <sheet name="ReproSpring2025coc" sheetId="8" r:id="rId5"/>
-    <sheet name="ReproSpring2025cocsize" sheetId="7" r:id="rId6"/>
-    <sheet name="T0" sheetId="4" r:id="rId7"/>
-    <sheet name="README" sheetId="2" r:id="rId8"/>
+    <sheet name="ReproSpring2025weightfasting" sheetId="13" r:id="rId3"/>
+    <sheet name="ReproSpring2025hatchlingsLotD" sheetId="11" r:id="rId4"/>
+    <sheet name="ReproSpring2025hatchlingsLotE" sheetId="12" r:id="rId5"/>
+    <sheet name="ReproSpring2025coc" sheetId="8" r:id="rId6"/>
+    <sheet name="ReproSpring2025cocsize" sheetId="7" r:id="rId7"/>
+    <sheet name="T0" sheetId="4" r:id="rId8"/>
+    <sheet name="README" sheetId="2" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ReproSpring2025coc!$A$1:$L$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ReproSpring2025coc!$A$1:$L$253</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ReproSpring2025weight!$A$1:$P$577</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ReproSpring2025weightfasting!$A$1:$P$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6180" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6916" uniqueCount="118">
   <si>
     <t>Date</t>
   </si>
@@ -1034,7 +1036,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill>
@@ -1067,6 +1069,62 @@
       <fill>
         <patternFill>
           <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFDEFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFDEFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -20582,7 +20640,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E4C65D-F359-AD49-BC7D-8ABA3238360F}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q577"/>
+  <dimension ref="A1:Q587"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -21446,7 +21504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -21496,7 +21554,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -22846,7 +22904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -22896,7 +22954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>37</v>
       </c>
@@ -24246,7 +24304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>37</v>
       </c>
@@ -24296,7 +24354,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>37</v>
       </c>
@@ -25646,7 +25704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>37</v>
       </c>
@@ -25696,7 +25754,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>37</v>
       </c>
@@ -27046,7 +27104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>37</v>
       </c>
@@ -27096,7 +27154,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>37</v>
       </c>
@@ -28646,7 +28704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>11</v>
       </c>
@@ -28696,7 +28754,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>11</v>
       </c>
@@ -30046,7 +30104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>11</v>
       </c>
@@ -30096,7 +30154,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>11</v>
       </c>
@@ -31446,7 +31504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>11</v>
       </c>
@@ -31496,7 +31554,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>11</v>
       </c>
@@ -32846,7 +32904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>11</v>
       </c>
@@ -32896,7 +32954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>11</v>
       </c>
@@ -34246,7 +34304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>11</v>
       </c>
@@ -34296,7 +34354,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>11</v>
       </c>
@@ -35847,7 +35905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>37</v>
       </c>
@@ -35897,7 +35955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>37</v>
       </c>
@@ -37247,7 +37305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>37</v>
       </c>
@@ -37297,7 +37355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>37</v>
       </c>
@@ -38647,7 +38705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>37</v>
       </c>
@@ -38697,7 +38755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>37</v>
       </c>
@@ -40047,7 +40105,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>37</v>
       </c>
@@ -40097,7 +40155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>37</v>
       </c>
@@ -41447,7 +41505,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>37</v>
       </c>
@@ -41497,7 +41555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>37</v>
       </c>
@@ -42047,7 +42105,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>37</v>
       </c>
@@ -42097,7 +42155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>37</v>
       </c>
@@ -42147,7 +42205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>37</v>
       </c>
@@ -42197,7 +42255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>37</v>
       </c>
@@ -43047,7 +43105,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>11</v>
       </c>
@@ -43097,7 +43155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="451" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>11</v>
       </c>
@@ -44447,7 +44505,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="478" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>11</v>
       </c>
@@ -44497,7 +44555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>11</v>
       </c>
@@ -45847,7 +45905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="506" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>11</v>
       </c>
@@ -45897,7 +45955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="507" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>11</v>
       </c>
@@ -47247,7 +47305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="534" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>11</v>
       </c>
@@ -47297,7 +47355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>11</v>
       </c>
@@ -48647,7 +48705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>11</v>
       </c>
@@ -48697,7 +48755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>11</v>
       </c>
@@ -49247,7 +49305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>11</v>
       </c>
@@ -49297,7 +49355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>11</v>
       </c>
@@ -49347,7 +49405,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>11</v>
       </c>
@@ -49397,7 +49455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>11</v>
       </c>
@@ -49447,16 +49505,20 @@
         <v>18</v>
       </c>
     </row>
+    <row r="587" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O587" s="33"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P577" xr:uid="{39E4C65D-F359-AD49-BC7D-8ABA3238360F}">
-    <filterColumn colId="2">
+    <filterColumn colId="8">
       <filters>
-        <filter val="28"/>
+        <filter val="5"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="7">
+    <filterColumn colId="9">
       <filters>
-        <filter val="N"/>
+        <filter val="1"/>
+        <filter val="3"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -49469,6 +49531,7308 @@
     <sortCondition ref="K2:K289"/>
   </sortState>
   <conditionalFormatting sqref="M2:M577">
+    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="Green">
+      <formula>NOT(ISERROR(SEARCH("Green",M2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="6" operator="containsText" text="Orange">
+      <formula>NOT(ISERROR(SEARCH("Orange",M2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="Yellow">
+      <formula>NOT(ISERROR(SEARCH("Yellow",M2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="17" priority="8" operator="containsText" text="Pink">
+      <formula>NOT(ISERROR(SEARCH("Pink",M2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="Green">
+      <formula>NOT(ISERROR(SEARCH("Green",M1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="Orange">
+      <formula>NOT(ISERROR(SEARCH("Orange",M1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="Yellow">
+      <formula>NOT(ISERROR(SEARCH("Yellow",M1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="Pink">
+      <formula>NOT(ISERROR(SEARCH("Pink",M1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B6C79C-735D-7745-9103-3B789D76AD05}">
+  <dimension ref="A1:P145"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.5" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.1640625" customWidth="1"/>
+    <col min="11" max="11" width="19.6640625" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" s="36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C2" s="29">
+        <v>29</v>
+      </c>
+      <c r="D2" s="29">
+        <v>1</v>
+      </c>
+      <c r="E2" s="29">
+        <v>1</v>
+      </c>
+      <c r="F2" s="28">
+        <v>0.94179999999999997</v>
+      </c>
+      <c r="G2" s="28">
+        <v>0</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="31">
+        <v>1</v>
+      </c>
+      <c r="J2" s="28">
+        <v>1</v>
+      </c>
+      <c r="K2" s="28">
+        <v>1</v>
+      </c>
+      <c r="L2" s="28">
+        <v>74</v>
+      </c>
+      <c r="M2" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="33">
+        <v>560.6</v>
+      </c>
+      <c r="P2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C3" s="29">
+        <v>29</v>
+      </c>
+      <c r="D3" s="29">
+        <v>2</v>
+      </c>
+      <c r="E3" s="29">
+        <v>1</v>
+      </c>
+      <c r="F3" s="28">
+        <v>0.94179999999999997</v>
+      </c>
+      <c r="G3" s="28">
+        <v>0</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="31">
+        <v>1</v>
+      </c>
+      <c r="J3" s="28">
+        <v>1</v>
+      </c>
+      <c r="K3" s="28">
+        <v>2</v>
+      </c>
+      <c r="L3" s="28">
+        <v>69</v>
+      </c>
+      <c r="M3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" s="33">
+        <v>484.3</v>
+      </c>
+      <c r="P3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C4" s="29">
+        <v>29</v>
+      </c>
+      <c r="D4" s="29">
+        <v>5</v>
+      </c>
+      <c r="E4" s="29">
+        <v>3</v>
+      </c>
+      <c r="F4" s="28">
+        <v>9.4181000000000008</v>
+      </c>
+      <c r="G4" s="28">
+        <v>0</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="31">
+        <v>2</v>
+      </c>
+      <c r="J4" s="28">
+        <v>1</v>
+      </c>
+      <c r="K4" s="28">
+        <v>1</v>
+      </c>
+      <c r="L4" s="28">
+        <v>36</v>
+      </c>
+      <c r="M4" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" s="33">
+        <v>578.5</v>
+      </c>
+      <c r="P4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C5" s="29">
+        <v>29</v>
+      </c>
+      <c r="D5" s="29">
+        <v>6</v>
+      </c>
+      <c r="E5" s="29">
+        <v>3</v>
+      </c>
+      <c r="F5" s="28">
+        <v>9.4181000000000008</v>
+      </c>
+      <c r="G5" s="28">
+        <v>0</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="31">
+        <v>2</v>
+      </c>
+      <c r="J5" s="28">
+        <v>1</v>
+      </c>
+      <c r="K5" s="28">
+        <v>2</v>
+      </c>
+      <c r="L5" s="28">
+        <v>45</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="33">
+        <v>645.20000000000005</v>
+      </c>
+      <c r="P5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C6" s="29">
+        <v>29</v>
+      </c>
+      <c r="D6" s="29">
+        <v>9</v>
+      </c>
+      <c r="E6" s="29">
+        <v>5</v>
+      </c>
+      <c r="F6" s="28">
+        <v>52.9619</v>
+      </c>
+      <c r="G6" s="28">
+        <v>0</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="31">
+        <v>3</v>
+      </c>
+      <c r="J6" s="28">
+        <v>1</v>
+      </c>
+      <c r="K6" s="28">
+        <v>1</v>
+      </c>
+      <c r="L6" s="28">
+        <v>39</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" s="33">
+        <v>475.5</v>
+      </c>
+      <c r="P6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C7" s="29">
+        <v>29</v>
+      </c>
+      <c r="D7" s="29">
+        <v>10</v>
+      </c>
+      <c r="E7" s="29">
+        <v>5</v>
+      </c>
+      <c r="F7" s="28">
+        <v>52.9619</v>
+      </c>
+      <c r="G7" s="28">
+        <v>0</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="31">
+        <v>3</v>
+      </c>
+      <c r="J7" s="28">
+        <v>1</v>
+      </c>
+      <c r="K7" s="28">
+        <v>2</v>
+      </c>
+      <c r="L7" s="28">
+        <v>31</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O7" s="33">
+        <v>523.79999999999995</v>
+      </c>
+      <c r="P7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C8" s="29">
+        <v>29</v>
+      </c>
+      <c r="D8" s="29">
+        <v>13</v>
+      </c>
+      <c r="E8" s="29">
+        <v>7</v>
+      </c>
+      <c r="F8" s="28">
+        <v>94.180999999999997</v>
+      </c>
+      <c r="G8" s="28">
+        <v>0</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="31">
+        <v>4</v>
+      </c>
+      <c r="J8" s="28">
+        <v>1</v>
+      </c>
+      <c r="K8" s="28">
+        <v>1</v>
+      </c>
+      <c r="L8" s="28">
+        <v>21</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" s="33">
+        <v>530.29999999999995</v>
+      </c>
+      <c r="P8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C9" s="29">
+        <v>29</v>
+      </c>
+      <c r="D9" s="29">
+        <v>14</v>
+      </c>
+      <c r="E9" s="29">
+        <v>7</v>
+      </c>
+      <c r="F9" s="28">
+        <v>94.180999999999997</v>
+      </c>
+      <c r="G9" s="28">
+        <v>0</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="31">
+        <v>4</v>
+      </c>
+      <c r="J9" s="28">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28">
+        <v>2</v>
+      </c>
+      <c r="L9" s="28">
+        <v>44</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="33">
+        <v>460.6</v>
+      </c>
+      <c r="P9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C10" s="29">
+        <v>29</v>
+      </c>
+      <c r="D10" s="29">
+        <v>17</v>
+      </c>
+      <c r="E10" s="29">
+        <v>9</v>
+      </c>
+      <c r="F10" s="28">
+        <v>167.48009999999999</v>
+      </c>
+      <c r="G10" s="28">
+        <v>0</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="31">
+        <v>5</v>
+      </c>
+      <c r="J10" s="28">
+        <v>1</v>
+      </c>
+      <c r="K10" s="28">
+        <v>1</v>
+      </c>
+      <c r="L10" s="28">
+        <v>31</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O10" s="33">
+        <v>644.20000000000005</v>
+      </c>
+      <c r="P10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C11" s="29">
+        <v>29</v>
+      </c>
+      <c r="D11" s="29">
+        <v>18</v>
+      </c>
+      <c r="E11" s="29">
+        <v>9</v>
+      </c>
+      <c r="F11" s="28">
+        <v>167.48009999999999</v>
+      </c>
+      <c r="G11" s="28">
+        <v>0</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="31">
+        <v>5</v>
+      </c>
+      <c r="J11" s="28">
+        <v>1</v>
+      </c>
+      <c r="K11" s="28">
+        <v>2</v>
+      </c>
+      <c r="L11" s="28">
+        <v>20</v>
+      </c>
+      <c r="M11" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="33">
+        <v>617.9</v>
+      </c>
+      <c r="P11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C12" s="29">
+        <v>29</v>
+      </c>
+      <c r="D12" s="29">
+        <v>21</v>
+      </c>
+      <c r="E12" s="29">
+        <v>11</v>
+      </c>
+      <c r="F12" s="28">
+        <v>297.82639999999998</v>
+      </c>
+      <c r="G12" s="28">
+        <v>0</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="31">
+        <v>6</v>
+      </c>
+      <c r="J12" s="28">
+        <v>1</v>
+      </c>
+      <c r="K12" s="28">
+        <v>1</v>
+      </c>
+      <c r="L12" s="28">
+        <v>4</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="33">
+        <v>690.7</v>
+      </c>
+      <c r="P12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C13" s="29">
+        <v>29</v>
+      </c>
+      <c r="D13" s="29">
+        <v>22</v>
+      </c>
+      <c r="E13" s="29">
+        <v>11</v>
+      </c>
+      <c r="F13" s="28">
+        <v>297.82639999999998</v>
+      </c>
+      <c r="G13" s="28">
+        <v>0</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="31">
+        <v>6</v>
+      </c>
+      <c r="J13" s="28">
+        <v>1</v>
+      </c>
+      <c r="K13" s="28">
+        <v>2</v>
+      </c>
+      <c r="L13" s="28">
+        <v>43</v>
+      </c>
+      <c r="M13" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="33">
+        <v>479.6</v>
+      </c>
+      <c r="P13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C14" s="29">
+        <v>29</v>
+      </c>
+      <c r="D14" s="29">
+        <v>25</v>
+      </c>
+      <c r="E14" s="29">
+        <v>13</v>
+      </c>
+      <c r="F14" s="28">
+        <v>529.61860000000001</v>
+      </c>
+      <c r="G14" s="28">
+        <v>0</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="31">
+        <v>7</v>
+      </c>
+      <c r="J14" s="28">
+        <v>1</v>
+      </c>
+      <c r="K14" s="28">
+        <v>1</v>
+      </c>
+      <c r="L14" s="28">
+        <v>13</v>
+      </c>
+      <c r="M14" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="33">
+        <v>356.5</v>
+      </c>
+      <c r="P14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C15" s="29">
+        <v>29</v>
+      </c>
+      <c r="D15" s="29">
+        <v>26</v>
+      </c>
+      <c r="E15" s="29">
+        <v>13</v>
+      </c>
+      <c r="F15" s="28">
+        <v>529.61860000000001</v>
+      </c>
+      <c r="G15" s="28">
+        <v>0</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="31">
+        <v>7</v>
+      </c>
+      <c r="J15" s="28">
+        <v>1</v>
+      </c>
+      <c r="K15" s="28">
+        <v>2</v>
+      </c>
+      <c r="L15" s="28">
+        <v>1</v>
+      </c>
+      <c r="M15" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N15" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15" s="33">
+        <v>281.3</v>
+      </c>
+      <c r="P15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C16" s="29">
+        <v>29</v>
+      </c>
+      <c r="D16" s="29">
+        <v>29</v>
+      </c>
+      <c r="E16" s="29">
+        <v>15</v>
+      </c>
+      <c r="F16" s="28">
+        <v>0.70640000000000003</v>
+      </c>
+      <c r="G16" s="28">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="31">
+        <v>1</v>
+      </c>
+      <c r="J16" s="28">
+        <v>1</v>
+      </c>
+      <c r="K16" s="28">
+        <v>1</v>
+      </c>
+      <c r="L16" s="28">
+        <v>73</v>
+      </c>
+      <c r="M16" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N16" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" s="33">
+        <v>450.7</v>
+      </c>
+      <c r="P16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C17" s="29">
+        <v>29</v>
+      </c>
+      <c r="D17" s="29">
+        <v>30</v>
+      </c>
+      <c r="E17" s="29">
+        <v>15</v>
+      </c>
+      <c r="F17" s="28">
+        <v>0.70640000000000003</v>
+      </c>
+      <c r="G17" s="28">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="H17" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="31">
+        <v>1</v>
+      </c>
+      <c r="J17" s="28">
+        <v>1</v>
+      </c>
+      <c r="K17" s="28">
+        <v>2</v>
+      </c>
+      <c r="L17" s="28">
+        <v>77</v>
+      </c>
+      <c r="M17" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N17" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O17" s="33">
+        <v>412.2</v>
+      </c>
+      <c r="P17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C18" s="29">
+        <v>29</v>
+      </c>
+      <c r="D18" s="29">
+        <v>33</v>
+      </c>
+      <c r="E18" s="29">
+        <v>17</v>
+      </c>
+      <c r="F18" s="28">
+        <v>7.0636000000000001</v>
+      </c>
+      <c r="G18" s="28">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="31">
+        <v>2</v>
+      </c>
+      <c r="J18" s="28">
+        <v>1</v>
+      </c>
+      <c r="K18" s="28">
+        <v>1</v>
+      </c>
+      <c r="L18" s="28">
+        <v>29</v>
+      </c>
+      <c r="M18" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N18" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" s="33">
+        <v>602</v>
+      </c>
+      <c r="P18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C19" s="29">
+        <v>29</v>
+      </c>
+      <c r="D19" s="29">
+        <v>34</v>
+      </c>
+      <c r="E19" s="29">
+        <v>17</v>
+      </c>
+      <c r="F19" s="28">
+        <v>7.0636000000000001</v>
+      </c>
+      <c r="G19" s="28">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="31">
+        <v>2</v>
+      </c>
+      <c r="J19" s="28">
+        <v>1</v>
+      </c>
+      <c r="K19" s="28">
+        <v>2</v>
+      </c>
+      <c r="L19" s="28">
+        <v>29</v>
+      </c>
+      <c r="M19" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N19" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="33">
+        <v>577.6</v>
+      </c>
+      <c r="P19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C20" s="29">
+        <v>29</v>
+      </c>
+      <c r="D20" s="29">
+        <v>37</v>
+      </c>
+      <c r="E20" s="29">
+        <v>19</v>
+      </c>
+      <c r="F20" s="28">
+        <v>39.721400000000003</v>
+      </c>
+      <c r="G20" s="28">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="31">
+        <v>3</v>
+      </c>
+      <c r="J20" s="28">
+        <v>1</v>
+      </c>
+      <c r="K20" s="28">
+        <v>1</v>
+      </c>
+      <c r="L20" s="28">
+        <v>20</v>
+      </c>
+      <c r="M20" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="33">
+        <v>750</v>
+      </c>
+      <c r="P20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C21" s="29">
+        <v>29</v>
+      </c>
+      <c r="D21" s="29">
+        <v>38</v>
+      </c>
+      <c r="E21" s="29">
+        <v>19</v>
+      </c>
+      <c r="F21" s="28">
+        <v>39.721400000000003</v>
+      </c>
+      <c r="G21" s="28">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="31">
+        <v>3</v>
+      </c>
+      <c r="J21" s="28">
+        <v>1</v>
+      </c>
+      <c r="K21" s="28">
+        <v>2</v>
+      </c>
+      <c r="L21" s="28">
+        <v>74</v>
+      </c>
+      <c r="M21" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N21" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O21" s="33">
+        <v>243</v>
+      </c>
+      <c r="P21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C22" s="29">
+        <v>29</v>
+      </c>
+      <c r="D22" s="29">
+        <v>41</v>
+      </c>
+      <c r="E22" s="29">
+        <v>21</v>
+      </c>
+      <c r="F22" s="28">
+        <v>70.6357</v>
+      </c>
+      <c r="G22" s="28">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="H22" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="31">
+        <v>4</v>
+      </c>
+      <c r="J22" s="28">
+        <v>1</v>
+      </c>
+      <c r="K22" s="28">
+        <v>1</v>
+      </c>
+      <c r="L22" s="28">
+        <v>20</v>
+      </c>
+      <c r="M22" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" s="33">
+        <v>536.6</v>
+      </c>
+      <c r="P22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C23" s="29">
+        <v>29</v>
+      </c>
+      <c r="D23" s="29">
+        <v>42</v>
+      </c>
+      <c r="E23" s="29">
+        <v>21</v>
+      </c>
+      <c r="F23" s="28">
+        <v>70.6357</v>
+      </c>
+      <c r="G23" s="28">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="H23" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="31">
+        <v>4</v>
+      </c>
+      <c r="J23" s="28">
+        <v>1</v>
+      </c>
+      <c r="K23" s="28">
+        <v>2</v>
+      </c>
+      <c r="L23" s="28">
+        <v>74</v>
+      </c>
+      <c r="M23" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N23" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" s="33">
+        <v>463.3</v>
+      </c>
+      <c r="P23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C24" s="29">
+        <v>29</v>
+      </c>
+      <c r="D24" s="29">
+        <v>45</v>
+      </c>
+      <c r="E24" s="29">
+        <v>23</v>
+      </c>
+      <c r="F24" s="28">
+        <v>125.6101</v>
+      </c>
+      <c r="G24" s="28">
+        <v>0.11609999999999999</v>
+      </c>
+      <c r="H24" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="31">
+        <v>5</v>
+      </c>
+      <c r="J24" s="28">
+        <v>1</v>
+      </c>
+      <c r="K24" s="28">
+        <v>1</v>
+      </c>
+      <c r="L24" s="28">
+        <v>79</v>
+      </c>
+      <c r="M24" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N24" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="O24" s="33">
+        <v>856.7</v>
+      </c>
+      <c r="P24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C25" s="29">
+        <v>29</v>
+      </c>
+      <c r="D25" s="29">
+        <v>46</v>
+      </c>
+      <c r="E25" s="29">
+        <v>23</v>
+      </c>
+      <c r="F25" s="28">
+        <v>125.6101</v>
+      </c>
+      <c r="G25" s="28">
+        <v>0.11609999999999999</v>
+      </c>
+      <c r="H25" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="31">
+        <v>5</v>
+      </c>
+      <c r="J25" s="28">
+        <v>1</v>
+      </c>
+      <c r="K25" s="28">
+        <v>2</v>
+      </c>
+      <c r="L25" s="28">
+        <v>65</v>
+      </c>
+      <c r="M25" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N25" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O25" s="33">
+        <v>361.8</v>
+      </c>
+      <c r="P25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C26" s="29">
+        <v>29</v>
+      </c>
+      <c r="D26" s="29">
+        <v>49</v>
+      </c>
+      <c r="E26" s="29">
+        <v>25</v>
+      </c>
+      <c r="F26" s="28">
+        <v>223.3698</v>
+      </c>
+      <c r="G26" s="28">
+        <v>0.2064</v>
+      </c>
+      <c r="H26" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="31">
+        <v>6</v>
+      </c>
+      <c r="J26" s="28">
+        <v>1</v>
+      </c>
+      <c r="K26" s="28">
+        <v>1</v>
+      </c>
+      <c r="L26" s="28">
+        <v>55</v>
+      </c>
+      <c r="M26" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N26" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26" s="33">
+        <v>454.9</v>
+      </c>
+      <c r="P26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C27" s="29">
+        <v>29</v>
+      </c>
+      <c r="D27" s="29">
+        <v>50</v>
+      </c>
+      <c r="E27" s="29">
+        <v>25</v>
+      </c>
+      <c r="F27" s="28">
+        <v>223.3698</v>
+      </c>
+      <c r="G27" s="28">
+        <v>0.2064</v>
+      </c>
+      <c r="H27" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="31">
+        <v>6</v>
+      </c>
+      <c r="J27" s="28">
+        <v>1</v>
+      </c>
+      <c r="K27" s="28">
+        <v>2</v>
+      </c>
+      <c r="L27" s="28">
+        <v>13</v>
+      </c>
+      <c r="M27" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N27" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" s="33">
+        <v>584.79999999999995</v>
+      </c>
+      <c r="P27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C28" s="29">
+        <v>29</v>
+      </c>
+      <c r="D28" s="29">
+        <v>53</v>
+      </c>
+      <c r="E28" s="29">
+        <v>27</v>
+      </c>
+      <c r="F28" s="28">
+        <v>397.214</v>
+      </c>
+      <c r="G28" s="28">
+        <v>0.36709999999999998</v>
+      </c>
+      <c r="H28" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="31">
+        <v>7</v>
+      </c>
+      <c r="J28" s="28">
+        <v>1</v>
+      </c>
+      <c r="K28" s="28">
+        <v>1</v>
+      </c>
+      <c r="L28" s="28">
+        <v>66</v>
+      </c>
+      <c r="M28" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N28" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" s="33">
+        <v>519.5</v>
+      </c>
+      <c r="P28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C29" s="29">
+        <v>29</v>
+      </c>
+      <c r="D29" s="29">
+        <v>54</v>
+      </c>
+      <c r="E29" s="29">
+        <v>27</v>
+      </c>
+      <c r="F29" s="28">
+        <v>397.214</v>
+      </c>
+      <c r="G29" s="28">
+        <v>0.36709999999999998</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="31">
+        <v>7</v>
+      </c>
+      <c r="J29" s="28">
+        <v>1</v>
+      </c>
+      <c r="K29" s="28">
+        <v>2</v>
+      </c>
+      <c r="L29" s="28">
+        <v>46</v>
+      </c>
+      <c r="M29" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N29" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O29" s="33">
+        <v>280.3</v>
+      </c>
+      <c r="P29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C30" s="29">
+        <v>29</v>
+      </c>
+      <c r="D30" s="29">
+        <v>57</v>
+      </c>
+      <c r="E30" s="29">
+        <v>29</v>
+      </c>
+      <c r="F30" s="28">
+        <v>0.47089999999999999</v>
+      </c>
+      <c r="G30" s="28">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="H30" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="31">
+        <v>1</v>
+      </c>
+      <c r="J30" s="28">
+        <v>1</v>
+      </c>
+      <c r="K30" s="28">
+        <v>1</v>
+      </c>
+      <c r="L30" s="28">
+        <v>80</v>
+      </c>
+      <c r="M30" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N30" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="O30" s="33">
+        <v>545.20000000000005</v>
+      </c>
+      <c r="P30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C31" s="29">
+        <v>29</v>
+      </c>
+      <c r="D31" s="29">
+        <v>58</v>
+      </c>
+      <c r="E31" s="29">
+        <v>29</v>
+      </c>
+      <c r="F31" s="28">
+        <v>0.47089999999999999</v>
+      </c>
+      <c r="G31" s="28">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="H31" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="31">
+        <v>1</v>
+      </c>
+      <c r="J31" s="28">
+        <v>1</v>
+      </c>
+      <c r="K31" s="28">
+        <v>2</v>
+      </c>
+      <c r="L31" s="28">
+        <v>9</v>
+      </c>
+      <c r="M31" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N31" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O31" s="33">
+        <v>639.79999999999995</v>
+      </c>
+      <c r="P31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C32" s="29">
+        <v>29</v>
+      </c>
+      <c r="D32" s="29">
+        <v>61</v>
+      </c>
+      <c r="E32" s="29">
+        <v>31</v>
+      </c>
+      <c r="F32" s="28">
+        <v>4.7089999999999996</v>
+      </c>
+      <c r="G32" s="28">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="H32" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="31">
+        <v>2</v>
+      </c>
+      <c r="J32" s="28">
+        <v>1</v>
+      </c>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
+        <v>10</v>
+      </c>
+      <c r="M32" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N32" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O32" s="33">
+        <v>549.6</v>
+      </c>
+      <c r="P32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C33" s="29">
+        <v>29</v>
+      </c>
+      <c r="D33" s="29">
+        <v>62</v>
+      </c>
+      <c r="E33" s="29">
+        <v>31</v>
+      </c>
+      <c r="F33" s="28">
+        <v>4.7089999999999996</v>
+      </c>
+      <c r="G33" s="28">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="H33" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="31">
+        <v>2</v>
+      </c>
+      <c r="J33" s="28">
+        <v>1</v>
+      </c>
+      <c r="K33" s="28">
+        <v>2</v>
+      </c>
+      <c r="L33" s="28">
+        <v>55</v>
+      </c>
+      <c r="M33" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N33" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" s="33">
+        <v>592.20000000000005</v>
+      </c>
+      <c r="P33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C34" s="29">
+        <v>29</v>
+      </c>
+      <c r="D34" s="29">
+        <v>65</v>
+      </c>
+      <c r="E34" s="29">
+        <v>33</v>
+      </c>
+      <c r="F34" s="28">
+        <v>26.480899999999998</v>
+      </c>
+      <c r="G34" s="28">
+        <v>7.3400000000000007E-2</v>
+      </c>
+      <c r="H34" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="31">
+        <v>3</v>
+      </c>
+      <c r="J34" s="28">
+        <v>1</v>
+      </c>
+      <c r="K34" s="28">
+        <v>1</v>
+      </c>
+      <c r="L34" s="28">
+        <v>78</v>
+      </c>
+      <c r="M34" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N34" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O34" s="33">
+        <v>496.9</v>
+      </c>
+      <c r="P34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C35" s="29">
+        <v>29</v>
+      </c>
+      <c r="D35" s="29">
+        <v>66</v>
+      </c>
+      <c r="E35" s="29">
+        <v>33</v>
+      </c>
+      <c r="F35" s="28">
+        <v>26.480899999999998</v>
+      </c>
+      <c r="G35" s="28">
+        <v>7.3400000000000007E-2</v>
+      </c>
+      <c r="H35" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="31">
+        <v>3</v>
+      </c>
+      <c r="J35" s="28">
+        <v>1</v>
+      </c>
+      <c r="K35" s="28">
+        <v>2</v>
+      </c>
+      <c r="L35" s="28">
+        <v>18</v>
+      </c>
+      <c r="M35" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N35" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" s="33">
+        <v>548.70000000000005</v>
+      </c>
+      <c r="P35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C36" s="29">
+        <v>29</v>
+      </c>
+      <c r="D36" s="29">
+        <v>69</v>
+      </c>
+      <c r="E36" s="29">
+        <v>35</v>
+      </c>
+      <c r="F36" s="28">
+        <v>47.090499999999999</v>
+      </c>
+      <c r="G36" s="28">
+        <v>0.1305</v>
+      </c>
+      <c r="H36" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="31">
+        <v>4</v>
+      </c>
+      <c r="J36" s="28">
+        <v>1</v>
+      </c>
+      <c r="K36" s="28">
+        <v>1</v>
+      </c>
+      <c r="L36" s="28">
+        <v>65</v>
+      </c>
+      <c r="M36" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N36" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" s="33">
+        <v>410.5</v>
+      </c>
+      <c r="P36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C37" s="29">
+        <v>29</v>
+      </c>
+      <c r="D37" s="29">
+        <v>70</v>
+      </c>
+      <c r="E37" s="29">
+        <v>35</v>
+      </c>
+      <c r="F37" s="28">
+        <v>47.090499999999999</v>
+      </c>
+      <c r="G37" s="28">
+        <v>0.1305</v>
+      </c>
+      <c r="H37" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="31">
+        <v>4</v>
+      </c>
+      <c r="J37" s="28">
+        <v>1</v>
+      </c>
+      <c r="K37" s="28">
+        <v>2</v>
+      </c>
+      <c r="L37" s="28">
+        <v>78</v>
+      </c>
+      <c r="M37" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N37" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O37" s="33">
+        <v>467.9</v>
+      </c>
+      <c r="P37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C38" s="29">
+        <v>29</v>
+      </c>
+      <c r="D38" s="29">
+        <v>73</v>
+      </c>
+      <c r="E38" s="29">
+        <v>37</v>
+      </c>
+      <c r="F38" s="28">
+        <v>83.740099999999998</v>
+      </c>
+      <c r="G38" s="28">
+        <v>0.2321</v>
+      </c>
+      <c r="H38" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="31">
+        <v>5</v>
+      </c>
+      <c r="J38" s="28">
+        <v>1</v>
+      </c>
+      <c r="K38" s="28">
+        <v>1</v>
+      </c>
+      <c r="L38" s="28">
+        <v>13</v>
+      </c>
+      <c r="M38" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N38" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O38" s="33">
+        <v>466.1</v>
+      </c>
+      <c r="P38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C39" s="29">
+        <v>29</v>
+      </c>
+      <c r="D39" s="29">
+        <v>74</v>
+      </c>
+      <c r="E39" s="29">
+        <v>37</v>
+      </c>
+      <c r="F39" s="28">
+        <v>83.740099999999998</v>
+      </c>
+      <c r="G39" s="28">
+        <v>0.2321</v>
+      </c>
+      <c r="H39" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="31">
+        <v>5</v>
+      </c>
+      <c r="J39" s="28">
+        <v>1</v>
+      </c>
+      <c r="K39" s="28">
+        <v>2</v>
+      </c>
+      <c r="L39" s="28">
+        <v>1</v>
+      </c>
+      <c r="M39" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N39" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O39" s="33">
+        <v>498.3</v>
+      </c>
+      <c r="P39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C40" s="29">
+        <v>29</v>
+      </c>
+      <c r="D40" s="29">
+        <v>77</v>
+      </c>
+      <c r="E40" s="29">
+        <v>39</v>
+      </c>
+      <c r="F40" s="28">
+        <v>148.91319999999999</v>
+      </c>
+      <c r="G40" s="28">
+        <v>0.4128</v>
+      </c>
+      <c r="H40" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="31">
+        <v>6</v>
+      </c>
+      <c r="J40" s="28">
+        <v>1</v>
+      </c>
+      <c r="K40" s="28">
+        <v>1</v>
+      </c>
+      <c r="L40" s="28">
+        <v>9</v>
+      </c>
+      <c r="M40" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N40" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O40" s="33">
+        <v>841.3</v>
+      </c>
+      <c r="P40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C41" s="29">
+        <v>29</v>
+      </c>
+      <c r="D41" s="29">
+        <v>78</v>
+      </c>
+      <c r="E41" s="29">
+        <v>39</v>
+      </c>
+      <c r="F41" s="28">
+        <v>148.91319999999999</v>
+      </c>
+      <c r="G41" s="28">
+        <v>0.4128</v>
+      </c>
+      <c r="H41" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="31">
+        <v>6</v>
+      </c>
+      <c r="J41" s="28">
+        <v>1</v>
+      </c>
+      <c r="K41" s="28">
+        <v>2</v>
+      </c>
+      <c r="L41" s="28">
+        <v>3</v>
+      </c>
+      <c r="M41" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N41" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O41" s="33">
+        <v>367.4</v>
+      </c>
+      <c r="P41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C42" s="29">
+        <v>29</v>
+      </c>
+      <c r="D42" s="29">
+        <v>81</v>
+      </c>
+      <c r="E42" s="29">
+        <v>41</v>
+      </c>
+      <c r="F42" s="28">
+        <v>264.80930000000001</v>
+      </c>
+      <c r="G42" s="28">
+        <v>0.73409999999999997</v>
+      </c>
+      <c r="H42" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="31">
+        <v>7</v>
+      </c>
+      <c r="J42" s="28">
+        <v>1</v>
+      </c>
+      <c r="K42" s="28">
+        <v>1</v>
+      </c>
+      <c r="L42" s="28">
+        <v>78</v>
+      </c>
+      <c r="M42" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N42" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O42" s="33">
+        <v>338.4</v>
+      </c>
+      <c r="P42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C43" s="29">
+        <v>29</v>
+      </c>
+      <c r="D43" s="29">
+        <v>82</v>
+      </c>
+      <c r="E43" s="29">
+        <v>41</v>
+      </c>
+      <c r="F43" s="28">
+        <v>264.80930000000001</v>
+      </c>
+      <c r="G43" s="28">
+        <v>0.73409999999999997</v>
+      </c>
+      <c r="H43" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="31">
+        <v>7</v>
+      </c>
+      <c r="J43" s="28">
+        <v>1</v>
+      </c>
+      <c r="K43" s="28">
+        <v>2</v>
+      </c>
+      <c r="L43" s="28">
+        <v>18</v>
+      </c>
+      <c r="M43" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N43" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" s="33">
+        <v>782.2</v>
+      </c>
+      <c r="P43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C44" s="29">
+        <v>29</v>
+      </c>
+      <c r="D44" s="29">
+        <v>85</v>
+      </c>
+      <c r="E44" s="29">
+        <v>43</v>
+      </c>
+      <c r="F44" s="28">
+        <v>0.23549999999999999</v>
+      </c>
+      <c r="G44" s="28">
+        <v>2E-3</v>
+      </c>
+      <c r="H44" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="31">
+        <v>1</v>
+      </c>
+      <c r="J44" s="28">
+        <v>1</v>
+      </c>
+      <c r="K44" s="28">
+        <v>1</v>
+      </c>
+      <c r="L44" s="28">
+        <v>1</v>
+      </c>
+      <c r="M44" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N44" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O44" s="33">
+        <v>793.4</v>
+      </c>
+      <c r="P44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C45" s="29">
+        <v>29</v>
+      </c>
+      <c r="D45" s="29">
+        <v>86</v>
+      </c>
+      <c r="E45" s="29">
+        <v>43</v>
+      </c>
+      <c r="F45" s="28">
+        <v>0.23549999999999999</v>
+      </c>
+      <c r="G45" s="28">
+        <v>2E-3</v>
+      </c>
+      <c r="H45" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="31">
+        <v>1</v>
+      </c>
+      <c r="J45" s="28">
+        <v>1</v>
+      </c>
+      <c r="K45" s="28">
+        <v>2</v>
+      </c>
+      <c r="L45" s="28">
+        <v>21</v>
+      </c>
+      <c r="M45" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N45" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O45" s="33">
+        <v>566.6</v>
+      </c>
+      <c r="P45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C46" s="29">
+        <v>29</v>
+      </c>
+      <c r="D46" s="29">
+        <v>89</v>
+      </c>
+      <c r="E46" s="29">
+        <v>45</v>
+      </c>
+      <c r="F46" s="28">
+        <v>2.3544999999999998</v>
+      </c>
+      <c r="G46" s="28">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="H46" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" s="31">
+        <v>2</v>
+      </c>
+      <c r="J46" s="28">
+        <v>1</v>
+      </c>
+      <c r="K46" s="28">
+        <v>1</v>
+      </c>
+      <c r="L46" s="28">
+        <v>61</v>
+      </c>
+      <c r="M46" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N46" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O46" s="33">
+        <v>497.9</v>
+      </c>
+      <c r="P46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C47" s="29">
+        <v>29</v>
+      </c>
+      <c r="D47" s="29">
+        <v>90</v>
+      </c>
+      <c r="E47" s="29">
+        <v>45</v>
+      </c>
+      <c r="F47" s="28">
+        <v>2.3544999999999998</v>
+      </c>
+      <c r="G47" s="28">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="H47" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" s="31">
+        <v>2</v>
+      </c>
+      <c r="J47" s="28">
+        <v>1</v>
+      </c>
+      <c r="K47" s="28">
+        <v>2</v>
+      </c>
+      <c r="L47" s="28">
+        <v>14</v>
+      </c>
+      <c r="M47" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N47" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" s="33">
+        <v>504.9</v>
+      </c>
+      <c r="P47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C48" s="29">
+        <v>29</v>
+      </c>
+      <c r="D48" s="29">
+        <v>93</v>
+      </c>
+      <c r="E48" s="29">
+        <v>47</v>
+      </c>
+      <c r="F48" s="28">
+        <v>13.240500000000001</v>
+      </c>
+      <c r="G48" s="28">
+        <v>0.1101</v>
+      </c>
+      <c r="H48" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="31">
+        <v>3</v>
+      </c>
+      <c r="J48" s="28">
+        <v>1</v>
+      </c>
+      <c r="K48" s="28">
+        <v>1</v>
+      </c>
+      <c r="L48" s="28">
+        <v>31</v>
+      </c>
+      <c r="M48" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N48" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O48" s="33">
+        <v>541.70000000000005</v>
+      </c>
+      <c r="P48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C49" s="29">
+        <v>29</v>
+      </c>
+      <c r="D49" s="29">
+        <v>94</v>
+      </c>
+      <c r="E49" s="29">
+        <v>47</v>
+      </c>
+      <c r="F49" s="28">
+        <v>13.240500000000001</v>
+      </c>
+      <c r="G49" s="28">
+        <v>0.1101</v>
+      </c>
+      <c r="H49" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="31">
+        <v>3</v>
+      </c>
+      <c r="J49" s="28">
+        <v>1</v>
+      </c>
+      <c r="K49" s="28">
+        <v>2</v>
+      </c>
+      <c r="L49" s="28">
+        <v>20</v>
+      </c>
+      <c r="M49" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N49" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O49" s="33">
+        <v>531.79999999999995</v>
+      </c>
+      <c r="P49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C50" s="29">
+        <v>29</v>
+      </c>
+      <c r="D50" s="29">
+        <v>97</v>
+      </c>
+      <c r="E50" s="29">
+        <v>49</v>
+      </c>
+      <c r="F50" s="28">
+        <v>23.545200000000001</v>
+      </c>
+      <c r="G50" s="28">
+        <v>0.1958</v>
+      </c>
+      <c r="H50" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" s="31">
+        <v>4</v>
+      </c>
+      <c r="J50" s="28">
+        <v>1</v>
+      </c>
+      <c r="K50" s="28">
+        <v>1</v>
+      </c>
+      <c r="L50" s="28">
+        <v>14</v>
+      </c>
+      <c r="M50" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N50" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" s="33">
+        <v>532.6</v>
+      </c>
+      <c r="P50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C51" s="29">
+        <v>29</v>
+      </c>
+      <c r="D51" s="29">
+        <v>98</v>
+      </c>
+      <c r="E51" s="29">
+        <v>49</v>
+      </c>
+      <c r="F51" s="28">
+        <v>23.545200000000001</v>
+      </c>
+      <c r="G51" s="28">
+        <v>0.1958</v>
+      </c>
+      <c r="H51" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" s="31">
+        <v>4</v>
+      </c>
+      <c r="J51" s="28">
+        <v>1</v>
+      </c>
+      <c r="K51" s="28">
+        <v>2</v>
+      </c>
+      <c r="L51" s="28">
+        <v>10</v>
+      </c>
+      <c r="M51" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N51" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O51" s="33">
+        <v>943.6</v>
+      </c>
+      <c r="P51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C52" s="29">
+        <v>29</v>
+      </c>
+      <c r="D52" s="29">
+        <v>101</v>
+      </c>
+      <c r="E52" s="29">
+        <v>51</v>
+      </c>
+      <c r="F52" s="28">
+        <v>41.87</v>
+      </c>
+      <c r="G52" s="28">
+        <v>0.34820000000000001</v>
+      </c>
+      <c r="H52" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" s="31">
+        <v>5</v>
+      </c>
+      <c r="J52" s="28">
+        <v>1</v>
+      </c>
+      <c r="K52" s="28">
+        <v>1</v>
+      </c>
+      <c r="L52" s="28">
+        <v>34</v>
+      </c>
+      <c r="M52" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N52" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O52" s="33">
+        <v>566.20000000000005</v>
+      </c>
+      <c r="P52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C53" s="29">
+        <v>29</v>
+      </c>
+      <c r="D53" s="29">
+        <v>102</v>
+      </c>
+      <c r="E53" s="29">
+        <v>51</v>
+      </c>
+      <c r="F53" s="28">
+        <v>41.87</v>
+      </c>
+      <c r="G53" s="28">
+        <v>0.34820000000000001</v>
+      </c>
+      <c r="H53" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="31">
+        <v>5</v>
+      </c>
+      <c r="J53" s="28">
+        <v>1</v>
+      </c>
+      <c r="K53" s="28">
+        <v>2</v>
+      </c>
+      <c r="L53" s="28">
+        <v>23</v>
+      </c>
+      <c r="M53" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N53" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O53" s="33">
+        <v>636.1</v>
+      </c>
+      <c r="P53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C54" s="29">
+        <v>29</v>
+      </c>
+      <c r="D54" s="29">
+        <v>105</v>
+      </c>
+      <c r="E54" s="29">
+        <v>53</v>
+      </c>
+      <c r="F54" s="28">
+        <v>74.456599999999995</v>
+      </c>
+      <c r="G54" s="28">
+        <v>0.61919999999999997</v>
+      </c>
+      <c r="H54" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" s="31">
+        <v>6</v>
+      </c>
+      <c r="J54" s="28">
+        <v>1</v>
+      </c>
+      <c r="K54" s="28">
+        <v>1</v>
+      </c>
+      <c r="L54" s="28">
+        <v>74</v>
+      </c>
+      <c r="M54" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N54" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O54" s="33">
+        <v>195.9</v>
+      </c>
+      <c r="P54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C55" s="29">
+        <v>29</v>
+      </c>
+      <c r="D55" s="29">
+        <v>106</v>
+      </c>
+      <c r="E55" s="29">
+        <v>53</v>
+      </c>
+      <c r="F55" s="28">
+        <v>74.456599999999995</v>
+      </c>
+      <c r="G55" s="28">
+        <v>0.61919999999999997</v>
+      </c>
+      <c r="H55" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" s="31">
+        <v>6</v>
+      </c>
+      <c r="J55" s="28">
+        <v>1</v>
+      </c>
+      <c r="K55" s="28">
+        <v>2</v>
+      </c>
+      <c r="L55" s="28">
+        <v>69</v>
+      </c>
+      <c r="M55" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N55" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O55" s="33">
+        <v>242.5</v>
+      </c>
+      <c r="P55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C56" s="29">
+        <v>29</v>
+      </c>
+      <c r="D56" s="29">
+        <v>109</v>
+      </c>
+      <c r="E56" s="29">
+        <v>55</v>
+      </c>
+      <c r="F56" s="28">
+        <v>132.40469999999999</v>
+      </c>
+      <c r="G56" s="28">
+        <v>1.1012</v>
+      </c>
+      <c r="H56" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="31">
+        <v>7</v>
+      </c>
+      <c r="J56" s="28">
+        <v>1</v>
+      </c>
+      <c r="K56" s="28">
+        <v>1</v>
+      </c>
+      <c r="L56" s="28">
+        <v>39</v>
+      </c>
+      <c r="M56" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N56" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O56" s="33">
+        <v>579.1</v>
+      </c>
+      <c r="P56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C57" s="29">
+        <v>29</v>
+      </c>
+      <c r="D57" s="29">
+        <v>110</v>
+      </c>
+      <c r="E57" s="29">
+        <v>55</v>
+      </c>
+      <c r="F57" s="28">
+        <v>132.40469999999999</v>
+      </c>
+      <c r="G57" s="28">
+        <v>1.1012</v>
+      </c>
+      <c r="H57" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" s="31">
+        <v>7</v>
+      </c>
+      <c r="J57" s="28">
+        <v>1</v>
+      </c>
+      <c r="K57" s="28">
+        <v>2</v>
+      </c>
+      <c r="L57" s="28">
+        <v>31</v>
+      </c>
+      <c r="M57" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N57" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O57" s="33">
+        <v>364</v>
+      </c>
+      <c r="P57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C58" s="29">
+        <v>29</v>
+      </c>
+      <c r="D58" s="29">
+        <v>113</v>
+      </c>
+      <c r="E58" s="29">
+        <v>57</v>
+      </c>
+      <c r="F58" s="28">
+        <v>0</v>
+      </c>
+      <c r="G58" s="28">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="H58" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="31">
+        <v>1</v>
+      </c>
+      <c r="J58" s="28">
+        <v>1</v>
+      </c>
+      <c r="K58" s="28">
+        <v>1</v>
+      </c>
+      <c r="L58" s="28">
+        <v>32</v>
+      </c>
+      <c r="M58" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N58" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O58" s="33">
+        <v>411.4</v>
+      </c>
+      <c r="P58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C59" s="29">
+        <v>29</v>
+      </c>
+      <c r="D59" s="29">
+        <v>114</v>
+      </c>
+      <c r="E59" s="29">
+        <v>57</v>
+      </c>
+      <c r="F59" s="28">
+        <v>0</v>
+      </c>
+      <c r="G59" s="28">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="H59" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="31">
+        <v>1</v>
+      </c>
+      <c r="J59" s="28">
+        <v>1</v>
+      </c>
+      <c r="K59" s="28">
+        <v>2</v>
+      </c>
+      <c r="L59" s="28">
+        <v>61</v>
+      </c>
+      <c r="M59" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N59" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O59" s="33">
+        <v>492</v>
+      </c>
+      <c r="P59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C60" s="29">
+        <v>29</v>
+      </c>
+      <c r="D60" s="29">
+        <v>117</v>
+      </c>
+      <c r="E60" s="29">
+        <v>59</v>
+      </c>
+      <c r="F60" s="28">
+        <v>0</v>
+      </c>
+      <c r="G60" s="28">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="H60" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="31">
+        <v>2</v>
+      </c>
+      <c r="J60" s="28">
+        <v>1</v>
+      </c>
+      <c r="K60" s="28">
+        <v>1</v>
+      </c>
+      <c r="L60" s="28">
+        <v>3</v>
+      </c>
+      <c r="M60" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N60" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O60" s="33">
+        <v>626.1</v>
+      </c>
+      <c r="P60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C61" s="29">
+        <v>29</v>
+      </c>
+      <c r="D61" s="29">
+        <v>118</v>
+      </c>
+      <c r="E61" s="29">
+        <v>59</v>
+      </c>
+      <c r="F61" s="28">
+        <v>0</v>
+      </c>
+      <c r="G61" s="28">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="H61" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="31">
+        <v>2</v>
+      </c>
+      <c r="J61" s="28">
+        <v>1</v>
+      </c>
+      <c r="K61" s="28">
+        <v>2</v>
+      </c>
+      <c r="L61" s="28">
+        <v>79</v>
+      </c>
+      <c r="M61" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N61" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="O61" s="33">
+        <v>890.1</v>
+      </c>
+      <c r="P61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C62" s="29">
+        <v>29</v>
+      </c>
+      <c r="D62" s="29">
+        <v>121</v>
+      </c>
+      <c r="E62" s="29">
+        <v>61</v>
+      </c>
+      <c r="F62" s="28">
+        <v>0</v>
+      </c>
+      <c r="G62" s="28">
+        <v>0.14680000000000001</v>
+      </c>
+      <c r="H62" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="31">
+        <v>3</v>
+      </c>
+      <c r="J62" s="28">
+        <v>1</v>
+      </c>
+      <c r="K62" s="28">
+        <v>1</v>
+      </c>
+      <c r="L62" s="28">
+        <v>65</v>
+      </c>
+      <c r="M62" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N62" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O62" s="33">
+        <v>467.4</v>
+      </c>
+      <c r="P62" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C63" s="29">
+        <v>29</v>
+      </c>
+      <c r="D63" s="29">
+        <v>122</v>
+      </c>
+      <c r="E63" s="29">
+        <v>61</v>
+      </c>
+      <c r="F63" s="28">
+        <v>0</v>
+      </c>
+      <c r="G63" s="28">
+        <v>0.14680000000000001</v>
+      </c>
+      <c r="H63" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" s="31">
+        <v>3</v>
+      </c>
+      <c r="J63" s="28">
+        <v>1</v>
+      </c>
+      <c r="K63" s="28">
+        <v>2</v>
+      </c>
+      <c r="L63" s="28">
+        <v>78</v>
+      </c>
+      <c r="M63" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N63" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O63" s="33">
+        <v>520.4</v>
+      </c>
+      <c r="P63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C64" s="29">
+        <v>29</v>
+      </c>
+      <c r="D64" s="29">
+        <v>125</v>
+      </c>
+      <c r="E64" s="29">
+        <v>63</v>
+      </c>
+      <c r="F64" s="28">
+        <v>0</v>
+      </c>
+      <c r="G64" s="28">
+        <v>0.2611</v>
+      </c>
+      <c r="H64" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="31">
+        <v>4</v>
+      </c>
+      <c r="J64" s="28">
+        <v>1</v>
+      </c>
+      <c r="K64" s="28">
+        <v>1</v>
+      </c>
+      <c r="L64" s="28">
+        <v>46</v>
+      </c>
+      <c r="M64" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N64" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O64" s="33">
+        <v>689.4</v>
+      </c>
+      <c r="P64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C65" s="29">
+        <v>29</v>
+      </c>
+      <c r="D65" s="29">
+        <v>126</v>
+      </c>
+      <c r="E65" s="29">
+        <v>63</v>
+      </c>
+      <c r="F65" s="28">
+        <v>0</v>
+      </c>
+      <c r="G65" s="28">
+        <v>0.2611</v>
+      </c>
+      <c r="H65" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" s="31">
+        <v>4</v>
+      </c>
+      <c r="J65" s="28">
+        <v>1</v>
+      </c>
+      <c r="K65" s="28">
+        <v>2</v>
+      </c>
+      <c r="L65" s="28">
+        <v>80</v>
+      </c>
+      <c r="M65" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N65" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="O65" s="33">
+        <v>380.7</v>
+      </c>
+      <c r="P65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C66" s="29">
+        <v>29</v>
+      </c>
+      <c r="D66" s="29">
+        <v>129</v>
+      </c>
+      <c r="E66" s="29">
+        <v>65</v>
+      </c>
+      <c r="F66" s="28">
+        <v>0</v>
+      </c>
+      <c r="G66" s="28">
+        <v>0.46429999999999999</v>
+      </c>
+      <c r="H66" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="31">
+        <v>5</v>
+      </c>
+      <c r="J66" s="28">
+        <v>1</v>
+      </c>
+      <c r="K66" s="28">
+        <v>1</v>
+      </c>
+      <c r="L66" s="28">
+        <v>77</v>
+      </c>
+      <c r="M66" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N66" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O66" s="33">
+        <v>320.5</v>
+      </c>
+      <c r="P66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C67" s="29">
+        <v>29</v>
+      </c>
+      <c r="D67" s="29">
+        <v>130</v>
+      </c>
+      <c r="E67" s="29">
+        <v>65</v>
+      </c>
+      <c r="F67" s="28">
+        <v>0</v>
+      </c>
+      <c r="G67" s="28">
+        <v>0.46429999999999999</v>
+      </c>
+      <c r="H67" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" s="31">
+        <v>5</v>
+      </c>
+      <c r="J67" s="28">
+        <v>1</v>
+      </c>
+      <c r="K67" s="28">
+        <v>2</v>
+      </c>
+      <c r="L67" s="28">
+        <v>67</v>
+      </c>
+      <c r="M67" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N67" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O67" s="33">
+        <v>453.2</v>
+      </c>
+      <c r="P67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C68" s="29">
+        <v>29</v>
+      </c>
+      <c r="D68" s="29">
+        <v>133</v>
+      </c>
+      <c r="E68" s="29">
+        <v>67</v>
+      </c>
+      <c r="F68" s="28">
+        <v>0</v>
+      </c>
+      <c r="G68" s="28">
+        <v>0.8256</v>
+      </c>
+      <c r="H68" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="31">
+        <v>6</v>
+      </c>
+      <c r="J68" s="28">
+        <v>1</v>
+      </c>
+      <c r="K68" s="28">
+        <v>1</v>
+      </c>
+      <c r="L68" s="28">
+        <v>1</v>
+      </c>
+      <c r="M68" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N68" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O68" s="33">
+        <v>351.1</v>
+      </c>
+      <c r="P68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C69" s="29">
+        <v>29</v>
+      </c>
+      <c r="D69" s="29">
+        <v>134</v>
+      </c>
+      <c r="E69" s="29">
+        <v>67</v>
+      </c>
+      <c r="F69" s="28">
+        <v>0</v>
+      </c>
+      <c r="G69" s="28">
+        <v>0.8256</v>
+      </c>
+      <c r="H69" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="31">
+        <v>6</v>
+      </c>
+      <c r="J69" s="28">
+        <v>1</v>
+      </c>
+      <c r="K69" s="28">
+        <v>2</v>
+      </c>
+      <c r="L69" s="28">
+        <v>21</v>
+      </c>
+      <c r="M69" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N69" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O69" s="33">
+        <v>217.9</v>
+      </c>
+      <c r="P69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C70" s="29">
+        <v>29</v>
+      </c>
+      <c r="D70" s="29">
+        <v>137</v>
+      </c>
+      <c r="E70" s="29">
+        <v>69</v>
+      </c>
+      <c r="F70" s="28">
+        <v>0</v>
+      </c>
+      <c r="G70" s="28">
+        <v>1.4681999999999999</v>
+      </c>
+      <c r="H70" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="31">
+        <v>7</v>
+      </c>
+      <c r="J70" s="28">
+        <v>1</v>
+      </c>
+      <c r="K70" s="28">
+        <v>1</v>
+      </c>
+      <c r="L70" s="28">
+        <v>44</v>
+      </c>
+      <c r="M70" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N70" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O70" s="33">
+        <v>245.2</v>
+      </c>
+      <c r="P70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C71" s="29">
+        <v>29</v>
+      </c>
+      <c r="D71" s="29">
+        <v>138</v>
+      </c>
+      <c r="E71" s="29">
+        <v>69</v>
+      </c>
+      <c r="F71" s="28">
+        <v>0</v>
+      </c>
+      <c r="G71" s="28">
+        <v>1.4681999999999999</v>
+      </c>
+      <c r="H71" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="31">
+        <v>7</v>
+      </c>
+      <c r="J71" s="28">
+        <v>1</v>
+      </c>
+      <c r="K71" s="28">
+        <v>2</v>
+      </c>
+      <c r="L71" s="28">
+        <v>32</v>
+      </c>
+      <c r="M71" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N71" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O71" s="33">
+        <v>297.8</v>
+      </c>
+      <c r="P71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>37</v>
+      </c>
+      <c r="B72" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C72" s="29">
+        <v>29</v>
+      </c>
+      <c r="D72" s="29">
+        <v>141</v>
+      </c>
+      <c r="E72" s="29">
+        <v>71</v>
+      </c>
+      <c r="F72" s="28">
+        <v>0</v>
+      </c>
+      <c r="G72" s="28">
+        <v>0</v>
+      </c>
+      <c r="H72" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="31">
+        <v>0</v>
+      </c>
+      <c r="J72" s="28">
+        <v>1</v>
+      </c>
+      <c r="K72" s="28">
+        <v>1</v>
+      </c>
+      <c r="L72" s="28">
+        <v>23</v>
+      </c>
+      <c r="M72" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N72" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O72" s="33">
+        <v>320.7</v>
+      </c>
+      <c r="P72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="25">
+        <v>45771</v>
+      </c>
+      <c r="C73" s="29">
+        <v>29</v>
+      </c>
+      <c r="D73" s="29">
+        <v>142</v>
+      </c>
+      <c r="E73" s="29">
+        <v>71</v>
+      </c>
+      <c r="F73" s="28">
+        <v>0</v>
+      </c>
+      <c r="G73" s="28">
+        <v>0</v>
+      </c>
+      <c r="H73" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" s="31">
+        <v>0</v>
+      </c>
+      <c r="J73" s="28">
+        <v>1</v>
+      </c>
+      <c r="K73" s="28">
+        <v>2</v>
+      </c>
+      <c r="L73" s="28">
+        <v>4</v>
+      </c>
+      <c r="M73" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N73" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O73" s="33">
+        <v>553.6</v>
+      </c>
+      <c r="P73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C74" s="29">
+        <v>29</v>
+      </c>
+      <c r="D74" s="29">
+        <v>145</v>
+      </c>
+      <c r="E74" s="29">
+        <v>73</v>
+      </c>
+      <c r="F74" s="28">
+        <v>0.94179999999999997</v>
+      </c>
+      <c r="G74" s="28">
+        <v>0</v>
+      </c>
+      <c r="H74" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I74" s="31">
+        <v>1</v>
+      </c>
+      <c r="J74" s="28">
+        <v>3</v>
+      </c>
+      <c r="K74" s="28">
+        <v>1</v>
+      </c>
+      <c r="L74" s="28">
+        <v>54</v>
+      </c>
+      <c r="M74" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N74" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O74" s="33">
+        <v>573.1</v>
+      </c>
+      <c r="P74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C75" s="29">
+        <v>29</v>
+      </c>
+      <c r="D75" s="29">
+        <v>148</v>
+      </c>
+      <c r="E75" s="29">
+        <v>73</v>
+      </c>
+      <c r="F75" s="28">
+        <v>0.94179999999999997</v>
+      </c>
+      <c r="G75" s="28">
+        <v>0</v>
+      </c>
+      <c r="H75" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I75" s="31">
+        <v>1</v>
+      </c>
+      <c r="J75" s="28">
+        <v>3</v>
+      </c>
+      <c r="K75" s="28">
+        <v>2</v>
+      </c>
+      <c r="L75" s="28">
+        <v>71</v>
+      </c>
+      <c r="M75" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N75" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O75" s="33">
+        <v>721.3</v>
+      </c>
+      <c r="P75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C76" s="29">
+        <v>29</v>
+      </c>
+      <c r="D76" s="29">
+        <v>149</v>
+      </c>
+      <c r="E76" s="29">
+        <v>75</v>
+      </c>
+      <c r="F76" s="28">
+        <v>9.4181000000000008</v>
+      </c>
+      <c r="G76" s="28">
+        <v>0</v>
+      </c>
+      <c r="H76" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I76" s="31">
+        <v>2</v>
+      </c>
+      <c r="J76" s="28">
+        <v>3</v>
+      </c>
+      <c r="K76" s="28">
+        <v>1</v>
+      </c>
+      <c r="L76" s="28">
+        <v>17</v>
+      </c>
+      <c r="M76" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N76" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O76" s="33">
+        <v>519</v>
+      </c>
+      <c r="P76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C77" s="29">
+        <v>29</v>
+      </c>
+      <c r="D77" s="29">
+        <v>152</v>
+      </c>
+      <c r="E77" s="29">
+        <v>75</v>
+      </c>
+      <c r="F77" s="28">
+        <v>9.4181000000000008</v>
+      </c>
+      <c r="G77" s="28">
+        <v>0</v>
+      </c>
+      <c r="H77" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I77" s="31">
+        <v>2</v>
+      </c>
+      <c r="J77" s="28">
+        <v>3</v>
+      </c>
+      <c r="K77" s="28">
+        <v>2</v>
+      </c>
+      <c r="L77" s="28">
+        <v>52</v>
+      </c>
+      <c r="M77" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N77" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O77" s="33">
+        <v>573.6</v>
+      </c>
+      <c r="P77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C78" s="29">
+        <v>29</v>
+      </c>
+      <c r="D78" s="29">
+        <v>155</v>
+      </c>
+      <c r="E78" s="29">
+        <v>77</v>
+      </c>
+      <c r="F78" s="28">
+        <v>52.9619</v>
+      </c>
+      <c r="G78" s="28">
+        <v>0</v>
+      </c>
+      <c r="H78" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I78" s="31">
+        <v>3</v>
+      </c>
+      <c r="J78" s="28">
+        <v>3</v>
+      </c>
+      <c r="K78" s="28">
+        <v>1</v>
+      </c>
+      <c r="L78" s="28">
+        <v>48</v>
+      </c>
+      <c r="M78" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N78" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O78" s="33">
+        <v>577.6</v>
+      </c>
+      <c r="P78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C79" s="29">
+        <v>29</v>
+      </c>
+      <c r="D79" s="29">
+        <v>156</v>
+      </c>
+      <c r="E79" s="29">
+        <v>77</v>
+      </c>
+      <c r="F79" s="28">
+        <v>52.9619</v>
+      </c>
+      <c r="G79" s="28">
+        <v>0</v>
+      </c>
+      <c r="H79" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I79" s="31">
+        <v>3</v>
+      </c>
+      <c r="J79" s="28">
+        <v>3</v>
+      </c>
+      <c r="K79" s="28">
+        <v>2</v>
+      </c>
+      <c r="L79" s="28">
+        <v>70</v>
+      </c>
+      <c r="M79" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N79" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O79" s="33">
+        <v>414.5</v>
+      </c>
+      <c r="P79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C80" s="29">
+        <v>29</v>
+      </c>
+      <c r="D80" s="29">
+        <v>159</v>
+      </c>
+      <c r="E80" s="29">
+        <v>79</v>
+      </c>
+      <c r="F80" s="28">
+        <v>94.180999999999997</v>
+      </c>
+      <c r="G80" s="28">
+        <v>0</v>
+      </c>
+      <c r="H80" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I80" s="31">
+        <v>4</v>
+      </c>
+      <c r="J80" s="28">
+        <v>3</v>
+      </c>
+      <c r="K80" s="28">
+        <v>1</v>
+      </c>
+      <c r="L80" s="28">
+        <v>57</v>
+      </c>
+      <c r="M80" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N80" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O80" s="33">
+        <v>571.9</v>
+      </c>
+      <c r="P80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C81" s="29">
+        <v>29</v>
+      </c>
+      <c r="D81" s="29">
+        <v>160</v>
+      </c>
+      <c r="E81" s="29">
+        <v>79</v>
+      </c>
+      <c r="F81" s="28">
+        <v>94.180999999999997</v>
+      </c>
+      <c r="G81" s="28">
+        <v>0</v>
+      </c>
+      <c r="H81" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I81" s="31">
+        <v>4</v>
+      </c>
+      <c r="J81" s="28">
+        <v>3</v>
+      </c>
+      <c r="K81" s="28">
+        <v>2</v>
+      </c>
+      <c r="L81" s="28">
+        <v>76</v>
+      </c>
+      <c r="M81" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N81" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O81" s="33">
+        <v>568.6</v>
+      </c>
+      <c r="P81" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C82" s="29">
+        <v>29</v>
+      </c>
+      <c r="D82" s="29">
+        <v>163</v>
+      </c>
+      <c r="E82" s="29">
+        <v>81</v>
+      </c>
+      <c r="F82" s="28">
+        <v>167.48009999999999</v>
+      </c>
+      <c r="G82" s="28">
+        <v>0</v>
+      </c>
+      <c r="H82" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I82" s="31">
+        <v>5</v>
+      </c>
+      <c r="J82" s="28">
+        <v>3</v>
+      </c>
+      <c r="K82" s="28">
+        <v>1</v>
+      </c>
+      <c r="L82" s="28">
+        <v>49</v>
+      </c>
+      <c r="M82" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N82" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O82" s="33">
+        <v>463.5</v>
+      </c>
+      <c r="P82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C83" s="29">
+        <v>29</v>
+      </c>
+      <c r="D83" s="29">
+        <v>162</v>
+      </c>
+      <c r="E83" s="29">
+        <v>81</v>
+      </c>
+      <c r="F83" s="28">
+        <v>167.48009999999999</v>
+      </c>
+      <c r="G83" s="28">
+        <v>0</v>
+      </c>
+      <c r="H83" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I83" s="31">
+        <v>5</v>
+      </c>
+      <c r="J83" s="28">
+        <v>3</v>
+      </c>
+      <c r="K83" s="28">
+        <v>2</v>
+      </c>
+      <c r="L83" s="28">
+        <v>22</v>
+      </c>
+      <c r="M83" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N83" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O83" s="33">
+        <v>556.1</v>
+      </c>
+      <c r="P83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C84" s="29">
+        <v>29</v>
+      </c>
+      <c r="D84" s="29">
+        <v>168</v>
+      </c>
+      <c r="E84" s="29">
+        <v>83</v>
+      </c>
+      <c r="F84" s="28">
+        <v>297.82639999999998</v>
+      </c>
+      <c r="G84" s="28">
+        <v>0</v>
+      </c>
+      <c r="H84" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I84" s="31">
+        <v>6</v>
+      </c>
+      <c r="J84" s="28">
+        <v>3</v>
+      </c>
+      <c r="K84" s="28">
+        <v>1</v>
+      </c>
+      <c r="L84" s="28">
+        <v>70</v>
+      </c>
+      <c r="M84" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N84" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O84" s="33">
+        <v>568</v>
+      </c>
+      <c r="P84" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C85" s="29">
+        <v>29</v>
+      </c>
+      <c r="D85" s="29">
+        <v>167</v>
+      </c>
+      <c r="E85" s="29">
+        <v>83</v>
+      </c>
+      <c r="F85" s="28">
+        <v>297.82639999999998</v>
+      </c>
+      <c r="G85" s="28">
+        <v>0</v>
+      </c>
+      <c r="H85" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I85" s="31">
+        <v>6</v>
+      </c>
+      <c r="J85" s="28">
+        <v>3</v>
+      </c>
+      <c r="K85" s="28">
+        <v>2</v>
+      </c>
+      <c r="L85" s="28">
+        <v>59</v>
+      </c>
+      <c r="M85" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N85" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O85" s="33">
+        <v>481.3</v>
+      </c>
+      <c r="P85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C86" s="29">
+        <v>29</v>
+      </c>
+      <c r="D86" s="29">
+        <v>172</v>
+      </c>
+      <c r="E86" s="29">
+        <v>85</v>
+      </c>
+      <c r="F86" s="28">
+        <v>529.61860000000001</v>
+      </c>
+      <c r="G86" s="28">
+        <v>0</v>
+      </c>
+      <c r="H86" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I86" s="31">
+        <v>7</v>
+      </c>
+      <c r="J86" s="28">
+        <v>3</v>
+      </c>
+      <c r="K86" s="28">
+        <v>1</v>
+      </c>
+      <c r="L86" s="28">
+        <v>53</v>
+      </c>
+      <c r="M86" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N86" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O86" s="33">
+        <v>445.7</v>
+      </c>
+      <c r="P86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C87" s="29">
+        <v>29</v>
+      </c>
+      <c r="D87" s="29">
+        <v>169</v>
+      </c>
+      <c r="E87" s="29">
+        <v>85</v>
+      </c>
+      <c r="F87" s="28">
+        <v>529.61860000000001</v>
+      </c>
+      <c r="G87" s="28">
+        <v>0</v>
+      </c>
+      <c r="H87" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I87" s="31">
+        <v>7</v>
+      </c>
+      <c r="J87" s="28">
+        <v>3</v>
+      </c>
+      <c r="K87" s="28">
+        <v>2</v>
+      </c>
+      <c r="L87" s="28">
+        <v>8</v>
+      </c>
+      <c r="M87" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N87" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O87" s="33">
+        <v>514.70000000000005</v>
+      </c>
+      <c r="P87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C88" s="29">
+        <v>29</v>
+      </c>
+      <c r="D88" s="29">
+        <v>173</v>
+      </c>
+      <c r="E88" s="29">
+        <v>87</v>
+      </c>
+      <c r="F88" s="28">
+        <v>0.70640000000000003</v>
+      </c>
+      <c r="G88" s="28">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="H88" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" s="31">
+        <v>1</v>
+      </c>
+      <c r="J88" s="28">
+        <v>3</v>
+      </c>
+      <c r="K88" s="28">
+        <v>1</v>
+      </c>
+      <c r="L88" s="28">
+        <v>8</v>
+      </c>
+      <c r="M88" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N88" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O88" s="33">
+        <v>427</v>
+      </c>
+      <c r="P88" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C89" s="29">
+        <v>29</v>
+      </c>
+      <c r="D89" s="29">
+        <v>174</v>
+      </c>
+      <c r="E89" s="29">
+        <v>87</v>
+      </c>
+      <c r="F89" s="28">
+        <v>0.70640000000000003</v>
+      </c>
+      <c r="G89" s="28">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="H89" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" s="31">
+        <v>1</v>
+      </c>
+      <c r="J89" s="28">
+        <v>3</v>
+      </c>
+      <c r="K89" s="28">
+        <v>2</v>
+      </c>
+      <c r="L89" s="28">
+        <v>40</v>
+      </c>
+      <c r="M89" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N89" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O89" s="33">
+        <v>534.5</v>
+      </c>
+      <c r="P89" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C90" s="29">
+        <v>29</v>
+      </c>
+      <c r="D90" s="29">
+        <v>179</v>
+      </c>
+      <c r="E90" s="29">
+        <v>89</v>
+      </c>
+      <c r="F90" s="28">
+        <v>7.0636000000000001</v>
+      </c>
+      <c r="G90" s="28">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="H90" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" s="31">
+        <v>2</v>
+      </c>
+      <c r="J90" s="28">
+        <v>3</v>
+      </c>
+      <c r="K90" s="28">
+        <v>1</v>
+      </c>
+      <c r="L90" s="28">
+        <v>35</v>
+      </c>
+      <c r="M90" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N90" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O90" s="33">
+        <v>849.7</v>
+      </c>
+      <c r="P90" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C91" s="29">
+        <v>29</v>
+      </c>
+      <c r="D91" s="29">
+        <v>178</v>
+      </c>
+      <c r="E91" s="29">
+        <v>89</v>
+      </c>
+      <c r="F91" s="28">
+        <v>7.0636000000000001</v>
+      </c>
+      <c r="G91" s="28">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="H91" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" s="31">
+        <v>2</v>
+      </c>
+      <c r="J91" s="28">
+        <v>3</v>
+      </c>
+      <c r="K91" s="28">
+        <v>2</v>
+      </c>
+      <c r="L91" s="28">
+        <v>17</v>
+      </c>
+      <c r="M91" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N91" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O91" s="33">
+        <v>600.79999999999995</v>
+      </c>
+      <c r="P91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C92" s="29">
+        <v>29</v>
+      </c>
+      <c r="D92" s="29">
+        <v>183</v>
+      </c>
+      <c r="E92" s="29">
+        <v>91</v>
+      </c>
+      <c r="F92" s="28">
+        <v>39.721400000000003</v>
+      </c>
+      <c r="G92" s="28">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="H92" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I92" s="31">
+        <v>3</v>
+      </c>
+      <c r="J92" s="28">
+        <v>3</v>
+      </c>
+      <c r="K92" s="28">
+        <v>1</v>
+      </c>
+      <c r="L92" s="28">
+        <v>71</v>
+      </c>
+      <c r="M92" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N92" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O92" s="33">
+        <v>989.6</v>
+      </c>
+      <c r="P92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C93" s="29">
+        <v>29</v>
+      </c>
+      <c r="D93" s="29">
+        <v>184</v>
+      </c>
+      <c r="E93" s="29">
+        <v>91</v>
+      </c>
+      <c r="F93" s="28">
+        <v>39.721400000000003</v>
+      </c>
+      <c r="G93" s="28">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="H93" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I93" s="31">
+        <v>3</v>
+      </c>
+      <c r="J93" s="28">
+        <v>3</v>
+      </c>
+      <c r="K93" s="28">
+        <v>2</v>
+      </c>
+      <c r="L93" s="28">
+        <v>72</v>
+      </c>
+      <c r="M93" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N93" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O93" s="33">
+        <v>561.79999999999995</v>
+      </c>
+      <c r="P93" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C94" s="29">
+        <v>29</v>
+      </c>
+      <c r="D94" s="29">
+        <v>186</v>
+      </c>
+      <c r="E94" s="29">
+        <v>93</v>
+      </c>
+      <c r="F94" s="28">
+        <v>70.6357</v>
+      </c>
+      <c r="G94" s="28">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="H94" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" s="31">
+        <v>4</v>
+      </c>
+      <c r="J94" s="28">
+        <v>3</v>
+      </c>
+      <c r="K94" s="28">
+        <v>1</v>
+      </c>
+      <c r="L94" s="28">
+        <v>41</v>
+      </c>
+      <c r="M94" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N94" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O94" s="33">
+        <v>682.6</v>
+      </c>
+      <c r="P94" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C95" s="29">
+        <v>29</v>
+      </c>
+      <c r="D95" s="29">
+        <v>187</v>
+      </c>
+      <c r="E95" s="29">
+        <v>93</v>
+      </c>
+      <c r="F95" s="28">
+        <v>70.6357</v>
+      </c>
+      <c r="G95" s="28">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="H95" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I95" s="31">
+        <v>4</v>
+      </c>
+      <c r="J95" s="28">
+        <v>3</v>
+      </c>
+      <c r="K95" s="28">
+        <v>2</v>
+      </c>
+      <c r="L95" s="28">
+        <v>56</v>
+      </c>
+      <c r="M95" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N95" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O95" s="33">
+        <v>590.79999999999995</v>
+      </c>
+      <c r="P95" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C96" s="29">
+        <v>29</v>
+      </c>
+      <c r="D96" s="29">
+        <v>189</v>
+      </c>
+      <c r="E96" s="29">
+        <v>95</v>
+      </c>
+      <c r="F96" s="28">
+        <v>125.6101</v>
+      </c>
+      <c r="G96" s="28">
+        <v>0.11609999999999999</v>
+      </c>
+      <c r="H96" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" s="31">
+        <v>5</v>
+      </c>
+      <c r="J96" s="28">
+        <v>3</v>
+      </c>
+      <c r="K96" s="28">
+        <v>1</v>
+      </c>
+      <c r="L96" s="28">
+        <v>19</v>
+      </c>
+      <c r="M96" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N96" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O96" s="33">
+        <v>821.3</v>
+      </c>
+      <c r="P96" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C97" s="29">
+        <v>29</v>
+      </c>
+      <c r="D97" s="29">
+        <v>190</v>
+      </c>
+      <c r="E97" s="29">
+        <v>95</v>
+      </c>
+      <c r="F97" s="28">
+        <v>125.6101</v>
+      </c>
+      <c r="G97" s="28">
+        <v>0.11609999999999999</v>
+      </c>
+      <c r="H97" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I97" s="31">
+        <v>5</v>
+      </c>
+      <c r="J97" s="28">
+        <v>3</v>
+      </c>
+      <c r="K97" s="28">
+        <v>2</v>
+      </c>
+      <c r="L97" s="28">
+        <v>24</v>
+      </c>
+      <c r="M97" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N97" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O97" s="33">
+        <v>524.6</v>
+      </c>
+      <c r="P97" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C98" s="29">
+        <v>29</v>
+      </c>
+      <c r="D98" s="29">
+        <v>193</v>
+      </c>
+      <c r="E98" s="29">
+        <v>97</v>
+      </c>
+      <c r="F98" s="28">
+        <v>223.3698</v>
+      </c>
+      <c r="G98" s="28">
+        <v>0.2064</v>
+      </c>
+      <c r="H98" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" s="31">
+        <v>6</v>
+      </c>
+      <c r="J98" s="28">
+        <v>3</v>
+      </c>
+      <c r="K98" s="28">
+        <v>1</v>
+      </c>
+      <c r="L98" s="28">
+        <v>24</v>
+      </c>
+      <c r="M98" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N98" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O98" s="33">
+        <v>393.3</v>
+      </c>
+      <c r="P98" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C99" s="29">
+        <v>29</v>
+      </c>
+      <c r="D99" s="29">
+        <v>195</v>
+      </c>
+      <c r="E99" s="29">
+        <v>97</v>
+      </c>
+      <c r="F99" s="28">
+        <v>223.3698</v>
+      </c>
+      <c r="G99" s="28">
+        <v>0.2064</v>
+      </c>
+      <c r="H99" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I99" s="31">
+        <v>6</v>
+      </c>
+      <c r="J99" s="28">
+        <v>3</v>
+      </c>
+      <c r="K99" s="28">
+        <v>2</v>
+      </c>
+      <c r="L99" s="28">
+        <v>58</v>
+      </c>
+      <c r="M99" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N99" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O99" s="33">
+        <v>406.1</v>
+      </c>
+      <c r="P99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C100" s="29">
+        <v>29</v>
+      </c>
+      <c r="D100" s="29">
+        <v>196</v>
+      </c>
+      <c r="E100" s="29">
+        <v>98</v>
+      </c>
+      <c r="F100" s="28">
+        <v>397.214</v>
+      </c>
+      <c r="G100" s="28">
+        <v>0.36709999999999998</v>
+      </c>
+      <c r="H100" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I100" s="31">
+        <v>7</v>
+      </c>
+      <c r="J100" s="28">
+        <v>3</v>
+      </c>
+      <c r="K100" s="28">
+        <v>1</v>
+      </c>
+      <c r="L100" s="28">
+        <v>22</v>
+      </c>
+      <c r="M100" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N100" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O100" s="33">
+        <v>267.7</v>
+      </c>
+      <c r="P100" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C101" s="29">
+        <v>29</v>
+      </c>
+      <c r="D101" s="29">
+        <v>197</v>
+      </c>
+      <c r="E101" s="29">
+        <v>99</v>
+      </c>
+      <c r="F101" s="28">
+        <v>397.214</v>
+      </c>
+      <c r="G101" s="28">
+        <v>0.36709999999999998</v>
+      </c>
+      <c r="H101" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I101" s="31">
+        <v>7</v>
+      </c>
+      <c r="J101" s="28">
+        <v>3</v>
+      </c>
+      <c r="K101" s="28">
+        <v>2</v>
+      </c>
+      <c r="L101" s="28">
+        <v>25</v>
+      </c>
+      <c r="M101" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N101" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O101" s="33">
+        <v>484.3</v>
+      </c>
+      <c r="P101" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C102" s="29">
+        <v>29</v>
+      </c>
+      <c r="D102" s="29">
+        <v>203</v>
+      </c>
+      <c r="E102" s="29">
+        <v>101</v>
+      </c>
+      <c r="F102" s="28">
+        <v>0.47089999999999999</v>
+      </c>
+      <c r="G102" s="28">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="H102" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="31">
+        <v>1</v>
+      </c>
+      <c r="J102" s="28">
+        <v>3</v>
+      </c>
+      <c r="K102" s="28">
+        <v>1</v>
+      </c>
+      <c r="L102" s="28">
+        <v>49</v>
+      </c>
+      <c r="M102" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N102" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O102" s="33">
+        <v>441.9</v>
+      </c>
+      <c r="P102" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C103" s="29">
+        <v>29</v>
+      </c>
+      <c r="D103" s="29">
+        <v>202</v>
+      </c>
+      <c r="E103" s="29">
+        <v>101</v>
+      </c>
+      <c r="F103" s="28">
+        <v>0.47089999999999999</v>
+      </c>
+      <c r="G103" s="28">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="H103" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103" s="31">
+        <v>1</v>
+      </c>
+      <c r="J103" s="28">
+        <v>3</v>
+      </c>
+      <c r="K103" s="28">
+        <v>2</v>
+      </c>
+      <c r="L103" s="28">
+        <v>22</v>
+      </c>
+      <c r="M103" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N103" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O103" s="33">
+        <v>729</v>
+      </c>
+      <c r="P103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C104" s="29">
+        <v>29</v>
+      </c>
+      <c r="D104" s="29">
+        <v>205</v>
+      </c>
+      <c r="E104" s="29">
+        <v>103</v>
+      </c>
+      <c r="F104" s="28">
+        <v>4.7089999999999996</v>
+      </c>
+      <c r="G104" s="28">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="H104" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" s="31">
+        <v>2</v>
+      </c>
+      <c r="J104" s="28">
+        <v>3</v>
+      </c>
+      <c r="K104" s="28">
+        <v>1</v>
+      </c>
+      <c r="L104" s="28">
+        <v>33</v>
+      </c>
+      <c r="M104" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N104" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O104" s="33">
+        <v>567.20000000000005</v>
+      </c>
+      <c r="P104" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C105" s="29">
+        <v>29</v>
+      </c>
+      <c r="D105" s="29">
+        <v>208</v>
+      </c>
+      <c r="E105" s="29">
+        <v>103</v>
+      </c>
+      <c r="F105" s="28">
+        <v>4.7089999999999996</v>
+      </c>
+      <c r="G105" s="28">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="H105" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105" s="31">
+        <v>2</v>
+      </c>
+      <c r="J105" s="28">
+        <v>3</v>
+      </c>
+      <c r="K105" s="28">
+        <v>2</v>
+      </c>
+      <c r="L105" s="28">
+        <v>68</v>
+      </c>
+      <c r="M105" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N105" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O105" s="33">
+        <v>437</v>
+      </c>
+      <c r="P105" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C106" s="29">
+        <v>29</v>
+      </c>
+      <c r="D106" s="29">
+        <v>209</v>
+      </c>
+      <c r="E106" s="29">
+        <v>105</v>
+      </c>
+      <c r="F106" s="28">
+        <v>26.480899999999998</v>
+      </c>
+      <c r="G106" s="28">
+        <v>7.3400000000000007E-2</v>
+      </c>
+      <c r="H106" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106" s="31">
+        <v>3</v>
+      </c>
+      <c r="J106" s="28">
+        <v>3</v>
+      </c>
+      <c r="K106" s="28">
+        <v>1</v>
+      </c>
+      <c r="L106" s="28">
+        <v>7</v>
+      </c>
+      <c r="M106" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N106" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O106" s="33">
+        <v>414.2</v>
+      </c>
+      <c r="P106" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C107" s="29">
+        <v>29</v>
+      </c>
+      <c r="D107" s="29">
+        <v>210</v>
+      </c>
+      <c r="E107" s="29">
+        <v>105</v>
+      </c>
+      <c r="F107" s="28">
+        <v>26.480899999999998</v>
+      </c>
+      <c r="G107" s="28">
+        <v>7.3400000000000007E-2</v>
+      </c>
+      <c r="H107" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107" s="31">
+        <v>3</v>
+      </c>
+      <c r="J107" s="28">
+        <v>3</v>
+      </c>
+      <c r="K107" s="28">
+        <v>2</v>
+      </c>
+      <c r="L107" s="28">
+        <v>27</v>
+      </c>
+      <c r="M107" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N107" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O107" s="33">
+        <v>588.79999999999995</v>
+      </c>
+      <c r="P107" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C108" s="29">
+        <v>29</v>
+      </c>
+      <c r="D108" s="29">
+        <v>215</v>
+      </c>
+      <c r="E108" s="29">
+        <v>107</v>
+      </c>
+      <c r="F108" s="28">
+        <v>47.090499999999999</v>
+      </c>
+      <c r="G108" s="28">
+        <v>0.1305</v>
+      </c>
+      <c r="H108" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="31">
+        <v>4</v>
+      </c>
+      <c r="J108" s="28">
+        <v>3</v>
+      </c>
+      <c r="K108" s="28">
+        <v>1</v>
+      </c>
+      <c r="L108" s="28">
+        <v>68</v>
+      </c>
+      <c r="M108" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N108" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O108" s="33">
+        <v>468.9</v>
+      </c>
+      <c r="P108" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>11</v>
+      </c>
+      <c r="B109" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C109" s="29">
+        <v>29</v>
+      </c>
+      <c r="D109" s="29">
+        <v>216</v>
+      </c>
+      <c r="E109" s="29">
+        <v>107</v>
+      </c>
+      <c r="F109" s="28">
+        <v>47.090499999999999</v>
+      </c>
+      <c r="G109" s="28">
+        <v>0.1305</v>
+      </c>
+      <c r="H109" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I109" s="31">
+        <v>4</v>
+      </c>
+      <c r="J109" s="28">
+        <v>3</v>
+      </c>
+      <c r="K109" s="28">
+        <v>2</v>
+      </c>
+      <c r="L109" s="28">
+        <v>75</v>
+      </c>
+      <c r="M109" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N109" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O109" s="33">
+        <v>630.79999999999995</v>
+      </c>
+      <c r="P109" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>11</v>
+      </c>
+      <c r="B110" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C110" s="29">
+        <v>29</v>
+      </c>
+      <c r="D110" s="29">
+        <v>217</v>
+      </c>
+      <c r="E110" s="29">
+        <v>109</v>
+      </c>
+      <c r="F110" s="28">
+        <v>83.740099999999998</v>
+      </c>
+      <c r="G110" s="28">
+        <v>0.2321</v>
+      </c>
+      <c r="H110" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I110" s="31">
+        <v>5</v>
+      </c>
+      <c r="J110" s="28">
+        <v>3</v>
+      </c>
+      <c r="K110" s="28">
+        <v>1</v>
+      </c>
+      <c r="L110" s="28">
+        <v>7</v>
+      </c>
+      <c r="M110" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N110" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O110" s="33">
+        <v>525.29999999999995</v>
+      </c>
+      <c r="P110" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C111" s="29">
+        <v>29</v>
+      </c>
+      <c r="D111" s="29">
+        <v>218</v>
+      </c>
+      <c r="E111" s="29">
+        <v>109</v>
+      </c>
+      <c r="F111" s="28">
+        <v>83.740099999999998</v>
+      </c>
+      <c r="G111" s="28">
+        <v>0.2321</v>
+      </c>
+      <c r="H111" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I111" s="31">
+        <v>5</v>
+      </c>
+      <c r="J111" s="28">
+        <v>3</v>
+      </c>
+      <c r="K111" s="28">
+        <v>2</v>
+      </c>
+      <c r="L111" s="28">
+        <v>27</v>
+      </c>
+      <c r="M111" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N111" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O111" s="33">
+        <v>472.1</v>
+      </c>
+      <c r="P111" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>11</v>
+      </c>
+      <c r="B112" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C112" s="29">
+        <v>29</v>
+      </c>
+      <c r="D112" s="29">
+        <v>222</v>
+      </c>
+      <c r="E112" s="29">
+        <v>111</v>
+      </c>
+      <c r="F112" s="28">
+        <v>148.91319999999999</v>
+      </c>
+      <c r="G112" s="28">
+        <v>0.4128</v>
+      </c>
+      <c r="H112" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" s="31">
+        <v>6</v>
+      </c>
+      <c r="J112" s="28">
+        <v>3</v>
+      </c>
+      <c r="K112" s="28">
+        <v>1</v>
+      </c>
+      <c r="L112" s="28">
+        <v>16</v>
+      </c>
+      <c r="M112" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N112" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O112" s="33">
+        <v>279.89999999999998</v>
+      </c>
+      <c r="P112" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>11</v>
+      </c>
+      <c r="B113" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C113" s="29">
+        <v>29</v>
+      </c>
+      <c r="D113" s="29">
+        <v>223</v>
+      </c>
+      <c r="E113" s="29">
+        <v>111</v>
+      </c>
+      <c r="F113" s="28">
+        <v>148.91319999999999</v>
+      </c>
+      <c r="G113" s="28">
+        <v>0.4128</v>
+      </c>
+      <c r="H113" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="31">
+        <v>6</v>
+      </c>
+      <c r="J113" s="28">
+        <v>3</v>
+      </c>
+      <c r="K113" s="28">
+        <v>2</v>
+      </c>
+      <c r="L113" s="28">
+        <v>30</v>
+      </c>
+      <c r="M113" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N113" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O113" s="33">
+        <v>466.7</v>
+      </c>
+      <c r="P113" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>11</v>
+      </c>
+      <c r="B114" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C114" s="29">
+        <v>29</v>
+      </c>
+      <c r="D114" s="29">
+        <v>228</v>
+      </c>
+      <c r="E114" s="29">
+        <v>113</v>
+      </c>
+      <c r="F114" s="28">
+        <v>264.80930000000001</v>
+      </c>
+      <c r="G114" s="28">
+        <v>0.73409999999999997</v>
+      </c>
+      <c r="H114" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I114" s="31">
+        <v>7</v>
+      </c>
+      <c r="J114" s="28">
+        <v>3</v>
+      </c>
+      <c r="K114" s="28">
+        <v>1</v>
+      </c>
+      <c r="L114" s="28">
+        <v>56</v>
+      </c>
+      <c r="M114" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N114" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O114" s="33">
+        <v>330.7</v>
+      </c>
+      <c r="P114" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C115" s="29">
+        <v>29</v>
+      </c>
+      <c r="D115" s="29">
+        <v>225</v>
+      </c>
+      <c r="E115" s="29">
+        <v>113</v>
+      </c>
+      <c r="F115" s="28">
+        <v>264.80930000000001</v>
+      </c>
+      <c r="G115" s="28">
+        <v>0.73409999999999997</v>
+      </c>
+      <c r="H115" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I115" s="31">
+        <v>7</v>
+      </c>
+      <c r="J115" s="28">
+        <v>3</v>
+      </c>
+      <c r="K115" s="28">
+        <v>2</v>
+      </c>
+      <c r="L115" s="28">
+        <v>2</v>
+      </c>
+      <c r="M115" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N115" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O115" s="33">
+        <v>301.89999999999998</v>
+      </c>
+      <c r="P115" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>11</v>
+      </c>
+      <c r="B116" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C116" s="29">
+        <v>29</v>
+      </c>
+      <c r="D116" s="29">
+        <v>229</v>
+      </c>
+      <c r="E116" s="29">
+        <v>115</v>
+      </c>
+      <c r="F116" s="28">
+        <v>0.23549999999999999</v>
+      </c>
+      <c r="G116" s="28">
+        <v>2E-3</v>
+      </c>
+      <c r="H116" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I116" s="31">
+        <v>1</v>
+      </c>
+      <c r="J116" s="28">
+        <v>3</v>
+      </c>
+      <c r="K116" s="28">
+        <v>1</v>
+      </c>
+      <c r="L116" s="28">
+        <v>17</v>
+      </c>
+      <c r="M116" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N116" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O116" s="33">
+        <v>477.7</v>
+      </c>
+      <c r="P116" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C117" s="29">
+        <v>29</v>
+      </c>
+      <c r="D117" s="29">
+        <v>231</v>
+      </c>
+      <c r="E117" s="29">
+        <v>115</v>
+      </c>
+      <c r="F117" s="28">
+        <v>0.23549999999999999</v>
+      </c>
+      <c r="G117" s="28">
+        <v>2E-3</v>
+      </c>
+      <c r="H117" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I117" s="31">
+        <v>1</v>
+      </c>
+      <c r="J117" s="28">
+        <v>3</v>
+      </c>
+      <c r="K117" s="28">
+        <v>2</v>
+      </c>
+      <c r="L117" s="28">
+        <v>52</v>
+      </c>
+      <c r="M117" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N117" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O117" s="33">
+        <v>705.9</v>
+      </c>
+      <c r="P117" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C118" s="29">
+        <v>29</v>
+      </c>
+      <c r="D118" s="29">
+        <v>236</v>
+      </c>
+      <c r="E118" s="29">
+        <v>117</v>
+      </c>
+      <c r="F118" s="28">
+        <v>2.3544999999999998</v>
+      </c>
+      <c r="G118" s="28">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="H118" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I118" s="31">
+        <v>2</v>
+      </c>
+      <c r="J118" s="28">
+        <v>3</v>
+      </c>
+      <c r="K118" s="28">
+        <v>1</v>
+      </c>
+      <c r="L118" s="28">
+        <v>56</v>
+      </c>
+      <c r="M118" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N118" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O118" s="33">
+        <v>546.29999999999995</v>
+      </c>
+      <c r="P118" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C119" s="29">
+        <v>29</v>
+      </c>
+      <c r="D119" s="29">
+        <v>233</v>
+      </c>
+      <c r="E119" s="29">
+        <v>117</v>
+      </c>
+      <c r="F119" s="28">
+        <v>2.3544999999999998</v>
+      </c>
+      <c r="G119" s="28">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="H119" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I119" s="31">
+        <v>2</v>
+      </c>
+      <c r="J119" s="28">
+        <v>3</v>
+      </c>
+      <c r="K119" s="28">
+        <v>2</v>
+      </c>
+      <c r="L119" s="28">
+        <v>2</v>
+      </c>
+      <c r="M119" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N119" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O119" s="33">
+        <v>471.6</v>
+      </c>
+      <c r="P119" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>11</v>
+      </c>
+      <c r="B120" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C120" s="29">
+        <v>29</v>
+      </c>
+      <c r="D120" s="29">
+        <v>240</v>
+      </c>
+      <c r="E120" s="29">
+        <v>119</v>
+      </c>
+      <c r="F120" s="28">
+        <v>13.240500000000001</v>
+      </c>
+      <c r="G120" s="28">
+        <v>0.1101</v>
+      </c>
+      <c r="H120" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I120" s="31">
+        <v>3</v>
+      </c>
+      <c r="J120" s="28">
+        <v>3</v>
+      </c>
+      <c r="K120" s="28">
+        <v>1</v>
+      </c>
+      <c r="L120" s="28">
+        <v>70</v>
+      </c>
+      <c r="M120" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N120" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O120" s="33">
+        <v>749.7</v>
+      </c>
+      <c r="P120" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C121" s="29">
+        <v>29</v>
+      </c>
+      <c r="D121" s="29">
+        <v>237</v>
+      </c>
+      <c r="E121" s="29">
+        <v>119</v>
+      </c>
+      <c r="F121" s="28">
+        <v>13.240500000000001</v>
+      </c>
+      <c r="G121" s="28">
+        <v>0.1101</v>
+      </c>
+      <c r="H121" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" s="31">
+        <v>3</v>
+      </c>
+      <c r="J121" s="28">
+        <v>3</v>
+      </c>
+      <c r="K121" s="28">
+        <v>2</v>
+      </c>
+      <c r="L121" s="28">
+        <v>59</v>
+      </c>
+      <c r="M121" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N121" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O121" s="33">
+        <v>660.2</v>
+      </c>
+      <c r="P121" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C122" s="29">
+        <v>29</v>
+      </c>
+      <c r="D122" s="29">
+        <v>241</v>
+      </c>
+      <c r="E122" s="29">
+        <v>121</v>
+      </c>
+      <c r="F122" s="28">
+        <v>23.545200000000001</v>
+      </c>
+      <c r="G122" s="28">
+        <v>0.1958</v>
+      </c>
+      <c r="H122" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I122" s="31">
+        <v>4</v>
+      </c>
+      <c r="J122" s="28">
+        <v>3</v>
+      </c>
+      <c r="K122" s="28">
+        <v>1</v>
+      </c>
+      <c r="L122" s="28">
+        <v>8</v>
+      </c>
+      <c r="M122" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N122" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O122" s="33">
+        <v>398.6</v>
+      </c>
+      <c r="P122" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C123" s="29">
+        <v>29</v>
+      </c>
+      <c r="D123" s="29">
+        <v>242</v>
+      </c>
+      <c r="E123" s="29">
+        <v>121</v>
+      </c>
+      <c r="F123" s="28">
+        <v>23.545200000000001</v>
+      </c>
+      <c r="G123" s="28">
+        <v>0.1958</v>
+      </c>
+      <c r="H123" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I123" s="31">
+        <v>4</v>
+      </c>
+      <c r="J123" s="28">
+        <v>3</v>
+      </c>
+      <c r="K123" s="28">
+        <v>2</v>
+      </c>
+      <c r="L123" s="28">
+        <v>40</v>
+      </c>
+      <c r="M123" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N123" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O123" s="33">
+        <v>498.2</v>
+      </c>
+      <c r="P123" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>11</v>
+      </c>
+      <c r="B124" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C124" s="29">
+        <v>29</v>
+      </c>
+      <c r="D124" s="29">
+        <v>247</v>
+      </c>
+      <c r="E124" s="29">
+        <v>123</v>
+      </c>
+      <c r="F124" s="28">
+        <v>41.87</v>
+      </c>
+      <c r="G124" s="28">
+        <v>0.34820000000000001</v>
+      </c>
+      <c r="H124" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I124" s="31">
+        <v>5</v>
+      </c>
+      <c r="J124" s="28">
+        <v>3</v>
+      </c>
+      <c r="K124" s="28">
+        <v>1</v>
+      </c>
+      <c r="L124" s="28">
+        <v>68</v>
+      </c>
+      <c r="M124" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N124" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O124" s="33">
+        <v>436.4</v>
+      </c>
+      <c r="P124" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C125" s="29">
+        <v>29</v>
+      </c>
+      <c r="D125" s="29">
+        <v>248</v>
+      </c>
+      <c r="E125" s="29">
+        <v>123</v>
+      </c>
+      <c r="F125" s="28">
+        <v>41.87</v>
+      </c>
+      <c r="G125" s="28">
+        <v>0.34820000000000001</v>
+      </c>
+      <c r="H125" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I125" s="31">
+        <v>5</v>
+      </c>
+      <c r="J125" s="28">
+        <v>3</v>
+      </c>
+      <c r="K125" s="28">
+        <v>2</v>
+      </c>
+      <c r="L125" s="28">
+        <v>75</v>
+      </c>
+      <c r="M125" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N125" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O125" s="33">
+        <v>560.70000000000005</v>
+      </c>
+      <c r="P125" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C126" s="29">
+        <v>29</v>
+      </c>
+      <c r="D126" s="29">
+        <v>251</v>
+      </c>
+      <c r="E126" s="29">
+        <v>125</v>
+      </c>
+      <c r="F126" s="28">
+        <v>74.456599999999995</v>
+      </c>
+      <c r="G126" s="28">
+        <v>0.61919999999999997</v>
+      </c>
+      <c r="H126" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I126" s="31">
+        <v>6</v>
+      </c>
+      <c r="J126" s="28">
+        <v>3</v>
+      </c>
+      <c r="K126" s="28">
+        <v>1</v>
+      </c>
+      <c r="L126" s="28">
+        <v>62</v>
+      </c>
+      <c r="M126" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N126" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O126" s="33">
+        <v>588.6</v>
+      </c>
+      <c r="P126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>11</v>
+      </c>
+      <c r="B127" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C127" s="29">
+        <v>29</v>
+      </c>
+      <c r="D127" s="29">
+        <v>252</v>
+      </c>
+      <c r="E127" s="29">
+        <v>125</v>
+      </c>
+      <c r="F127" s="28">
+        <v>74.456599999999995</v>
+      </c>
+      <c r="G127" s="28">
+        <v>0.61919999999999997</v>
+      </c>
+      <c r="H127" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I127" s="31">
+        <v>6</v>
+      </c>
+      <c r="J127" s="28">
+        <v>3</v>
+      </c>
+      <c r="K127" s="28">
+        <v>2</v>
+      </c>
+      <c r="L127" s="28">
+        <v>62</v>
+      </c>
+      <c r="M127" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N127" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O127" s="33">
+        <v>360.8</v>
+      </c>
+      <c r="P127" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>11</v>
+      </c>
+      <c r="B128" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C128" s="29">
+        <v>29</v>
+      </c>
+      <c r="D128" s="29">
+        <v>256</v>
+      </c>
+      <c r="E128" s="29">
+        <v>127</v>
+      </c>
+      <c r="F128" s="28">
+        <v>132.40469999999999</v>
+      </c>
+      <c r="G128" s="28">
+        <v>1.1012</v>
+      </c>
+      <c r="H128" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I128" s="31">
+        <v>7</v>
+      </c>
+      <c r="J128" s="28">
+        <v>3</v>
+      </c>
+      <c r="K128" s="28">
+        <v>1</v>
+      </c>
+      <c r="L128" s="28">
+        <v>76</v>
+      </c>
+      <c r="M128" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N128" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O128" s="33">
+        <v>195.9</v>
+      </c>
+      <c r="P128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>11</v>
+      </c>
+      <c r="B129" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C129" s="29">
+        <v>29</v>
+      </c>
+      <c r="D129" s="29">
+        <v>253</v>
+      </c>
+      <c r="E129" s="29">
+        <v>127</v>
+      </c>
+      <c r="F129" s="28">
+        <v>132.40469999999999</v>
+      </c>
+      <c r="G129" s="28">
+        <v>1.1012</v>
+      </c>
+      <c r="H129" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I129" s="31">
+        <v>7</v>
+      </c>
+      <c r="J129" s="28">
+        <v>3</v>
+      </c>
+      <c r="K129" s="28">
+        <v>2</v>
+      </c>
+      <c r="L129" s="28">
+        <v>11</v>
+      </c>
+      <c r="M129" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N129" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O129" s="33">
+        <v>539.20000000000005</v>
+      </c>
+      <c r="P129" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>11</v>
+      </c>
+      <c r="B130" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C130" s="29">
+        <v>29</v>
+      </c>
+      <c r="D130" s="29">
+        <v>260</v>
+      </c>
+      <c r="E130" s="29">
+        <v>129</v>
+      </c>
+      <c r="F130" s="28">
+        <v>0</v>
+      </c>
+      <c r="G130" s="28">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="H130" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I130" s="31">
+        <v>1</v>
+      </c>
+      <c r="J130" s="28">
+        <v>3</v>
+      </c>
+      <c r="K130" s="28">
+        <v>1</v>
+      </c>
+      <c r="L130" s="28">
+        <v>75</v>
+      </c>
+      <c r="M130" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N130" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O130" s="33">
+        <v>532.20000000000005</v>
+      </c>
+      <c r="P130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>11</v>
+      </c>
+      <c r="B131" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C131" s="29">
+        <v>29</v>
+      </c>
+      <c r="D131" s="29">
+        <v>257</v>
+      </c>
+      <c r="E131" s="29">
+        <v>129</v>
+      </c>
+      <c r="F131" s="28">
+        <v>0</v>
+      </c>
+      <c r="G131" s="28">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="H131" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I131" s="31">
+        <v>1</v>
+      </c>
+      <c r="J131" s="28">
+        <v>3</v>
+      </c>
+      <c r="K131" s="28">
+        <v>2</v>
+      </c>
+      <c r="L131" s="28">
+        <v>7</v>
+      </c>
+      <c r="M131" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N131" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O131" s="33">
+        <v>564.79999999999995</v>
+      </c>
+      <c r="P131" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>11</v>
+      </c>
+      <c r="B132" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C132" s="29">
+        <v>29</v>
+      </c>
+      <c r="D132" s="29">
+        <v>263</v>
+      </c>
+      <c r="E132" s="29">
+        <v>131</v>
+      </c>
+      <c r="F132" s="28">
+        <v>0</v>
+      </c>
+      <c r="G132" s="28">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="H132" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I132" s="31">
+        <v>2</v>
+      </c>
+      <c r="J132" s="28">
+        <v>3</v>
+      </c>
+      <c r="K132" s="28">
+        <v>1</v>
+      </c>
+      <c r="L132" s="28">
+        <v>58</v>
+      </c>
+      <c r="M132" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N132" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O132" s="33">
+        <v>638.9</v>
+      </c>
+      <c r="P132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>11</v>
+      </c>
+      <c r="B133" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C133" s="29">
+        <v>29</v>
+      </c>
+      <c r="D133" s="29">
+        <v>262</v>
+      </c>
+      <c r="E133" s="29">
+        <v>131</v>
+      </c>
+      <c r="F133" s="28">
+        <v>0</v>
+      </c>
+      <c r="G133" s="28">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="H133" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I133" s="31">
+        <v>2</v>
+      </c>
+      <c r="J133" s="28">
+        <v>3</v>
+      </c>
+      <c r="K133" s="28">
+        <v>2</v>
+      </c>
+      <c r="L133" s="28">
+        <v>35</v>
+      </c>
+      <c r="M133" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N133" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O133" s="33">
+        <v>492.2</v>
+      </c>
+      <c r="P133" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>11</v>
+      </c>
+      <c r="B134" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C134" s="29">
+        <v>29</v>
+      </c>
+      <c r="D134" s="29">
+        <v>267</v>
+      </c>
+      <c r="E134" s="29">
+        <v>133</v>
+      </c>
+      <c r="F134" s="28">
+        <v>0</v>
+      </c>
+      <c r="G134" s="28">
+        <v>0.14680000000000001</v>
+      </c>
+      <c r="H134" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I134" s="31">
+        <v>3</v>
+      </c>
+      <c r="J134" s="28">
+        <v>3</v>
+      </c>
+      <c r="K134" s="28">
+        <v>1</v>
+      </c>
+      <c r="L134" s="28">
+        <v>57</v>
+      </c>
+      <c r="M134" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N134" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O134" s="33">
+        <v>607.70000000000005</v>
+      </c>
+      <c r="P134" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C135" s="29">
+        <v>29</v>
+      </c>
+      <c r="D135" s="29">
+        <v>268</v>
+      </c>
+      <c r="E135" s="29">
+        <v>133</v>
+      </c>
+      <c r="F135" s="28">
+        <v>0</v>
+      </c>
+      <c r="G135" s="28">
+        <v>0.14680000000000001</v>
+      </c>
+      <c r="H135" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I135" s="31">
+        <v>3</v>
+      </c>
+      <c r="J135" s="28">
+        <v>3</v>
+      </c>
+      <c r="K135" s="28">
+        <v>2</v>
+      </c>
+      <c r="L135" s="28">
+        <v>76</v>
+      </c>
+      <c r="M135" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N135" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="O135" s="33">
+        <v>665.3</v>
+      </c>
+      <c r="P135" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C136" s="29">
+        <v>29</v>
+      </c>
+      <c r="D136" s="29">
+        <v>269</v>
+      </c>
+      <c r="E136" s="29">
+        <v>135</v>
+      </c>
+      <c r="F136" s="28">
+        <v>0</v>
+      </c>
+      <c r="G136" s="28">
+        <v>0.2611</v>
+      </c>
+      <c r="H136" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I136" s="31">
+        <v>4</v>
+      </c>
+      <c r="J136" s="28">
+        <v>3</v>
+      </c>
+      <c r="K136" s="28">
+        <v>1</v>
+      </c>
+      <c r="L136" s="28">
+        <v>27</v>
+      </c>
+      <c r="M136" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N136" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O136" s="33">
+        <v>352.3</v>
+      </c>
+      <c r="P136" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>11</v>
+      </c>
+      <c r="B137" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C137" s="29">
+        <v>29</v>
+      </c>
+      <c r="D137" s="29">
+        <v>271</v>
+      </c>
+      <c r="E137" s="29">
+        <v>135</v>
+      </c>
+      <c r="F137" s="28">
+        <v>0</v>
+      </c>
+      <c r="G137" s="28">
+        <v>0.2611</v>
+      </c>
+      <c r="H137" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I137" s="31">
+        <v>4</v>
+      </c>
+      <c r="J137" s="28">
+        <v>3</v>
+      </c>
+      <c r="K137" s="28">
+        <v>2</v>
+      </c>
+      <c r="L137" s="28">
+        <v>51</v>
+      </c>
+      <c r="M137" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N137" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O137" s="33">
+        <v>619.20000000000005</v>
+      </c>
+      <c r="P137" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>11</v>
+      </c>
+      <c r="B138" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C138" s="29">
+        <v>29</v>
+      </c>
+      <c r="D138" s="29">
+        <v>273</v>
+      </c>
+      <c r="E138" s="29">
+        <v>137</v>
+      </c>
+      <c r="F138" s="28">
+        <v>0</v>
+      </c>
+      <c r="G138" s="28">
+        <v>0.46429999999999999</v>
+      </c>
+      <c r="H138" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I138" s="31">
+        <v>5</v>
+      </c>
+      <c r="J138" s="28">
+        <v>3</v>
+      </c>
+      <c r="K138" s="28">
+        <v>1</v>
+      </c>
+      <c r="L138" s="28">
+        <v>15</v>
+      </c>
+      <c r="M138" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N138" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O138" s="33">
+        <v>372.2</v>
+      </c>
+      <c r="P138" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C139" s="29">
+        <v>29</v>
+      </c>
+      <c r="D139" s="29">
+        <v>274</v>
+      </c>
+      <c r="E139" s="29">
+        <v>137</v>
+      </c>
+      <c r="F139" s="28">
+        <v>0</v>
+      </c>
+      <c r="G139" s="28">
+        <v>0.46429999999999999</v>
+      </c>
+      <c r="H139" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I139" s="31">
+        <v>5</v>
+      </c>
+      <c r="J139" s="28">
+        <v>3</v>
+      </c>
+      <c r="K139" s="28">
+        <v>2</v>
+      </c>
+      <c r="L139" s="28">
+        <v>15</v>
+      </c>
+      <c r="M139" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N139" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O139" s="33">
+        <v>361.2</v>
+      </c>
+      <c r="P139" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>11</v>
+      </c>
+      <c r="B140" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C140" s="29">
+        <v>29</v>
+      </c>
+      <c r="D140" s="29">
+        <v>278</v>
+      </c>
+      <c r="E140" s="29">
+        <v>139</v>
+      </c>
+      <c r="F140" s="28">
+        <v>0</v>
+      </c>
+      <c r="G140" s="28">
+        <v>0.8256</v>
+      </c>
+      <c r="H140" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I140" s="31">
+        <v>6</v>
+      </c>
+      <c r="J140" s="28">
+        <v>3</v>
+      </c>
+      <c r="K140" s="28">
+        <v>1</v>
+      </c>
+      <c r="L140" s="28">
+        <v>52</v>
+      </c>
+      <c r="M140" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N140" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O140" s="33">
+        <v>224.7</v>
+      </c>
+      <c r="P140" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>11</v>
+      </c>
+      <c r="B141" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C141" s="29">
+        <v>29</v>
+      </c>
+      <c r="D141" s="29">
+        <v>277</v>
+      </c>
+      <c r="E141" s="29">
+        <v>139</v>
+      </c>
+      <c r="F141" s="28">
+        <v>0</v>
+      </c>
+      <c r="G141" s="28">
+        <v>0.8256</v>
+      </c>
+      <c r="H141" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I141" s="31">
+        <v>6</v>
+      </c>
+      <c r="J141" s="28">
+        <v>3</v>
+      </c>
+      <c r="K141" s="28">
+        <v>2</v>
+      </c>
+      <c r="L141" s="28">
+        <v>12</v>
+      </c>
+      <c r="M141" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N141" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O141" s="33">
+        <v>278.8</v>
+      </c>
+      <c r="P141" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>11</v>
+      </c>
+      <c r="B142" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C142" s="29">
+        <v>29</v>
+      </c>
+      <c r="D142" s="29">
+        <v>282</v>
+      </c>
+      <c r="E142" s="29">
+        <v>141</v>
+      </c>
+      <c r="F142" s="28">
+        <v>0</v>
+      </c>
+      <c r="G142" s="28">
+        <v>1.4681999999999999</v>
+      </c>
+      <c r="H142" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I142" s="31">
+        <v>7</v>
+      </c>
+      <c r="J142" s="28">
+        <v>3</v>
+      </c>
+      <c r="K142" s="28">
+        <v>1</v>
+      </c>
+      <c r="L142" s="28">
+        <v>27</v>
+      </c>
+      <c r="M142" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N142" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O142" s="33">
+        <v>354.6</v>
+      </c>
+      <c r="P142" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>11</v>
+      </c>
+      <c r="B143" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C143" s="29">
+        <v>29</v>
+      </c>
+      <c r="D143" s="29">
+        <v>283</v>
+      </c>
+      <c r="E143" s="29">
+        <v>141</v>
+      </c>
+      <c r="F143" s="28">
+        <v>0</v>
+      </c>
+      <c r="G143" s="28">
+        <v>1.4681999999999999</v>
+      </c>
+      <c r="H143" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I143" s="31">
+        <v>7</v>
+      </c>
+      <c r="J143" s="28">
+        <v>3</v>
+      </c>
+      <c r="K143" s="28">
+        <v>2</v>
+      </c>
+      <c r="L143" s="28">
+        <v>51</v>
+      </c>
+      <c r="M143" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N143" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O143" s="33">
+        <v>280.39999999999998</v>
+      </c>
+      <c r="P143" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>11</v>
+      </c>
+      <c r="B144" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C144" s="29">
+        <v>29</v>
+      </c>
+      <c r="D144" s="29">
+        <v>288</v>
+      </c>
+      <c r="E144" s="29">
+        <v>143</v>
+      </c>
+      <c r="F144" s="28">
+        <v>0</v>
+      </c>
+      <c r="G144" s="28">
+        <v>0</v>
+      </c>
+      <c r="H144" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I144" s="31">
+        <v>0</v>
+      </c>
+      <c r="J144" s="28">
+        <v>3</v>
+      </c>
+      <c r="K144" s="28">
+        <v>1</v>
+      </c>
+      <c r="L144" s="28">
+        <v>35</v>
+      </c>
+      <c r="M144" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N144" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="O144" s="33">
+        <v>846.8</v>
+      </c>
+      <c r="P144" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" s="25">
+        <v>45777</v>
+      </c>
+      <c r="C145" s="29">
+        <v>29</v>
+      </c>
+      <c r="D145" s="29">
+        <v>286</v>
+      </c>
+      <c r="E145" s="29">
+        <v>143</v>
+      </c>
+      <c r="F145" s="28">
+        <v>0</v>
+      </c>
+      <c r="G145" s="28">
+        <v>0</v>
+      </c>
+      <c r="H145" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I145" s="31">
+        <v>0</v>
+      </c>
+      <c r="J145" s="28">
+        <v>3</v>
+      </c>
+      <c r="K145" s="28">
+        <v>2</v>
+      </c>
+      <c r="L145" s="28">
+        <v>17</v>
+      </c>
+      <c r="M145" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N145" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O145" s="33">
+        <v>631.20000000000005</v>
+      </c>
+      <c r="P145" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P145" xr:uid="{39E4C65D-F359-AD49-BC7D-8ABA3238360F}"/>
+  <conditionalFormatting sqref="M2:M145">
     <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="Green">
       <formula>NOT(ISERROR(SEARCH("Green",M2)))</formula>
     </cfRule>
@@ -49500,7 +56864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29985003-AF80-E741-8DDF-BC6E623CDF36}">
   <dimension ref="A1:AK74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -54074,7 +61438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E14CD86-B1D6-AA4C-9041-9559AD549E9E}">
   <dimension ref="A1:AJ37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -56327,7 +63691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACFE543-FF2B-0B4A-AC58-432810FDE959}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:P253"/>
@@ -62794,7 +70158,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A3F56E-E9D9-F34F-AB6B-BA5262DDDE04}">
   <dimension ref="A1:H819"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -85697,7 +93061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B91141E2-76C2-434B-A87F-697D52F93778}">
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -85798,7 +93162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{638B67DC-E444-4C42-846B-32DEF1BD372A}">
   <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/data/Data_Mix.xlsx
+++ b/data/Data_Mix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E78B1C-711E-F24D-A23F-6FCAF4F9D7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CF0679-031E-9446-97FB-B7D1FF1D4714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="14700" windowHeight="18380" activeTab="2" xr2:uid="{151B9EC8-58A5-074E-9B57-F0DD5BB2A4DA}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{151B9EC8-58A5-074E-9B57-F0DD5BB2A4DA}"/>
   </bookViews>
   <sheets>
     <sheet name="ReproAutumn2024" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="README" sheetId="2" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ReproAutumn2024!$A$1:$O$451</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ReproSpring2025coc!$A$1:$L$253</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ReproSpring2025weight!$A$1:$P$577</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ReproSpring2025weightfasting!$A$1:$P$145</definedName>
@@ -470,7 +471,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -835,11 +836,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1032,6 +1042,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1499,6 +1510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D187816-8F4C-A24D-9013-D6CCB511673A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O453"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10619,7 +10631,7 @@
       </c>
       <c r="N217" s="19"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
         <v>18</v>
       </c>
@@ -10663,7 +10675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A219" s="9" t="s">
         <v>18</v>
       </c>
@@ -10707,7 +10719,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A220" s="9" t="s">
         <v>18</v>
       </c>
@@ -10751,7 +10763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A221" s="9" t="s">
         <v>18</v>
       </c>
@@ -10795,7 +10807,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A222" s="9" t="s">
         <v>18</v>
       </c>
@@ -10839,7 +10851,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A223" s="9" t="s">
         <v>18</v>
       </c>
@@ -10883,7 +10895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A224" s="9" t="s">
         <v>18</v>
       </c>
@@ -10927,7 +10939,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
         <v>18</v>
       </c>
@@ -10971,7 +10983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
         <v>18</v>
       </c>
@@ -11015,7 +11027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
         <v>18</v>
       </c>
@@ -11059,7 +11071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A228" s="9" t="s">
         <v>18</v>
       </c>
@@ -11103,7 +11115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A229" s="9" t="s">
         <v>18</v>
       </c>
@@ -11147,7 +11159,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A230" s="9" t="s">
         <v>18</v>
       </c>
@@ -11191,7 +11203,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A231" s="9" t="s">
         <v>18</v>
       </c>
@@ -11235,7 +11247,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
         <v>18</v>
       </c>
@@ -11279,7 +11291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A233" s="9" t="s">
         <v>18</v>
       </c>
@@ -11323,7 +11335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A234" s="9" t="s">
         <v>18</v>
       </c>
@@ -11367,7 +11379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A235" s="9" t="s">
         <v>18</v>
       </c>
@@ -11411,7 +11423,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A236" s="9" t="s">
         <v>18</v>
       </c>
@@ -11455,7 +11467,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
         <v>18</v>
       </c>
@@ -11499,7 +11511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
         <v>18</v>
       </c>
@@ -11543,7 +11555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>18</v>
       </c>
@@ -11587,7 +11599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
         <v>18</v>
       </c>
@@ -11631,7 +11643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
         <v>18</v>
       </c>
@@ -11675,7 +11687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
         <v>18</v>
       </c>
@@ -11719,7 +11731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
         <v>18</v>
       </c>
@@ -11763,7 +11775,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
         <v>18</v>
       </c>
@@ -11807,7 +11819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A245" s="9" t="s">
         <v>18</v>
       </c>
@@ -11851,7 +11863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A246" s="9" t="s">
         <v>18</v>
       </c>
@@ -11895,7 +11907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A247" s="9" t="s">
         <v>18</v>
       </c>
@@ -11939,7 +11951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A248" s="9" t="s">
         <v>18</v>
       </c>
@@ -11983,7 +11995,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A249" s="9" t="s">
         <v>18</v>
       </c>
@@ -12027,7 +12039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A250" s="9" t="s">
         <v>18</v>
       </c>
@@ -12071,7 +12083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A251" s="9" t="s">
         <v>18</v>
       </c>
@@ -12115,7 +12127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A252" s="9" t="s">
         <v>18</v>
       </c>
@@ -12159,7 +12171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A253" s="9" t="s">
         <v>18</v>
       </c>
@@ -12203,7 +12215,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A254" s="9" t="s">
         <v>18</v>
       </c>
@@ -12247,7 +12259,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A255" s="9" t="s">
         <v>18</v>
       </c>
@@ -12291,7 +12303,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A256" s="9" t="s">
         <v>18</v>
       </c>
@@ -12335,7 +12347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A257" s="9" t="s">
         <v>18</v>
       </c>
@@ -12379,7 +12391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A258" s="9" t="s">
         <v>18</v>
       </c>
@@ -12423,7 +12435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A259" s="9" t="s">
         <v>18</v>
       </c>
@@ -12467,7 +12479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A260" s="9" t="s">
         <v>18</v>
       </c>
@@ -12511,7 +12523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A261" s="9" t="s">
         <v>18</v>
       </c>
@@ -12555,7 +12567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A262" s="9" t="s">
         <v>18</v>
       </c>
@@ -12599,7 +12611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A263" s="9" t="s">
         <v>18</v>
       </c>
@@ -12643,7 +12655,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A264" s="9" t="s">
         <v>18</v>
       </c>
@@ -12687,7 +12699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A265" s="9" t="s">
         <v>18</v>
       </c>
@@ -12731,7 +12743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A266" s="9" t="s">
         <v>18</v>
       </c>
@@ -12775,7 +12787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A267" s="9" t="s">
         <v>18</v>
       </c>
@@ -12819,7 +12831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A268" s="9" t="s">
         <v>18</v>
       </c>
@@ -12863,7 +12875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A269" s="9" t="s">
         <v>18</v>
       </c>
@@ -12907,7 +12919,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A270" s="9" t="s">
         <v>18</v>
       </c>
@@ -12951,7 +12963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A271" s="9" t="s">
         <v>18</v>
       </c>
@@ -12995,7 +13007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A272" s="9" t="s">
         <v>18</v>
       </c>
@@ -13039,7 +13051,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A273" s="9" t="s">
         <v>18</v>
       </c>
@@ -13083,7 +13095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A274" s="9" t="s">
         <v>18</v>
       </c>
@@ -13127,7 +13139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A275" s="9" t="s">
         <v>18</v>
       </c>
@@ -13171,7 +13183,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A276" s="9" t="s">
         <v>18</v>
       </c>
@@ -13215,7 +13227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A277" s="9" t="s">
         <v>18</v>
       </c>
@@ -13259,7 +13271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A278" s="9" t="s">
         <v>18</v>
       </c>
@@ -13303,7 +13315,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A279" s="9" t="s">
         <v>18</v>
       </c>
@@ -13347,7 +13359,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A280" s="9" t="s">
         <v>18</v>
       </c>
@@ -13391,7 +13403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A281" s="9" t="s">
         <v>18</v>
       </c>
@@ -13435,7 +13447,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A282" s="9" t="s">
         <v>18</v>
       </c>
@@ -13479,7 +13491,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A283" s="9" t="s">
         <v>18</v>
       </c>
@@ -13523,7 +13535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A284" s="9" t="s">
         <v>18</v>
       </c>
@@ -13567,7 +13579,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A285" s="9" t="s">
         <v>18</v>
       </c>
@@ -13611,7 +13623,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A286" s="9" t="s">
         <v>18</v>
       </c>
@@ -13655,7 +13667,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A287" s="9" t="s">
         <v>18</v>
       </c>
@@ -13699,7 +13711,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A288" s="9" t="s">
         <v>18</v>
       </c>
@@ -13743,7 +13755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="289" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A289" s="15" t="s">
         <v>18</v>
       </c>
@@ -13787,7 +13799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A290" s="5" t="s">
         <v>30</v>
       </c>
@@ -13831,7 +13843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A291" s="9" t="s">
         <v>30</v>
       </c>
@@ -13875,7 +13887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A292" s="9" t="s">
         <v>30</v>
       </c>
@@ -13919,7 +13931,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A293" s="9" t="s">
         <v>30</v>
       </c>
@@ -13963,7 +13975,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A294" s="9" t="s">
         <v>30</v>
       </c>
@@ -14007,7 +14019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A295" s="9" t="s">
         <v>30</v>
       </c>
@@ -14051,7 +14063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A296" s="9" t="s">
         <v>30</v>
       </c>
@@ -14095,7 +14107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A297" s="9" t="s">
         <v>30</v>
       </c>
@@ -14139,7 +14151,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A298" s="9" t="s">
         <v>30</v>
       </c>
@@ -14186,7 +14198,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A299" s="9" t="s">
         <v>30</v>
       </c>
@@ -14230,7 +14242,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A300" s="9" t="s">
         <v>30</v>
       </c>
@@ -14274,7 +14286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A301" s="9" t="s">
         <v>30</v>
       </c>
@@ -14318,7 +14330,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A302" s="9" t="s">
         <v>30</v>
       </c>
@@ -14362,7 +14374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A303" s="9" t="s">
         <v>30</v>
       </c>
@@ -14406,7 +14418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A304" s="9" t="s">
         <v>30</v>
       </c>
@@ -14450,7 +14462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A305" s="9" t="s">
         <v>30</v>
       </c>
@@ -14494,7 +14506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A306" s="9" t="s">
         <v>30</v>
       </c>
@@ -14538,7 +14550,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A307" s="9" t="s">
         <v>30</v>
       </c>
@@ -14582,7 +14594,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A308" s="9" t="s">
         <v>30</v>
       </c>
@@ -14626,7 +14638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A309" s="9" t="s">
         <v>30</v>
       </c>
@@ -14670,7 +14682,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A310" s="9" t="s">
         <v>30</v>
       </c>
@@ -14714,7 +14726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A311" s="9" t="s">
         <v>30</v>
       </c>
@@ -14758,7 +14770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A312" s="9" t="s">
         <v>30</v>
       </c>
@@ -14802,7 +14814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A313" s="9" t="s">
         <v>30</v>
       </c>
@@ -14846,7 +14858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A314" s="9" t="s">
         <v>30</v>
       </c>
@@ -14890,7 +14902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A315" s="9" t="s">
         <v>30</v>
       </c>
@@ -14934,7 +14946,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A316" s="9" t="s">
         <v>30</v>
       </c>
@@ -14978,7 +14990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A317" s="9" t="s">
         <v>30</v>
       </c>
@@ -15022,7 +15034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A318" s="9" t="s">
         <v>30</v>
       </c>
@@ -15064,7 +15076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A319" s="9" t="s">
         <v>30</v>
       </c>
@@ -15108,7 +15120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A320" s="9" t="s">
         <v>30</v>
       </c>
@@ -15152,7 +15164,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A321" s="9" t="s">
         <v>30</v>
       </c>
@@ -15196,7 +15208,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A322" s="9" t="s">
         <v>30</v>
       </c>
@@ -15240,7 +15252,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A323" s="9" t="s">
         <v>30</v>
       </c>
@@ -15284,7 +15296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A324" s="9" t="s">
         <v>30</v>
       </c>
@@ -15328,7 +15340,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A325" s="9" t="s">
         <v>30</v>
       </c>
@@ -15372,7 +15384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A326" s="9" t="s">
         <v>30</v>
       </c>
@@ -15416,7 +15428,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A327" s="9" t="s">
         <v>30</v>
       </c>
@@ -15460,7 +15472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A328" s="9" t="s">
         <v>30</v>
       </c>
@@ -15504,7 +15516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A329" s="9" t="s">
         <v>30</v>
       </c>
@@ -15548,7 +15560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A330" s="9" t="s">
         <v>30</v>
       </c>
@@ -15592,7 +15604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A331" s="9" t="s">
         <v>30</v>
       </c>
@@ -15636,7 +15648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A332" s="9" t="s">
         <v>30</v>
       </c>
@@ -15680,7 +15692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A333" s="9" t="s">
         <v>30</v>
       </c>
@@ -15724,7 +15736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A334" s="9" t="s">
         <v>30</v>
       </c>
@@ -15768,7 +15780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A335" s="9" t="s">
         <v>30</v>
       </c>
@@ -15812,7 +15824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A336" s="9" t="s">
         <v>30</v>
       </c>
@@ -15856,7 +15868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A337" s="9" t="s">
         <v>30</v>
       </c>
@@ -15900,7 +15912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A338" s="9" t="s">
         <v>30</v>
       </c>
@@ -15944,7 +15956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A339" s="9" t="s">
         <v>30</v>
       </c>
@@ -15988,7 +16000,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A340" s="9" t="s">
         <v>30</v>
       </c>
@@ -16032,7 +16044,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A341" s="9" t="s">
         <v>30</v>
       </c>
@@ -16076,7 +16088,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A342" s="9" t="s">
         <v>30</v>
       </c>
@@ -16120,7 +16132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A343" s="9" t="s">
         <v>30</v>
       </c>
@@ -16164,7 +16176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A344" s="9" t="s">
         <v>30</v>
       </c>
@@ -16208,7 +16220,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A345" s="9" t="s">
         <v>30</v>
       </c>
@@ -16252,7 +16264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A346" s="9" t="s">
         <v>30</v>
       </c>
@@ -16296,7 +16308,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A347" s="9" t="s">
         <v>30</v>
       </c>
@@ -16340,7 +16352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A348" s="9" t="s">
         <v>30</v>
       </c>
@@ -16384,7 +16396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A349" s="9" t="s">
         <v>30</v>
       </c>
@@ -16428,7 +16440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A350" s="9" t="s">
         <v>30</v>
       </c>
@@ -16472,7 +16484,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A351" s="9" t="s">
         <v>30</v>
       </c>
@@ -16516,7 +16528,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A352" s="9" t="s">
         <v>30</v>
       </c>
@@ -16560,7 +16572,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A353" s="9" t="s">
         <v>30</v>
       </c>
@@ -16604,7 +16616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A354" s="9" t="s">
         <v>30</v>
       </c>
@@ -16648,7 +16660,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A355" s="9" t="s">
         <v>30</v>
       </c>
@@ -16692,7 +16704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A356" s="9" t="s">
         <v>30</v>
       </c>
@@ -16736,7 +16748,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A357" s="9" t="s">
         <v>30</v>
       </c>
@@ -16780,7 +16792,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A358" s="9" t="s">
         <v>30</v>
       </c>
@@ -16824,7 +16836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A359" s="9" t="s">
         <v>30</v>
       </c>
@@ -16868,7 +16880,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A360" s="9" t="s">
         <v>30</v>
       </c>
@@ -16912,7 +16924,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="361" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A361" s="20" t="s">
         <v>30</v>
       </c>
@@ -16959,7 +16971,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A362" s="5" t="s">
         <v>31</v>
       </c>
@@ -16999,7 +17011,7 @@
       </c>
       <c r="N362" s="8"/>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A363" s="9" t="s">
         <v>31</v>
       </c>
@@ -17039,7 +17051,7 @@
       </c>
       <c r="N363" s="10"/>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A364" s="9" t="s">
         <v>31</v>
       </c>
@@ -17079,7 +17091,7 @@
       </c>
       <c r="N364" s="10"/>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A365" s="9" t="s">
         <v>31</v>
       </c>
@@ -17119,7 +17131,7 @@
       </c>
       <c r="N365" s="10"/>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A366" s="9" t="s">
         <v>31</v>
       </c>
@@ -17159,7 +17171,7 @@
       </c>
       <c r="N366" s="10"/>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A367" s="9" t="s">
         <v>31</v>
       </c>
@@ -17199,7 +17211,7 @@
       </c>
       <c r="N367" s="10"/>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:15" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A368" s="9" t="s">
         <v>31</v>
       </c>
@@ -17239,7 +17251,7 @@
       </c>
       <c r="N368" s="10"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A369" s="9" t="s">
         <v>31</v>
       </c>
@@ -17279,7 +17291,7 @@
       </c>
       <c r="N369" s="10"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A370" s="9" t="s">
         <v>31</v>
       </c>
@@ -17319,7 +17331,7 @@
       </c>
       <c r="N370" s="10"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A371" s="9" t="s">
         <v>31</v>
       </c>
@@ -17359,7 +17371,7 @@
       </c>
       <c r="N371" s="10"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A372" s="9" t="s">
         <v>31</v>
       </c>
@@ -17399,7 +17411,7 @@
       </c>
       <c r="N372" s="10"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A373" s="9" t="s">
         <v>31</v>
       </c>
@@ -17439,7 +17451,7 @@
       </c>
       <c r="N373" s="10"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A374" s="9" t="s">
         <v>31</v>
       </c>
@@ -17479,7 +17491,7 @@
       </c>
       <c r="N374" s="10"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A375" s="9" t="s">
         <v>31</v>
       </c>
@@ -17519,7 +17531,7 @@
       </c>
       <c r="N375" s="10"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A376" s="9" t="s">
         <v>31</v>
       </c>
@@ -17559,7 +17571,7 @@
       </c>
       <c r="N376" s="10"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A377" s="9" t="s">
         <v>31</v>
       </c>
@@ -17599,7 +17611,7 @@
       </c>
       <c r="N377" s="10"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A378" s="9" t="s">
         <v>31</v>
       </c>
@@ -17639,7 +17651,7 @@
       </c>
       <c r="N378" s="10"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A379" s="9" t="s">
         <v>31</v>
       </c>
@@ -17679,7 +17691,7 @@
       </c>
       <c r="N379" s="10"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A380" s="9" t="s">
         <v>31</v>
       </c>
@@ -17719,7 +17731,7 @@
       </c>
       <c r="N380" s="10"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A381" s="9" t="s">
         <v>31</v>
       </c>
@@ -17759,7 +17771,7 @@
       </c>
       <c r="N381" s="10"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A382" s="9" t="s">
         <v>31</v>
       </c>
@@ -17799,7 +17811,7 @@
       </c>
       <c r="N382" s="10"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A383" s="9" t="s">
         <v>31</v>
       </c>
@@ -17839,7 +17851,7 @@
       </c>
       <c r="N383" s="10"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A384" s="9" t="s">
         <v>31</v>
       </c>
@@ -17879,7 +17891,7 @@
       </c>
       <c r="N384" s="10"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A385" s="9" t="s">
         <v>31</v>
       </c>
@@ -17919,7 +17931,7 @@
       </c>
       <c r="N385" s="10"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A386" s="9" t="s">
         <v>31</v>
       </c>
@@ -17959,7 +17971,7 @@
       </c>
       <c r="N386" s="10"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A387" s="9" t="s">
         <v>31</v>
       </c>
@@ -17999,7 +18011,7 @@
       </c>
       <c r="N387" s="10"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A388" s="9" t="s">
         <v>31</v>
       </c>
@@ -18039,7 +18051,7 @@
       </c>
       <c r="N388" s="10"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A389" s="9" t="s">
         <v>31</v>
       </c>
@@ -18079,7 +18091,7 @@
       </c>
       <c r="N389" s="10"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A390" s="9" t="s">
         <v>31</v>
       </c>
@@ -18119,7 +18131,7 @@
       </c>
       <c r="N390" s="10"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A391" s="9" t="s">
         <v>31</v>
       </c>
@@ -18159,7 +18171,7 @@
       </c>
       <c r="N391" s="10"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A392" s="9" t="s">
         <v>31</v>
       </c>
@@ -18199,7 +18211,7 @@
       </c>
       <c r="N392" s="10"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A393" s="9" t="s">
         <v>31</v>
       </c>
@@ -18239,7 +18251,7 @@
       </c>
       <c r="N393" s="10"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A394" s="9" t="s">
         <v>31</v>
       </c>
@@ -18279,7 +18291,7 @@
       </c>
       <c r="N394" s="10"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A395" s="9" t="s">
         <v>31</v>
       </c>
@@ -18319,7 +18331,7 @@
       </c>
       <c r="N395" s="10"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A396" s="9" t="s">
         <v>31</v>
       </c>
@@ -18359,7 +18371,7 @@
       </c>
       <c r="N396" s="10"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A397" s="9" t="s">
         <v>31</v>
       </c>
@@ -18399,7 +18411,7 @@
       </c>
       <c r="N397" s="10"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A398" s="9" t="s">
         <v>31</v>
       </c>
@@ -18439,7 +18451,7 @@
       </c>
       <c r="N398" s="10"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A399" s="9" t="s">
         <v>31</v>
       </c>
@@ -18479,7 +18491,7 @@
       </c>
       <c r="N399" s="10"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A400" s="9" t="s">
         <v>31</v>
       </c>
@@ -18519,7 +18531,7 @@
       </c>
       <c r="N400" s="10"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A401" s="9" t="s">
         <v>31</v>
       </c>
@@ -18559,7 +18571,7 @@
       </c>
       <c r="N401" s="10"/>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A402" s="9" t="s">
         <v>31</v>
       </c>
@@ -18599,7 +18611,7 @@
       </c>
       <c r="N402" s="10"/>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A403" s="9" t="s">
         <v>31</v>
       </c>
@@ -18639,7 +18651,7 @@
       </c>
       <c r="N403" s="10"/>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A404" s="9" t="s">
         <v>31</v>
       </c>
@@ -18679,7 +18691,7 @@
       </c>
       <c r="N404" s="10"/>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A405" s="9" t="s">
         <v>31</v>
       </c>
@@ -18719,7 +18731,7 @@
       </c>
       <c r="N405" s="10"/>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A406" s="9" t="s">
         <v>31</v>
       </c>
@@ -18759,7 +18771,7 @@
       </c>
       <c r="N406" s="10"/>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A407" s="9" t="s">
         <v>31</v>
       </c>
@@ -18799,7 +18811,7 @@
       </c>
       <c r="N407" s="10"/>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A408" s="9" t="s">
         <v>31</v>
       </c>
@@ -18839,7 +18851,7 @@
       </c>
       <c r="N408" s="10"/>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A409" s="9" t="s">
         <v>31</v>
       </c>
@@ -18879,7 +18891,7 @@
       </c>
       <c r="N409" s="10"/>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A410" s="9" t="s">
         <v>31</v>
       </c>
@@ -18919,7 +18931,7 @@
       </c>
       <c r="N410" s="10"/>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A411" s="9" t="s">
         <v>31</v>
       </c>
@@ -18959,7 +18971,7 @@
       </c>
       <c r="N411" s="10"/>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A412" s="9" t="s">
         <v>31</v>
       </c>
@@ -18999,7 +19011,7 @@
       </c>
       <c r="N412" s="10"/>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A413" s="9" t="s">
         <v>31</v>
       </c>
@@ -19039,7 +19051,7 @@
       </c>
       <c r="N413" s="10"/>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A414" s="9" t="s">
         <v>31</v>
       </c>
@@ -19079,7 +19091,7 @@
       </c>
       <c r="N414" s="10"/>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A415" s="9" t="s">
         <v>31</v>
       </c>
@@ -19119,7 +19131,7 @@
       </c>
       <c r="N415" s="10"/>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A416" s="9" t="s">
         <v>31</v>
       </c>
@@ -19159,7 +19171,7 @@
       </c>
       <c r="N416" s="10"/>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A417" s="9" t="s">
         <v>31</v>
       </c>
@@ -19199,7 +19211,7 @@
       </c>
       <c r="N417" s="10"/>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A418" s="9" t="s">
         <v>31</v>
       </c>
@@ -19239,7 +19251,7 @@
       </c>
       <c r="N418" s="10"/>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A419" s="9" t="s">
         <v>31</v>
       </c>
@@ -19279,7 +19291,7 @@
       </c>
       <c r="N419" s="10"/>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A420" s="9" t="s">
         <v>31</v>
       </c>
@@ -19319,7 +19331,7 @@
       </c>
       <c r="N420" s="10"/>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A421" s="9" t="s">
         <v>31</v>
       </c>
@@ -19359,7 +19371,7 @@
       </c>
       <c r="N421" s="10"/>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A422" s="9" t="s">
         <v>31</v>
       </c>
@@ -19399,7 +19411,7 @@
       </c>
       <c r="N422" s="10"/>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A423" s="9" t="s">
         <v>31</v>
       </c>
@@ -19439,7 +19451,7 @@
       </c>
       <c r="N423" s="10"/>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A424" s="9" t="s">
         <v>31</v>
       </c>
@@ -19479,7 +19491,7 @@
       </c>
       <c r="N424" s="10"/>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A425" s="9" t="s">
         <v>31</v>
       </c>
@@ -19519,7 +19531,7 @@
       </c>
       <c r="N425" s="10"/>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A426" s="9" t="s">
         <v>31</v>
       </c>
@@ -19559,7 +19571,7 @@
       </c>
       <c r="N426" s="10"/>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A427" s="9" t="s">
         <v>31</v>
       </c>
@@ -19599,7 +19611,7 @@
       </c>
       <c r="N427" s="10"/>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A428" s="9" t="s">
         <v>31</v>
       </c>
@@ -19639,7 +19651,7 @@
       </c>
       <c r="N428" s="10"/>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A429" s="9" t="s">
         <v>31</v>
       </c>
@@ -19679,7 +19691,7 @@
       </c>
       <c r="N429" s="10"/>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A430" s="9" t="s">
         <v>31</v>
       </c>
@@ -19719,7 +19731,7 @@
       </c>
       <c r="N430" s="10"/>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A431" s="9" t="s">
         <v>31</v>
       </c>
@@ -19759,7 +19771,7 @@
       </c>
       <c r="N431" s="10"/>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A432" s="9" t="s">
         <v>31</v>
       </c>
@@ -19799,7 +19811,7 @@
       </c>
       <c r="N432" s="10"/>
     </row>
-    <row r="433" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A433" s="15" t="s">
         <v>31</v>
       </c>
@@ -20217,7 +20229,7 @@
       </c>
       <c r="N442" s="10"/>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="9" t="s">
         <v>35</v>
       </c>
@@ -20261,7 +20273,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="9" t="s">
         <v>35</v>
       </c>
@@ -20305,7 +20317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="9" t="s">
         <v>35</v>
       </c>
@@ -20349,7 +20361,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="9" t="s">
         <v>35</v>
       </c>
@@ -20393,7 +20405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="9" t="s">
         <v>35</v>
       </c>
@@ -20437,7 +20449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="9" t="s">
         <v>35</v>
       </c>
@@ -20481,7 +20493,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" s="9" t="s">
         <v>35</v>
       </c>
@@ -20525,7 +20537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="9" t="s">
         <v>35</v>
       </c>
@@ -20569,7 +20581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:14" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A451" s="20" t="s">
         <v>35</v>
       </c>
@@ -20632,6 +20644,13 @@
       <c r="G453" s="21"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O451" xr:uid="{7D187816-8F4C-A24D-9013-D6CCB511673A}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21504,7 +21523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -22306,49 +22325,49 @@
     </row>
     <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B34" s="25">
-        <v>45742</v>
-      </c>
-      <c r="C34" s="29">
+        <v>45748</v>
+      </c>
+      <c r="C34">
         <v>0</v>
       </c>
       <c r="D34" s="29">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="E34" s="29">
+        <v>75</v>
+      </c>
+      <c r="F34" s="28">
+        <v>9.4181000000000008</v>
+      </c>
+      <c r="G34" s="28">
+        <v>0</v>
+      </c>
+      <c r="H34" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="31">
+        <v>2</v>
+      </c>
+      <c r="J34" s="28">
+        <v>3</v>
+      </c>
+      <c r="K34" s="28">
+        <v>1</v>
+      </c>
+      <c r="L34" s="28">
         <v>17</v>
       </c>
-      <c r="F34" s="28">
-        <v>7.0636000000000001</v>
-      </c>
-      <c r="G34" s="28">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="H34" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" s="31">
-        <v>2</v>
-      </c>
-      <c r="J34" s="28">
-        <v>1</v>
-      </c>
-      <c r="K34" s="28">
-        <v>1</v>
-      </c>
-      <c r="L34" s="28">
-        <v>29</v>
-      </c>
       <c r="M34" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N34" s="28" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O34" s="33">
-        <v>540.20000000000005</v>
+        <v>550.70000000000005</v>
       </c>
       <c r="P34" t="s">
         <v>18</v>
@@ -22356,49 +22375,49 @@
     </row>
     <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B35" s="25">
-        <v>45742</v>
-      </c>
-      <c r="C35" s="29">
+        <v>45748</v>
+      </c>
+      <c r="C35">
         <v>0</v>
       </c>
       <c r="D35" s="29">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="E35" s="29">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F35" s="28">
-        <v>7.0636000000000001</v>
+        <v>9.4181000000000008</v>
       </c>
       <c r="G35" s="28">
-        <v>6.4999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I35" s="31">
         <v>2</v>
       </c>
       <c r="J35" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35" s="28">
         <v>2</v>
       </c>
       <c r="L35" s="28">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="M35" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N35" s="28" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O35" s="33">
-        <v>533.6</v>
+        <v>491.9</v>
       </c>
       <c r="P35" t="s">
         <v>18</v>
@@ -22904,7 +22923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -23715,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="D62" s="29">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="E62" s="29">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F62" s="28">
-        <v>4.7089999999999996</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G62" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H62" s="31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I62" s="31">
         <v>2</v>
@@ -23739,16 +23758,16 @@
         <v>1</v>
       </c>
       <c r="L62" s="28">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M62" s="28" t="s">
         <v>43</v>
       </c>
       <c r="N62" s="28" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O62" s="33">
-        <v>363</v>
+        <v>540.20000000000005</v>
       </c>
       <c r="P62" t="s">
         <v>18</v>
@@ -23765,19 +23784,19 @@
         <v>0</v>
       </c>
       <c r="D63" s="29">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E63" s="29">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F63" s="28">
-        <v>4.7089999999999996</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G63" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H63" s="31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I63" s="31">
         <v>2</v>
@@ -23789,16 +23808,16 @@
         <v>2</v>
       </c>
       <c r="L63" s="28">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="M63" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N63" s="28" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="O63" s="33">
-        <v>614.70000000000005</v>
+        <v>533.6</v>
       </c>
       <c r="P63" t="s">
         <v>18</v>
@@ -24304,7 +24323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>37</v>
       </c>
@@ -25106,49 +25125,49 @@
     </row>
     <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B90" s="25">
-        <v>45742</v>
-      </c>
-      <c r="C90" s="29">
+        <v>45748</v>
+      </c>
+      <c r="C90">
         <v>0</v>
       </c>
       <c r="D90" s="29">
+        <v>179</v>
+      </c>
+      <c r="E90" s="29">
         <v>89</v>
       </c>
-      <c r="E90" s="29">
-        <v>45</v>
-      </c>
       <c r="F90" s="28">
-        <v>2.3544999999999998</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G90" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H90" s="31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I90" s="31">
         <v>2</v>
       </c>
       <c r="J90" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K90" s="28">
         <v>1</v>
       </c>
       <c r="L90" s="28">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="M90" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N90" s="28" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="O90" s="33">
-        <v>554.79999999999995</v>
+        <v>576.1</v>
       </c>
       <c r="P90" t="s">
         <v>18</v>
@@ -25156,49 +25175,49 @@
     </row>
     <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B91" s="25">
-        <v>45742</v>
-      </c>
-      <c r="C91" s="29">
+        <v>45748</v>
+      </c>
+      <c r="C91">
         <v>0</v>
       </c>
       <c r="D91" s="29">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="E91" s="29">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="F91" s="28">
-        <v>2.3544999999999998</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G91" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H91" s="31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I91" s="31">
         <v>2</v>
       </c>
       <c r="J91" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K91" s="28">
         <v>2</v>
       </c>
       <c r="L91" s="28">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M91" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N91" s="28" t="s">
         <v>21</v>
       </c>
       <c r="O91" s="33">
-        <v>527.29999999999995</v>
+        <v>591.79999999999995</v>
       </c>
       <c r="P91" t="s">
         <v>18</v>
@@ -25704,7 +25723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>37</v>
       </c>
@@ -26515,19 +26534,19 @@
         <v>0</v>
       </c>
       <c r="D118" s="29">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="E118" s="29">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F118" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G118" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H118" s="31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I118" s="31">
         <v>2</v>
@@ -26539,7 +26558,7 @@
         <v>1</v>
       </c>
       <c r="L118" s="28">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M118" s="28" t="s">
         <v>43</v>
@@ -26548,7 +26567,7 @@
         <v>19</v>
       </c>
       <c r="O118" s="33">
-        <v>380.2</v>
+        <v>363</v>
       </c>
       <c r="P118" t="s">
         <v>18</v>
@@ -26565,19 +26584,19 @@
         <v>0</v>
       </c>
       <c r="D119" s="29">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="E119" s="29">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F119" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G119" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H119" s="31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I119" s="31">
         <v>2</v>
@@ -26589,16 +26608,16 @@
         <v>2</v>
       </c>
       <c r="L119" s="28">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="M119" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N119" s="28" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="O119" s="33">
-        <v>702.7</v>
+        <v>614.70000000000005</v>
       </c>
       <c r="P119" t="s">
         <v>18</v>
@@ -27104,7 +27123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>37</v>
       </c>
@@ -27706,49 +27725,49 @@
     </row>
     <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B142" s="25">
-        <v>45742</v>
-      </c>
-      <c r="C142" s="29">
+        <v>45748</v>
+      </c>
+      <c r="C142">
         <v>0</v>
       </c>
       <c r="D142" s="29">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="E142" s="29">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="F142" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G142" s="28">
-        <v>0</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H142" s="31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I142" s="31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J142" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K142" s="28">
         <v>1</v>
       </c>
       <c r="L142" s="28">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="M142" s="28" t="s">
         <v>44</v>
       </c>
       <c r="N142" s="28" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O142" s="33">
-        <v>507.5</v>
+        <v>527.4</v>
       </c>
       <c r="P142" t="s">
         <v>18</v>
@@ -27756,40 +27775,40 @@
     </row>
     <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B143" s="25">
-        <v>45742</v>
-      </c>
-      <c r="C143" s="29">
+        <v>45748</v>
+      </c>
+      <c r="C143">
         <v>0</v>
       </c>
       <c r="D143" s="29">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="E143" s="29">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="F143" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G143" s="28">
-        <v>0</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H143" s="31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I143" s="31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J143" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K143" s="28">
         <v>2</v>
       </c>
       <c r="L143" s="28">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="M143" s="28" t="s">
         <v>45</v>
@@ -27798,7 +27817,7 @@
         <v>19</v>
       </c>
       <c r="O143" s="33">
-        <v>308</v>
+        <v>322.39999999999998</v>
       </c>
       <c r="P143" t="s">
         <v>18</v>
@@ -28106,49 +28125,49 @@
     </row>
     <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B150" s="25">
-        <v>45748</v>
-      </c>
-      <c r="C150">
+        <v>45742</v>
+      </c>
+      <c r="C150" s="29">
         <v>0</v>
       </c>
       <c r="D150" s="29">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="E150" s="29">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F150" s="28">
-        <v>9.4181000000000008</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G150" s="28">
-        <v>0</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H150" s="31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I150" s="31">
         <v>2</v>
       </c>
       <c r="J150" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K150" s="28">
         <v>1</v>
       </c>
       <c r="L150" s="28">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="M150" s="28" t="s">
         <v>44</v>
       </c>
       <c r="N150" s="28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O150" s="33">
-        <v>550.70000000000005</v>
+        <v>554.79999999999995</v>
       </c>
       <c r="P150" t="s">
         <v>18</v>
@@ -28156,49 +28175,49 @@
     </row>
     <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B151" s="25">
-        <v>45748</v>
-      </c>
-      <c r="C151">
+        <v>45742</v>
+      </c>
+      <c r="C151" s="29">
         <v>0</v>
       </c>
       <c r="D151" s="29">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="E151" s="29">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F151" s="28">
-        <v>9.4181000000000008</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G151" s="28">
-        <v>0</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H151" s="31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I151" s="31">
         <v>2</v>
       </c>
       <c r="J151" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K151" s="28">
         <v>2</v>
       </c>
       <c r="L151" s="28">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="M151" s="28" t="s">
         <v>45</v>
       </c>
       <c r="N151" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O151" s="33">
-        <v>491.9</v>
+        <v>527.29999999999995</v>
       </c>
       <c r="P151" t="s">
         <v>18</v>
@@ -28704,7 +28723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>11</v>
       </c>
@@ -29515,19 +29534,19 @@
         <v>0</v>
       </c>
       <c r="D178" s="29">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="E178" s="29">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="F178" s="28">
-        <v>7.0636000000000001</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G178" s="28">
-        <v>6.4999999999999997E-3</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H178" s="31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I178" s="31">
         <v>2</v>
@@ -29539,16 +29558,16 @@
         <v>1</v>
       </c>
       <c r="L178" s="28">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="M178" s="28" t="s">
         <v>43</v>
       </c>
       <c r="N178" s="28" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="O178" s="33">
-        <v>576.1</v>
+        <v>564.20000000000005</v>
       </c>
       <c r="P178" t="s">
         <v>18</v>
@@ -29565,19 +29584,19 @@
         <v>0</v>
       </c>
       <c r="D179" s="29">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="E179" s="29">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="F179" s="28">
-        <v>7.0636000000000001</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G179" s="28">
-        <v>6.4999999999999997E-3</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H179" s="31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I179" s="31">
         <v>2</v>
@@ -29589,16 +29608,16 @@
         <v>2</v>
       </c>
       <c r="L179" s="28">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="M179" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N179" s="28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O179" s="33">
-        <v>591.79999999999995</v>
+        <v>653.70000000000005</v>
       </c>
       <c r="P179" t="s">
         <v>18</v>
@@ -30104,7 +30123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>11</v>
       </c>
@@ -30906,49 +30925,49 @@
     </row>
     <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B206" s="25">
-        <v>45748</v>
-      </c>
-      <c r="C206">
+        <v>45742</v>
+      </c>
+      <c r="C206" s="29">
         <v>0</v>
       </c>
       <c r="D206" s="29">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="E206" s="29">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F206" s="28">
-        <v>4.7089999999999996</v>
+        <v>0</v>
       </c>
       <c r="G206" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H206" s="31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I206" s="31">
         <v>2</v>
       </c>
       <c r="J206" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K206" s="28">
         <v>1</v>
       </c>
       <c r="L206" s="28">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="M206" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N206" s="28" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O206" s="33">
-        <v>527.4</v>
+        <v>380.2</v>
       </c>
       <c r="P206" t="s">
         <v>18</v>
@@ -30956,49 +30975,49 @@
     </row>
     <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B207" s="25">
-        <v>45748</v>
-      </c>
-      <c r="C207">
+        <v>45742</v>
+      </c>
+      <c r="C207" s="29">
         <v>0</v>
       </c>
       <c r="D207" s="29">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="E207" s="29">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F207" s="28">
-        <v>4.7089999999999996</v>
+        <v>0</v>
       </c>
       <c r="G207" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H207" s="31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I207" s="31">
         <v>2</v>
       </c>
       <c r="J207" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K207" s="28">
         <v>2</v>
       </c>
       <c r="L207" s="28">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="M207" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N207" s="28" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="O207" s="33">
-        <v>322.39999999999998</v>
+        <v>702.7</v>
       </c>
       <c r="P207" t="s">
         <v>18</v>
@@ -31504,7 +31523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>11</v>
       </c>
@@ -32315,19 +32334,19 @@
         <v>0</v>
       </c>
       <c r="D234" s="29">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="E234" s="29">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F234" s="28">
-        <v>2.3544999999999998</v>
+        <v>0</v>
       </c>
       <c r="G234" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H234" s="31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I234" s="31">
         <v>2</v>
@@ -32339,7 +32358,7 @@
         <v>1</v>
       </c>
       <c r="L234" s="28">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M234" s="28" t="s">
         <v>43</v>
@@ -32348,7 +32367,7 @@
         <v>20</v>
       </c>
       <c r="O234" s="33">
-        <v>564.20000000000005</v>
+        <v>541.70000000000005</v>
       </c>
       <c r="P234" t="s">
         <v>18</v>
@@ -32365,19 +32384,19 @@
         <v>0</v>
       </c>
       <c r="D235" s="29">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="E235" s="29">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F235" s="28">
-        <v>2.3544999999999998</v>
+        <v>0</v>
       </c>
       <c r="G235" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H235" s="31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I235" s="31">
         <v>2</v>
@@ -32389,16 +32408,16 @@
         <v>2</v>
       </c>
       <c r="L235" s="28">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="M235" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N235" s="28" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="O235" s="33">
-        <v>653.70000000000005</v>
+        <v>418.7</v>
       </c>
       <c r="P235" t="s">
         <v>18</v>
@@ -32904,7 +32923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>11</v>
       </c>
@@ -33706,49 +33725,49 @@
     </row>
     <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B262" s="25">
-        <v>45748</v>
-      </c>
-      <c r="C262">
+        <v>45742</v>
+      </c>
+      <c r="C262" s="29">
         <v>0</v>
       </c>
       <c r="D262" s="29">
-        <v>263</v>
+        <v>141</v>
       </c>
       <c r="E262" s="29">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="F262" s="28">
         <v>0</v>
       </c>
       <c r="G262" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H262" s="31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I262" s="31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J262" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K262" s="28">
         <v>1</v>
       </c>
       <c r="L262" s="28">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="M262" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N262" s="28" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="O262" s="33">
-        <v>541.70000000000005</v>
+        <v>507.5</v>
       </c>
       <c r="P262" t="s">
         <v>18</v>
@@ -33756,49 +33775,49 @@
     </row>
     <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B263" s="25">
-        <v>45748</v>
-      </c>
-      <c r="C263">
+        <v>45742</v>
+      </c>
+      <c r="C263" s="29">
         <v>0</v>
       </c>
       <c r="D263" s="29">
-        <v>262</v>
+        <v>142</v>
       </c>
       <c r="E263" s="29">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="F263" s="28">
         <v>0</v>
       </c>
       <c r="G263" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H263" s="31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I263" s="31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J263" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K263" s="28">
         <v>2</v>
       </c>
       <c r="L263" s="28">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="M263" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N263" s="28" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O263" s="33">
-        <v>418.7</v>
+        <v>308</v>
       </c>
       <c r="P263" t="s">
         <v>18</v>
@@ -34304,7 +34323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>11</v>
       </c>
@@ -35905,7 +35924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>37</v>
       </c>
@@ -36707,49 +36726,49 @@
     </row>
     <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B322" s="25">
-        <v>45770</v>
+        <v>45776</v>
       </c>
       <c r="C322" s="29">
         <v>28</v>
       </c>
       <c r="D322" s="29">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="E322" s="29">
+        <v>75</v>
+      </c>
+      <c r="F322" s="28">
+        <v>9.4181000000000008</v>
+      </c>
+      <c r="G322" s="28">
+        <v>0</v>
+      </c>
+      <c r="H322" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I322" s="31">
+        <v>2</v>
+      </c>
+      <c r="J322" s="28">
+        <v>3</v>
+      </c>
+      <c r="K322" s="28">
+        <v>1</v>
+      </c>
+      <c r="L322" s="28">
         <v>17</v>
       </c>
-      <c r="F322" s="28">
-        <v>7.0636000000000001</v>
-      </c>
-      <c r="G322" s="28">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="H322" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="I322" s="31">
-        <v>2</v>
-      </c>
-      <c r="J322" s="28">
-        <v>1</v>
-      </c>
-      <c r="K322" s="28">
-        <v>1</v>
-      </c>
-      <c r="L322" s="28">
-        <v>29</v>
-      </c>
       <c r="M322" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N322" s="28" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O322" s="33">
-        <v>814.7</v>
+        <v>604.5</v>
       </c>
       <c r="P322" t="s">
         <v>18</v>
@@ -36757,49 +36776,49 @@
     </row>
     <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B323" s="25">
-        <v>45770</v>
+        <v>45776</v>
       </c>
       <c r="C323" s="29">
         <v>28</v>
       </c>
       <c r="D323" s="29">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="E323" s="29">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F323" s="28">
-        <v>7.0636000000000001</v>
+        <v>9.4181000000000008</v>
       </c>
       <c r="G323" s="28">
-        <v>6.4999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="H323" s="31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I323" s="31">
         <v>2</v>
       </c>
       <c r="J323" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K323" s="28">
         <v>2</v>
       </c>
       <c r="L323" s="28">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="M323" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N323" s="28" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O323" s="33">
-        <v>810.3</v>
+        <v>648.5</v>
       </c>
       <c r="P323" t="s">
         <v>18</v>
@@ -37305,7 +37324,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>37</v>
       </c>
@@ -38116,19 +38135,19 @@
         <v>28</v>
       </c>
       <c r="D350" s="29">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="E350" s="29">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F350" s="28">
-        <v>4.7089999999999996</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G350" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H350" s="31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I350" s="31">
         <v>2</v>
@@ -38140,16 +38159,16 @@
         <v>1</v>
       </c>
       <c r="L350" s="28">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M350" s="28" t="s">
         <v>43</v>
       </c>
       <c r="N350" s="28" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O350" s="33">
-        <v>762.6</v>
+        <v>814.7</v>
       </c>
       <c r="P350" t="s">
         <v>18</v>
@@ -38166,19 +38185,19 @@
         <v>28</v>
       </c>
       <c r="D351" s="29">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E351" s="29">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F351" s="28">
-        <v>4.7089999999999996</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G351" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H351" s="31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I351" s="31">
         <v>2</v>
@@ -38190,16 +38209,16 @@
         <v>2</v>
       </c>
       <c r="L351" s="28">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="M351" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N351" s="28" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="O351" s="33">
-        <v>842</v>
+        <v>810.3</v>
       </c>
       <c r="P351" t="s">
         <v>18</v>
@@ -38705,7 +38724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>37</v>
       </c>
@@ -39507,49 +39526,49 @@
     </row>
     <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B378" s="25">
-        <v>45770</v>
+        <v>45776</v>
       </c>
       <c r="C378" s="29">
         <v>28</v>
       </c>
       <c r="D378" s="29">
+        <v>179</v>
+      </c>
+      <c r="E378" s="29">
         <v>89</v>
       </c>
-      <c r="E378" s="29">
-        <v>45</v>
-      </c>
       <c r="F378" s="28">
-        <v>2.3544999999999998</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G378" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H378" s="31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I378" s="31">
         <v>2</v>
       </c>
       <c r="J378" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K378" s="28">
         <v>1</v>
       </c>
       <c r="L378" s="28">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="M378" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N378" s="28" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="O378" s="33">
-        <v>663.3</v>
+        <v>1068</v>
       </c>
       <c r="P378" t="s">
         <v>18</v>
@@ -39557,49 +39576,49 @@
     </row>
     <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B379" s="25">
-        <v>45770</v>
+        <v>45776</v>
       </c>
       <c r="C379" s="29">
         <v>28</v>
       </c>
       <c r="D379" s="29">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="E379" s="29">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="F379" s="28">
-        <v>2.3544999999999998</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G379" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H379" s="31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I379" s="31">
         <v>2</v>
       </c>
       <c r="J379" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K379" s="28">
         <v>2</v>
       </c>
       <c r="L379" s="28">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M379" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N379" s="28" t="s">
         <v>21</v>
       </c>
       <c r="O379" s="33">
-        <v>630.4</v>
+        <v>716.2</v>
       </c>
       <c r="P379" t="s">
         <v>18</v>
@@ -40105,7 +40124,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>37</v>
       </c>
@@ -40916,19 +40935,19 @@
         <v>28</v>
       </c>
       <c r="D406" s="29">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="E406" s="29">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F406" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G406" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H406" s="31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I406" s="31">
         <v>2</v>
@@ -40940,7 +40959,7 @@
         <v>1</v>
       </c>
       <c r="L406" s="28">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M406" s="28" t="s">
         <v>43</v>
@@ -40949,7 +40968,7 @@
         <v>19</v>
       </c>
       <c r="O406" s="33">
-        <v>829.2</v>
+        <v>762.6</v>
       </c>
       <c r="P406" t="s">
         <v>18</v>
@@ -40966,19 +40985,19 @@
         <v>28</v>
       </c>
       <c r="D407" s="29">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="E407" s="29">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F407" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G407" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H407" s="31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I407" s="31">
         <v>2</v>
@@ -40990,16 +41009,16 @@
         <v>2</v>
       </c>
       <c r="L407" s="28">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="M407" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N407" s="28" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="O407" s="33">
-        <v>1152.7</v>
+        <v>842</v>
       </c>
       <c r="P407" t="s">
         <v>18</v>
@@ -41505,7 +41524,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>37</v>
       </c>
@@ -42107,49 +42126,49 @@
     </row>
     <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B430" s="25">
-        <v>45770</v>
+        <v>45776</v>
       </c>
       <c r="C430" s="29">
         <v>28</v>
       </c>
       <c r="D430" s="29">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="E430" s="29">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="F430" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G430" s="28">
-        <v>0</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H430" s="31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I430" s="31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J430" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K430" s="28">
         <v>1</v>
       </c>
       <c r="L430" s="28">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="M430" s="28" t="s">
         <v>44</v>
       </c>
       <c r="N430" s="28" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O430" s="33">
-        <v>725.8</v>
+        <v>738.6</v>
       </c>
       <c r="P430" t="s">
         <v>18</v>
@@ -42157,40 +42176,40 @@
     </row>
     <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B431" s="25">
-        <v>45770</v>
+        <v>45776</v>
       </c>
       <c r="C431" s="29">
         <v>28</v>
       </c>
       <c r="D431" s="29">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="E431" s="29">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="F431" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G431" s="28">
-        <v>0</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H431" s="31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I431" s="31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J431" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K431" s="28">
         <v>2</v>
       </c>
       <c r="L431" s="28">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="M431" s="28" t="s">
         <v>45</v>
@@ -42199,7 +42218,7 @@
         <v>19</v>
       </c>
       <c r="O431" s="33">
-        <v>547.5</v>
+        <v>576.1</v>
       </c>
       <c r="P431" t="s">
         <v>18</v>
@@ -42507,49 +42526,49 @@
     </row>
     <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B438" s="25">
-        <v>45776</v>
+        <v>45770</v>
       </c>
       <c r="C438" s="29">
         <v>28</v>
       </c>
       <c r="D438" s="29">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="E438" s="29">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F438" s="28">
-        <v>9.4181000000000008</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G438" s="28">
-        <v>0</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H438" s="31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I438" s="31">
         <v>2</v>
       </c>
       <c r="J438" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K438" s="28">
         <v>1</v>
       </c>
       <c r="L438" s="28">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="M438" s="28" t="s">
         <v>44</v>
       </c>
       <c r="N438" s="28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O438" s="33">
-        <v>604.5</v>
+        <v>663.3</v>
       </c>
       <c r="P438" t="s">
         <v>18</v>
@@ -42557,49 +42576,49 @@
     </row>
     <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B439" s="25">
-        <v>45776</v>
+        <v>45770</v>
       </c>
       <c r="C439" s="29">
         <v>28</v>
       </c>
       <c r="D439" s="29">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="E439" s="29">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F439" s="28">
-        <v>9.4181000000000008</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G439" s="28">
-        <v>0</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H439" s="31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I439" s="31">
         <v>2</v>
       </c>
       <c r="J439" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K439" s="28">
         <v>2</v>
       </c>
       <c r="L439" s="28">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="M439" s="28" t="s">
         <v>45</v>
       </c>
       <c r="N439" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O439" s="33">
-        <v>648.5</v>
+        <v>630.4</v>
       </c>
       <c r="P439" t="s">
         <v>18</v>
@@ -43105,7 +43124,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="450" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>11</v>
       </c>
@@ -43916,19 +43935,19 @@
         <v>28</v>
       </c>
       <c r="D466" s="29">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="E466" s="29">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="F466" s="28">
-        <v>7.0636000000000001</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G466" s="28">
-        <v>6.4999999999999997E-3</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H466" s="31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I466" s="31">
         <v>2</v>
@@ -43940,16 +43959,16 @@
         <v>1</v>
       </c>
       <c r="L466" s="28">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="M466" s="28" t="s">
         <v>43</v>
       </c>
       <c r="N466" s="28" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="O466" s="33">
-        <v>1068</v>
+        <v>778.2</v>
       </c>
       <c r="P466" t="s">
         <v>18</v>
@@ -43966,19 +43985,19 @@
         <v>28</v>
       </c>
       <c r="D467" s="29">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="E467" s="29">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="F467" s="28">
-        <v>7.0636000000000001</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G467" s="28">
-        <v>6.4999999999999997E-3</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H467" s="31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I467" s="31">
         <v>2</v>
@@ -43990,16 +44009,16 @@
         <v>2</v>
       </c>
       <c r="L467" s="28">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="M467" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N467" s="28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O467" s="33">
-        <v>716.2</v>
+        <v>691.8</v>
       </c>
       <c r="P467" t="s">
         <v>18</v>
@@ -44505,7 +44524,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="478" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>11</v>
       </c>
@@ -45307,49 +45326,49 @@
     </row>
     <row r="494" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B494" s="25">
-        <v>45776</v>
+        <v>45770</v>
       </c>
       <c r="C494" s="29">
         <v>28</v>
       </c>
       <c r="D494" s="29">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="E494" s="29">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F494" s="28">
-        <v>4.7089999999999996</v>
+        <v>0</v>
       </c>
       <c r="G494" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H494" s="31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I494" s="31">
         <v>2</v>
       </c>
       <c r="J494" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K494" s="28">
         <v>1</v>
       </c>
       <c r="L494" s="28">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="M494" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N494" s="28" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O494" s="33">
-        <v>738.6</v>
+        <v>829.2</v>
       </c>
       <c r="P494" t="s">
         <v>18</v>
@@ -45357,49 +45376,49 @@
     </row>
     <row r="495" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B495" s="25">
-        <v>45776</v>
+        <v>45770</v>
       </c>
       <c r="C495" s="29">
         <v>28</v>
       </c>
       <c r="D495" s="29">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="E495" s="29">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F495" s="28">
-        <v>4.7089999999999996</v>
+        <v>0</v>
       </c>
       <c r="G495" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H495" s="31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I495" s="31">
         <v>2</v>
       </c>
       <c r="J495" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K495" s="28">
         <v>2</v>
       </c>
       <c r="L495" s="28">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="M495" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N495" s="28" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="O495" s="33">
-        <v>576.1</v>
+        <v>1152.7</v>
       </c>
       <c r="P495" t="s">
         <v>18</v>
@@ -45905,7 +45924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="506" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>11</v>
       </c>
@@ -46716,19 +46735,19 @@
         <v>28</v>
       </c>
       <c r="D522" s="29">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="E522" s="29">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F522" s="28">
-        <v>2.3544999999999998</v>
+        <v>0</v>
       </c>
       <c r="G522" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H522" s="31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I522" s="31">
         <v>2</v>
@@ -46740,7 +46759,7 @@
         <v>1</v>
       </c>
       <c r="L522" s="28">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M522" s="28" t="s">
         <v>43</v>
@@ -46749,7 +46768,7 @@
         <v>20</v>
       </c>
       <c r="O522" s="33">
-        <v>778.2</v>
+        <v>857.1</v>
       </c>
       <c r="P522" t="s">
         <v>18</v>
@@ -46766,19 +46785,19 @@
         <v>28</v>
       </c>
       <c r="D523" s="29">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="E523" s="29">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F523" s="28">
-        <v>2.3544999999999998</v>
+        <v>0</v>
       </c>
       <c r="G523" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H523" s="31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I523" s="31">
         <v>2</v>
@@ -46790,16 +46809,16 @@
         <v>2</v>
       </c>
       <c r="L523" s="28">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="M523" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N523" s="28" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="O523" s="33">
-        <v>691.8</v>
+        <v>642.20000000000005</v>
       </c>
       <c r="P523" t="s">
         <v>18</v>
@@ -47305,7 +47324,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="534" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>11</v>
       </c>
@@ -48107,49 +48126,49 @@
     </row>
     <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B550" s="25">
-        <v>45776</v>
+        <v>45770</v>
       </c>
       <c r="C550" s="29">
         <v>28</v>
       </c>
       <c r="D550" s="29">
-        <v>263</v>
+        <v>141</v>
       </c>
       <c r="E550" s="29">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="F550" s="28">
         <v>0</v>
       </c>
       <c r="G550" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H550" s="31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I550" s="31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J550" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K550" s="28">
         <v>1</v>
       </c>
       <c r="L550" s="28">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="M550" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N550" s="28" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="O550" s="33">
-        <v>857.1</v>
+        <v>725.8</v>
       </c>
       <c r="P550" t="s">
         <v>18</v>
@@ -48157,49 +48176,49 @@
     </row>
     <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B551" s="25">
-        <v>45776</v>
+        <v>45770</v>
       </c>
       <c r="C551" s="29">
         <v>28</v>
       </c>
       <c r="D551" s="29">
-        <v>262</v>
+        <v>142</v>
       </c>
       <c r="E551" s="29">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="F551" s="28">
         <v>0</v>
       </c>
       <c r="G551" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H551" s="31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I551" s="31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J551" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K551" s="28">
         <v>2</v>
       </c>
       <c r="L551" s="28">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="M551" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N551" s="28" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O551" s="33">
-        <v>642.20000000000005</v>
+        <v>547.5</v>
       </c>
       <c r="P551" t="s">
         <v>18</v>
@@ -48705,7 +48724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>11</v>
       </c>
@@ -49521,6 +49540,14 @@
         <filter val="3"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:P575">
+      <sortCondition ref="C1:C577"/>
+    </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P289">
     <sortCondition ref="A2:A289"/>
@@ -49564,6 +49591,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B6C79C-735D-7745-9103-3B789D76AD05}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P145"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -49630,7 +49658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -49680,7 +49708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -49730,7 +49758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -49780,7 +49808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -49830,7 +49858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -49880,7 +49908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -49930,7 +49958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -49980,7 +50008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -50030,7 +50058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -50130,7 +50158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -50180,7 +50208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -50230,7 +50258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -50280,7 +50308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -50330,7 +50358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -50380,7 +50408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -50430,107 +50458,107 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B18" s="25">
-        <v>45771</v>
+        <v>45777</v>
       </c>
       <c r="C18" s="29">
         <v>29</v>
       </c>
       <c r="D18" s="29">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="E18" s="29">
+        <v>75</v>
+      </c>
+      <c r="F18" s="28">
+        <v>9.4181000000000008</v>
+      </c>
+      <c r="G18" s="28">
+        <v>0</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="31">
+        <v>2</v>
+      </c>
+      <c r="J18" s="28">
+        <v>3</v>
+      </c>
+      <c r="K18" s="28">
+        <v>1</v>
+      </c>
+      <c r="L18" s="28">
         <v>17</v>
       </c>
-      <c r="F18" s="28">
-        <v>7.0636000000000001</v>
-      </c>
-      <c r="G18" s="28">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="H18" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" s="31">
-        <v>2</v>
-      </c>
-      <c r="J18" s="28">
-        <v>1</v>
-      </c>
-      <c r="K18" s="28">
-        <v>1</v>
-      </c>
-      <c r="L18" s="28">
-        <v>29</v>
-      </c>
       <c r="M18" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O18" s="33">
-        <v>602</v>
+        <v>519</v>
       </c>
       <c r="P18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B19" s="25">
-        <v>45771</v>
+        <v>45777</v>
       </c>
       <c r="C19" s="29">
         <v>29</v>
       </c>
       <c r="D19" s="29">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="E19" s="29">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F19" s="28">
-        <v>7.0636000000000001</v>
+        <v>9.4181000000000008</v>
       </c>
       <c r="G19" s="28">
-        <v>6.4999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I19" s="31">
         <v>2</v>
       </c>
       <c r="J19" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" s="28">
         <v>2</v>
       </c>
       <c r="L19" s="28">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N19" s="28" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O19" s="33">
-        <v>577.6</v>
+        <v>573.6</v>
       </c>
       <c r="P19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -50580,7 +50608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -50630,7 +50658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -50680,7 +50708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -50730,7 +50758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -50830,7 +50858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -50880,7 +50908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -50930,7 +50958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -50980,7 +51008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -51030,7 +51058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -51080,7 +51108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -51130,7 +51158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -51141,19 +51169,19 @@
         <v>29</v>
       </c>
       <c r="D32" s="29">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="E32" s="29">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F32" s="28">
-        <v>4.7089999999999996</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G32" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I32" s="31">
         <v>2</v>
@@ -51165,22 +51193,22 @@
         <v>1</v>
       </c>
       <c r="L32" s="28">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M32" s="28" t="s">
         <v>43</v>
       </c>
       <c r="N32" s="28" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O32" s="33">
-        <v>549.6</v>
+        <v>602</v>
       </c>
       <c r="P32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -51191,19 +51219,19 @@
         <v>29</v>
       </c>
       <c r="D33" s="29">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E33" s="29">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F33" s="28">
-        <v>4.7089999999999996</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G33" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I33" s="31">
         <v>2</v>
@@ -51215,22 +51243,22 @@
         <v>2</v>
       </c>
       <c r="L33" s="28">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="M33" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N33" s="28" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="O33" s="33">
-        <v>592.20000000000005</v>
+        <v>577.6</v>
       </c>
       <c r="P33" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -51280,7 +51308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -51330,7 +51358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -51380,7 +51408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -51430,7 +51458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -51530,7 +51558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>37</v>
       </c>
@@ -51580,7 +51608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -51630,7 +51658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -51680,7 +51708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -51730,7 +51758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -51780,7 +51808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -51830,107 +51858,107 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B46" s="25">
-        <v>45771</v>
+        <v>45777</v>
       </c>
       <c r="C46" s="29">
         <v>29</v>
       </c>
       <c r="D46" s="29">
+        <v>179</v>
+      </c>
+      <c r="E46" s="29">
         <v>89</v>
       </c>
-      <c r="E46" s="29">
-        <v>45</v>
-      </c>
       <c r="F46" s="28">
-        <v>2.3544999999999998</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G46" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I46" s="31">
         <v>2</v>
       </c>
       <c r="J46" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K46" s="28">
         <v>1</v>
       </c>
       <c r="L46" s="28">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="M46" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N46" s="28" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="O46" s="33">
-        <v>497.9</v>
+        <v>849.7</v>
       </c>
       <c r="P46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B47" s="25">
-        <v>45771</v>
+        <v>45777</v>
       </c>
       <c r="C47" s="29">
         <v>29</v>
       </c>
       <c r="D47" s="29">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="E47" s="29">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="F47" s="28">
-        <v>2.3544999999999998</v>
+        <v>7.0636000000000001</v>
       </c>
       <c r="G47" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I47" s="31">
         <v>2</v>
       </c>
       <c r="J47" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K47" s="28">
         <v>2</v>
       </c>
       <c r="L47" s="28">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M47" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N47" s="28" t="s">
         <v>21</v>
       </c>
       <c r="O47" s="33">
-        <v>504.9</v>
+        <v>600.79999999999995</v>
       </c>
       <c r="P47" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>37</v>
       </c>
@@ -51980,7 +52008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>37</v>
       </c>
@@ -52030,7 +52058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -52080,7 +52108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>37</v>
       </c>
@@ -52130,7 +52158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>37</v>
       </c>
@@ -52230,7 +52258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>37</v>
       </c>
@@ -52280,7 +52308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>37</v>
       </c>
@@ -52330,7 +52358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>37</v>
       </c>
@@ -52380,7 +52408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -52430,7 +52458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>37</v>
       </c>
@@ -52480,7 +52508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>37</v>
       </c>
@@ -52530,7 +52558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>37</v>
       </c>
@@ -52541,19 +52569,19 @@
         <v>29</v>
       </c>
       <c r="D60" s="29">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="E60" s="29">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F60" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G60" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H60" s="31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I60" s="31">
         <v>2</v>
@@ -52565,7 +52593,7 @@
         <v>1</v>
       </c>
       <c r="L60" s="28">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M60" s="28" t="s">
         <v>43</v>
@@ -52574,13 +52602,13 @@
         <v>19</v>
       </c>
       <c r="O60" s="33">
-        <v>626.1</v>
+        <v>549.6</v>
       </c>
       <c r="P60" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -52591,19 +52619,19 @@
         <v>29</v>
       </c>
       <c r="D61" s="29">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="E61" s="29">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F61" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G61" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H61" s="31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I61" s="31">
         <v>2</v>
@@ -52615,22 +52643,22 @@
         <v>2</v>
       </c>
       <c r="L61" s="28">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="M61" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N61" s="28" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="O61" s="33">
-        <v>890.1</v>
+        <v>592.20000000000005</v>
       </c>
       <c r="P61" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>37</v>
       </c>
@@ -52680,7 +52708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>37</v>
       </c>
@@ -52730,7 +52758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>37</v>
       </c>
@@ -52780,7 +52808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -52830,7 +52858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>37</v>
       </c>
@@ -52930,7 +52958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>37</v>
       </c>
@@ -52980,7 +53008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>37</v>
       </c>
@@ -53030,7 +53058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>37</v>
       </c>
@@ -53080,7 +53108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>37</v>
       </c>
@@ -53130,92 +53158,92 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B72" s="25">
-        <v>45771</v>
+        <v>45777</v>
       </c>
       <c r="C72" s="29">
         <v>29</v>
       </c>
       <c r="D72" s="29">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="E72" s="29">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="F72" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G72" s="28">
-        <v>0</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H72" s="31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I72" s="31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K72" s="28">
         <v>1</v>
       </c>
       <c r="L72" s="28">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="M72" s="28" t="s">
         <v>44</v>
       </c>
       <c r="N72" s="28" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O72" s="33">
-        <v>320.7</v>
+        <v>567.20000000000005</v>
       </c>
       <c r="P72" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B73" s="25">
-        <v>45771</v>
+        <v>45777</v>
       </c>
       <c r="C73" s="29">
         <v>29</v>
       </c>
       <c r="D73" s="29">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="E73" s="29">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="F73" s="28">
-        <v>0</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="G73" s="28">
-        <v>0</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="H73" s="31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I73" s="31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J73" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K73" s="28">
         <v>2</v>
       </c>
       <c r="L73" s="28">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="M73" s="28" t="s">
         <v>45</v>
@@ -53224,13 +53252,13 @@
         <v>19</v>
       </c>
       <c r="O73" s="33">
-        <v>553.6</v>
+        <v>437</v>
       </c>
       <c r="P73" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -53280,7 +53308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -53330,107 +53358,107 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B76" s="25">
-        <v>45777</v>
+        <v>45771</v>
       </c>
       <c r="C76" s="29">
         <v>29</v>
       </c>
       <c r="D76" s="29">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="E76" s="29">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F76" s="28">
-        <v>9.4181000000000008</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G76" s="28">
-        <v>0</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H76" s="31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I76" s="31">
         <v>2</v>
       </c>
       <c r="J76" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K76" s="28">
         <v>1</v>
       </c>
       <c r="L76" s="28">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="M76" s="28" t="s">
         <v>44</v>
       </c>
       <c r="N76" s="28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O76" s="33">
-        <v>519</v>
+        <v>497.9</v>
       </c>
       <c r="P76" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B77" s="25">
-        <v>45777</v>
+        <v>45771</v>
       </c>
       <c r="C77" s="29">
         <v>29</v>
       </c>
       <c r="D77" s="29">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="E77" s="29">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F77" s="28">
-        <v>9.4181000000000008</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G77" s="28">
-        <v>0</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H77" s="31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I77" s="31">
         <v>2</v>
       </c>
       <c r="J77" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K77" s="28">
         <v>2</v>
       </c>
       <c r="L77" s="28">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="M77" s="28" t="s">
         <v>45</v>
       </c>
       <c r="N77" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O77" s="33">
-        <v>573.6</v>
+        <v>504.9</v>
       </c>
       <c r="P77" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -53480,7 +53508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -53530,7 +53558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -53580,7 +53608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -53630,7 +53658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -53730,7 +53758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -53780,7 +53808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -53830,7 +53858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -53880,7 +53908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -53930,7 +53958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -53980,7 +54008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -54030,7 +54058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -54041,19 +54069,19 @@
         <v>29</v>
       </c>
       <c r="D90" s="29">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="E90" s="29">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="F90" s="28">
-        <v>7.0636000000000001</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G90" s="28">
-        <v>6.4999999999999997E-3</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H90" s="31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I90" s="31">
         <v>2</v>
@@ -54065,22 +54093,22 @@
         <v>1</v>
       </c>
       <c r="L90" s="28">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="M90" s="28" t="s">
         <v>43</v>
       </c>
       <c r="N90" s="28" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="O90" s="33">
-        <v>849.7</v>
+        <v>546.29999999999995</v>
       </c>
       <c r="P90" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -54091,19 +54119,19 @@
         <v>29</v>
       </c>
       <c r="D91" s="29">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="E91" s="29">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="F91" s="28">
-        <v>7.0636000000000001</v>
+        <v>2.3544999999999998</v>
       </c>
       <c r="G91" s="28">
-        <v>6.4999999999999997E-3</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="H91" s="31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I91" s="31">
         <v>2</v>
@@ -54115,22 +54143,22 @@
         <v>2</v>
       </c>
       <c r="L91" s="28">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="M91" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N91" s="28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O91" s="33">
-        <v>600.79999999999995</v>
+        <v>471.6</v>
       </c>
       <c r="P91" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -54180,7 +54208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -54230,7 +54258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -54280,7 +54308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -54330,7 +54358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -54430,7 +54458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -54480,7 +54508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -54530,7 +54558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -54580,7 +54608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -54630,7 +54658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -54680,7 +54708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -54730,107 +54758,107 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B104" s="25">
-        <v>45777</v>
+        <v>45771</v>
       </c>
       <c r="C104" s="29">
         <v>29</v>
       </c>
       <c r="D104" s="29">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="E104" s="29">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F104" s="28">
-        <v>4.7089999999999996</v>
+        <v>0</v>
       </c>
       <c r="G104" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H104" s="31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I104" s="31">
         <v>2</v>
       </c>
       <c r="J104" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K104" s="28">
         <v>1</v>
       </c>
       <c r="L104" s="28">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="M104" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N104" s="28" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O104" s="33">
-        <v>567.20000000000005</v>
+        <v>626.1</v>
       </c>
       <c r="P104" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B105" s="25">
-        <v>45777</v>
+        <v>45771</v>
       </c>
       <c r="C105" s="29">
         <v>29</v>
       </c>
       <c r="D105" s="29">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="E105" s="29">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F105" s="28">
-        <v>4.7089999999999996</v>
+        <v>0</v>
       </c>
       <c r="G105" s="28">
-        <v>1.3100000000000001E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H105" s="31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I105" s="31">
         <v>2</v>
       </c>
       <c r="J105" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K105" s="28">
         <v>2</v>
       </c>
       <c r="L105" s="28">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="M105" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N105" s="28" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="O105" s="33">
-        <v>437</v>
+        <v>890.1</v>
       </c>
       <c r="P105" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -54880,7 +54908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -54930,7 +54958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -54980,7 +55008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -55030,7 +55058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>11</v>
       </c>
@@ -55130,7 +55158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>11</v>
       </c>
@@ -55180,7 +55208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -55230,7 +55258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -55280,7 +55308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -55330,7 +55358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -55380,7 +55408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -55430,7 +55458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -55441,19 +55469,19 @@
         <v>29</v>
       </c>
       <c r="D118" s="29">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="E118" s="29">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F118" s="28">
-        <v>2.3544999999999998</v>
+        <v>0</v>
       </c>
       <c r="G118" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H118" s="31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I118" s="31">
         <v>2</v>
@@ -55465,7 +55493,7 @@
         <v>1</v>
       </c>
       <c r="L118" s="28">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M118" s="28" t="s">
         <v>43</v>
@@ -55474,13 +55502,13 @@
         <v>20</v>
       </c>
       <c r="O118" s="33">
-        <v>546.29999999999995</v>
+        <v>638.9</v>
       </c>
       <c r="P118" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -55491,19 +55519,19 @@
         <v>29</v>
       </c>
       <c r="D119" s="29">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="E119" s="29">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F119" s="28">
-        <v>2.3544999999999998</v>
+        <v>0</v>
       </c>
       <c r="G119" s="28">
-        <v>1.9599999999999999E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="H119" s="31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I119" s="31">
         <v>2</v>
@@ -55515,22 +55543,22 @@
         <v>2</v>
       </c>
       <c r="L119" s="28">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="M119" s="28" t="s">
         <v>46</v>
       </c>
       <c r="N119" s="28" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="O119" s="33">
-        <v>471.6</v>
+        <v>492.2</v>
       </c>
       <c r="P119" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -55580,7 +55608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -55630,7 +55658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -55680,7 +55708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -55730,7 +55758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -55830,7 +55858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -55880,7 +55908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -55930,7 +55958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -55980,7 +56008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -56030,7 +56058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>11</v>
       </c>
@@ -56080,7 +56108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>11</v>
       </c>
@@ -56130,107 +56158,107 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B132" s="25">
-        <v>45777</v>
+        <v>45771</v>
       </c>
       <c r="C132" s="29">
         <v>29</v>
       </c>
       <c r="D132" s="29">
-        <v>263</v>
+        <v>141</v>
       </c>
       <c r="E132" s="29">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="F132" s="28">
         <v>0</v>
       </c>
       <c r="G132" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I132" s="31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J132" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K132" s="28">
         <v>1</v>
       </c>
       <c r="L132" s="28">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="M132" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N132" s="28" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="O132" s="33">
-        <v>638.9</v>
+        <v>620.70000000000005</v>
       </c>
       <c r="P132" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B133" s="25">
-        <v>45777</v>
+        <v>45771</v>
       </c>
       <c r="C133" s="29">
         <v>29</v>
       </c>
       <c r="D133" s="29">
-        <v>262</v>
+        <v>142</v>
       </c>
       <c r="E133" s="29">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="F133" s="28">
         <v>0</v>
       </c>
       <c r="G133" s="28">
-        <v>2.6100000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H133" s="31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I133" s="31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J133" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K133" s="28">
         <v>2</v>
       </c>
       <c r="L133" s="28">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="M133" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N133" s="28" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O133" s="33">
-        <v>492.2</v>
+        <v>553.6</v>
       </c>
       <c r="P133" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>11</v>
       </c>
@@ -56280,7 +56308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>11</v>
       </c>
@@ -56330,7 +56358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>11</v>
       </c>
@@ -56380,7 +56408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>11</v>
       </c>
@@ -56430,7 +56458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>11</v>
       </c>
@@ -56530,7 +56558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>11</v>
       </c>
@@ -56580,7 +56608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>11</v>
       </c>
@@ -56630,7 +56658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -56680,7 +56708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>11</v>
       </c>
@@ -56730,7 +56758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>11</v>
       </c>
@@ -56780,7 +56808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>11</v>
       </c>
@@ -56831,7 +56859,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P145" xr:uid="{39E4C65D-F359-AD49-BC7D-8ABA3238360F}"/>
+  <autoFilter ref="A1:P145" xr:uid="{39E4C65D-F359-AD49-BC7D-8ABA3238360F}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="5"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:P145">
+      <sortCondition ref="H1:H145"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="M2:M145">
     <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="Green">
       <formula>NOT(ISERROR(SEARCH("Green",M2)))</formula>
@@ -63693,7 +63735,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACFE543-FF2B-0B4A-AC58-432810FDE959}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -63702,7 +63743,7 @@
     <col min="13" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -63740,7 +63781,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -63778,7 +63819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -63816,7 +63857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -63854,7 +63895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -63892,7 +63933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -63930,7 +63971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -63968,7 +64009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -64006,7 +64047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -64044,7 +64085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -64082,7 +64123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -64120,7 +64161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -64158,7 +64199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -64195,8 +64236,9 @@
       <c r="L13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M13" s="92"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -64234,7 +64276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -64272,7 +64314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -64310,7 +64352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -64348,7 +64390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -64386,7 +64428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -64424,7 +64466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -64462,7 +64504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -64500,7 +64542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -64538,7 +64580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -64576,7 +64618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -64614,7 +64656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -64652,7 +64694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -64690,7 +64732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -64728,7 +64770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -64766,7 +64808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -64804,7 +64846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -64842,7 +64884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -64880,7 +64922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -64918,7 +64960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -64956,7 +64998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -64994,7 +65036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -65032,7 +65074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -65070,7 +65112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -65108,7 +65150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -65146,7 +65188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -65184,7 +65226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>37</v>
       </c>
@@ -65222,7 +65264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -65260,7 +65302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -65298,7 +65340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -65336,7 +65378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -65374,7 +65416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -65412,7 +65454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -65450,7 +65492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>37</v>
       </c>
@@ -65488,7 +65530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>37</v>
       </c>
@@ -65526,7 +65568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>37</v>
       </c>
@@ -65564,7 +65606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -65602,7 +65644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>37</v>
       </c>
@@ -65640,7 +65682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>37</v>
       </c>
@@ -65678,7 +65720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>37</v>
       </c>
@@ -65716,7 +65758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>37</v>
       </c>
@@ -65754,7 +65796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>37</v>
       </c>
@@ -65792,7 +65834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>37</v>
       </c>
@@ -65830,7 +65872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -65868,7 +65910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>37</v>
       </c>
@@ -65906,7 +65948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>37</v>
       </c>
@@ -65944,7 +65986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>37</v>
       </c>
@@ -65982,7 +66024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -66020,7 +66062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>37</v>
       </c>
@@ -66058,7 +66100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>37</v>
       </c>
@@ -66096,7 +66138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>37</v>
       </c>
@@ -66134,7 +66176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -66172,7 +66214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>37</v>
       </c>
@@ -66210,7 +66252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>37</v>
       </c>
@@ -66248,7 +66290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>37</v>
       </c>
@@ -66286,7 +66328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>37</v>
       </c>
@@ -66324,7 +66366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>37</v>
       </c>
@@ -66362,7 +66404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>37</v>
       </c>
@@ -66476,7 +66518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -66514,7 +66556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -66552,7 +66594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -66590,7 +66632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -66628,7 +66670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -66666,7 +66708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -66704,7 +66746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -66742,7 +66784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -66780,7 +66822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -66818,7 +66860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -66856,7 +66898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -66894,7 +66936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -66932,7 +66974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -66970,7 +67012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -67008,7 +67050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -67046,7 +67088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -67084,7 +67126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -67122,7 +67164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -67160,7 +67202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -67198,7 +67240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -67236,7 +67278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -67274,7 +67316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -67312,7 +67354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -67350,7 +67392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -67388,7 +67430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -67426,7 +67468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -67464,7 +67506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -67502,7 +67544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -67540,7 +67582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -67578,7 +67620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -67616,7 +67658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -67654,7 +67696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -67692,7 +67734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -67730,7 +67772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -67769,7 +67811,7 @@
       </c>
       <c r="P107" s="29"/>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -67847,7 +67889,7 @@
       </c>
       <c r="P109" s="29"/>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>11</v>
       </c>
@@ -67883,7 +67925,7 @@
       </c>
       <c r="P110" s="29"/>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>11</v>
       </c>
@@ -67919,7 +67961,7 @@
       </c>
       <c r="P111" s="29"/>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>11</v>
       </c>
@@ -67955,7 +67997,7 @@
       </c>
       <c r="P112" s="29"/>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -67991,7 +68033,7 @@
       </c>
       <c r="P113" s="29"/>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -68027,7 +68069,7 @@
       </c>
       <c r="P114" s="29"/>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -68063,7 +68105,7 @@
       </c>
       <c r="P115" s="29"/>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -68099,7 +68141,7 @@
       </c>
       <c r="P116" s="29"/>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -68135,7 +68177,7 @@
       </c>
       <c r="P117" s="29"/>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -68171,7 +68213,7 @@
       </c>
       <c r="P118" s="29"/>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -68207,7 +68249,7 @@
       </c>
       <c r="P119" s="29"/>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -68243,7 +68285,7 @@
       </c>
       <c r="P120" s="29"/>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -68279,7 +68321,7 @@
       </c>
       <c r="P121" s="29"/>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -68315,7 +68357,7 @@
       </c>
       <c r="P122" s="29"/>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -68351,7 +68393,7 @@
       </c>
       <c r="P123" s="29"/>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -68387,7 +68429,7 @@
       </c>
       <c r="P124" s="29"/>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -68423,7 +68465,7 @@
       </c>
       <c r="P125" s="29"/>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -68459,7 +68501,7 @@
       </c>
       <c r="P126" s="29"/>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -68495,7 +68537,7 @@
       </c>
       <c r="P127" s="29"/>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -68531,7 +68573,7 @@
       </c>
       <c r="P128" s="29"/>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -68567,7 +68609,7 @@
       </c>
       <c r="P129" s="29"/>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>11</v>
       </c>
@@ -68603,7 +68645,7 @@
       </c>
       <c r="P130" s="29"/>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>11</v>
       </c>
@@ -68639,7 +68681,7 @@
       </c>
       <c r="P131" s="29"/>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>11</v>
       </c>
@@ -68675,7 +68717,7 @@
       </c>
       <c r="P132" s="29"/>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>11</v>
       </c>
@@ -68711,7 +68753,7 @@
       </c>
       <c r="P133" s="29"/>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>11</v>
       </c>
@@ -68747,7 +68789,7 @@
       </c>
       <c r="P134" s="29"/>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>11</v>
       </c>
@@ -68783,7 +68825,7 @@
       </c>
       <c r="P135" s="29"/>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>11</v>
       </c>
@@ -68819,7 +68861,7 @@
       </c>
       <c r="P136" s="29"/>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>11</v>
       </c>
@@ -68855,7 +68897,7 @@
       </c>
       <c r="P137" s="29"/>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>11</v>
       </c>
@@ -68891,7 +68933,7 @@
       </c>
       <c r="P138" s="29"/>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>11</v>
       </c>
@@ -68927,7 +68969,7 @@
       </c>
       <c r="P139" s="29"/>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>11</v>
       </c>
@@ -68963,7 +69005,7 @@
       </c>
       <c r="P140" s="29"/>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>11</v>
       </c>
@@ -68999,7 +69041,7 @@
       </c>
       <c r="P141" s="29"/>
     </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -69035,7 +69077,7 @@
       </c>
       <c r="P142" s="29"/>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>11</v>
       </c>
@@ -69071,7 +69113,7 @@
       </c>
       <c r="P143" s="29"/>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>11</v>
       </c>
@@ -69140,7 +69182,7 @@
       </c>
       <c r="P145" s="29"/>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B146" s="25"/>
       <c r="C146" s="29"/>
       <c r="D146" s="28"/>
@@ -69150,7 +69192,7 @@
       <c r="H146" s="28"/>
       <c r="P146" s="29"/>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B147" s="25"/>
       <c r="C147" s="29"/>
       <c r="D147" s="28"/>
@@ -69160,7 +69202,7 @@
       <c r="H147" s="28"/>
       <c r="P147" s="29"/>
     </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B148" s="25"/>
       <c r="C148" s="29"/>
       <c r="D148" s="28"/>
@@ -69170,7 +69212,7 @@
       <c r="H148" s="28"/>
       <c r="P148" s="29"/>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B149" s="25"/>
       <c r="C149" s="29"/>
       <c r="D149" s="28"/>
@@ -69180,7 +69222,7 @@
       <c r="H149" s="28"/>
       <c r="P149" s="29"/>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B150" s="25"/>
       <c r="C150" s="29"/>
       <c r="D150" s="28"/>
@@ -69190,7 +69232,7 @@
       <c r="H150" s="28"/>
       <c r="P150" s="29"/>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B151" s="25"/>
       <c r="C151" s="29"/>
       <c r="D151" s="28"/>
@@ -69200,7 +69242,7 @@
       <c r="H151" s="28"/>
       <c r="P151" s="29"/>
     </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B152" s="25"/>
       <c r="C152" s="29"/>
       <c r="D152" s="28"/>
@@ -69210,7 +69252,7 @@
       <c r="H152" s="28"/>
       <c r="P152" s="29"/>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B153" s="25"/>
       <c r="C153" s="29"/>
       <c r="D153" s="28"/>
@@ -69220,7 +69262,7 @@
       <c r="H153" s="28"/>
       <c r="P153" s="29"/>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B154" s="25"/>
       <c r="C154" s="29"/>
       <c r="D154" s="28"/>
@@ -69230,7 +69272,7 @@
       <c r="H154" s="28"/>
       <c r="P154" s="29"/>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B155" s="25"/>
       <c r="C155" s="29"/>
       <c r="D155" s="28"/>
@@ -69240,7 +69282,7 @@
       <c r="H155" s="28"/>
       <c r="P155" s="29"/>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B156" s="25"/>
       <c r="C156" s="29"/>
       <c r="D156" s="28"/>
@@ -69250,7 +69292,7 @@
       <c r="H156" s="28"/>
       <c r="P156" s="29"/>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B157" s="25"/>
       <c r="C157" s="29"/>
       <c r="D157" s="28"/>
@@ -69260,7 +69302,7 @@
       <c r="H157" s="28"/>
       <c r="P157" s="29"/>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B158" s="25"/>
       <c r="C158" s="29"/>
       <c r="D158" s="28"/>
@@ -69270,7 +69312,7 @@
       <c r="H158" s="28"/>
       <c r="P158" s="29"/>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B159" s="25"/>
       <c r="C159" s="29"/>
       <c r="D159" s="28"/>
@@ -69280,7 +69322,7 @@
       <c r="H159" s="28"/>
       <c r="P159" s="29"/>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B160" s="25"/>
       <c r="C160" s="29"/>
       <c r="D160" s="28"/>
@@ -69290,7 +69332,7 @@
       <c r="H160" s="28"/>
       <c r="P160" s="29"/>
     </row>
-    <row r="161" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B161" s="25"/>
       <c r="C161" s="29"/>
       <c r="D161" s="28"/>
@@ -69300,7 +69342,7 @@
       <c r="H161" s="28"/>
       <c r="P161" s="29"/>
     </row>
-    <row r="162" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B162" s="25"/>
       <c r="C162" s="29"/>
       <c r="D162" s="28"/>
@@ -69310,7 +69352,7 @@
       <c r="H162" s="28"/>
       <c r="P162" s="29"/>
     </row>
-    <row r="163" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B163" s="25"/>
       <c r="C163" s="29"/>
       <c r="D163" s="28"/>
@@ -69320,7 +69362,7 @@
       <c r="H163" s="28"/>
       <c r="P163" s="29"/>
     </row>
-    <row r="164" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B164" s="25"/>
       <c r="C164" s="29"/>
       <c r="D164" s="28"/>
@@ -69330,7 +69372,7 @@
       <c r="H164" s="28"/>
       <c r="P164" s="29"/>
     </row>
-    <row r="165" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B165" s="25"/>
       <c r="C165" s="29"/>
       <c r="D165" s="28"/>
@@ -69340,7 +69382,7 @@
       <c r="H165" s="28"/>
       <c r="P165" s="29"/>
     </row>
-    <row r="166" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B166" s="25"/>
       <c r="C166" s="29"/>
       <c r="D166" s="28"/>
@@ -69350,7 +69392,7 @@
       <c r="H166" s="28"/>
       <c r="P166" s="29"/>
     </row>
-    <row r="167" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B167" s="25"/>
       <c r="C167" s="29"/>
       <c r="D167" s="28"/>
@@ -69360,7 +69402,7 @@
       <c r="H167" s="28"/>
       <c r="P167" s="29"/>
     </row>
-    <row r="168" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B168" s="25"/>
       <c r="C168" s="29"/>
       <c r="D168" s="28"/>
@@ -69370,7 +69412,7 @@
       <c r="H168" s="28"/>
       <c r="P168" s="29"/>
     </row>
-    <row r="169" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B169" s="25"/>
       <c r="C169" s="29"/>
       <c r="D169" s="28"/>
@@ -69380,7 +69422,7 @@
       <c r="H169" s="28"/>
       <c r="P169" s="29"/>
     </row>
-    <row r="170" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B170" s="25"/>
       <c r="C170" s="29"/>
       <c r="D170" s="28"/>
@@ -69390,7 +69432,7 @@
       <c r="H170" s="28"/>
       <c r="P170" s="29"/>
     </row>
-    <row r="171" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B171" s="25"/>
       <c r="C171" s="29"/>
       <c r="D171" s="28"/>
@@ -69400,7 +69442,7 @@
       <c r="H171" s="28"/>
       <c r="P171" s="29"/>
     </row>
-    <row r="172" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B172" s="25"/>
       <c r="C172" s="29"/>
       <c r="D172" s="28"/>
@@ -69410,7 +69452,7 @@
       <c r="H172" s="28"/>
       <c r="P172" s="29"/>
     </row>
-    <row r="173" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B173" s="25"/>
       <c r="C173" s="29"/>
       <c r="D173" s="28"/>
@@ -69420,7 +69462,7 @@
       <c r="H173" s="28"/>
       <c r="P173" s="29"/>
     </row>
-    <row r="174" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B174" s="25"/>
       <c r="C174" s="29"/>
       <c r="D174" s="28"/>
@@ -69430,7 +69472,7 @@
       <c r="H174" s="28"/>
       <c r="P174" s="29"/>
     </row>
-    <row r="175" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B175" s="25"/>
       <c r="C175" s="29"/>
       <c r="D175" s="28"/>
@@ -69440,7 +69482,7 @@
       <c r="H175" s="28"/>
       <c r="P175" s="29"/>
     </row>
-    <row r="176" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B176" s="25"/>
       <c r="C176" s="29"/>
       <c r="D176" s="28"/>
@@ -69450,7 +69492,7 @@
       <c r="H176" s="28"/>
       <c r="P176" s="29"/>
     </row>
-    <row r="177" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B177" s="25"/>
       <c r="C177" s="29"/>
       <c r="D177" s="28"/>
@@ -69460,7 +69502,7 @@
       <c r="H177" s="28"/>
       <c r="P177" s="29"/>
     </row>
-    <row r="178" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B178" s="25"/>
       <c r="C178" s="29"/>
       <c r="D178" s="28"/>
@@ -69470,7 +69512,7 @@
       <c r="H178" s="28"/>
       <c r="P178" s="29"/>
     </row>
-    <row r="179" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B179" s="25"/>
       <c r="C179" s="29"/>
       <c r="D179" s="28"/>
@@ -69479,7 +69521,7 @@
       <c r="G179" s="31"/>
       <c r="H179" s="28"/>
     </row>
-    <row r="180" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B180" s="25"/>
       <c r="C180" s="29"/>
       <c r="D180" s="28"/>
@@ -69488,7 +69530,7 @@
       <c r="G180" s="31"/>
       <c r="H180" s="28"/>
     </row>
-    <row r="181" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B181" s="25"/>
       <c r="C181" s="29"/>
       <c r="D181" s="28"/>
@@ -69497,7 +69539,7 @@
       <c r="G181" s="31"/>
       <c r="H181" s="28"/>
     </row>
-    <row r="182" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B182" s="25"/>
       <c r="C182" s="29"/>
       <c r="D182" s="28"/>
@@ -69506,7 +69548,7 @@
       <c r="G182" s="31"/>
       <c r="H182" s="28"/>
     </row>
-    <row r="183" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B183" s="25"/>
       <c r="C183" s="29"/>
       <c r="D183" s="28"/>
@@ -69515,7 +69557,7 @@
       <c r="G183" s="31"/>
       <c r="H183" s="28"/>
     </row>
-    <row r="184" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B184" s="25"/>
       <c r="C184" s="29"/>
       <c r="D184" s="28"/>
@@ -69524,7 +69566,7 @@
       <c r="G184" s="31"/>
       <c r="H184" s="28"/>
     </row>
-    <row r="185" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B185" s="25"/>
       <c r="C185" s="29"/>
       <c r="D185" s="28"/>
@@ -69533,7 +69575,7 @@
       <c r="G185" s="31"/>
       <c r="H185" s="28"/>
     </row>
-    <row r="186" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B186" s="25"/>
       <c r="C186" s="29"/>
       <c r="D186" s="28"/>
@@ -69542,7 +69584,7 @@
       <c r="G186" s="31"/>
       <c r="H186" s="28"/>
     </row>
-    <row r="187" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B187" s="25"/>
       <c r="C187" s="29"/>
       <c r="D187" s="28"/>
@@ -69551,7 +69593,7 @@
       <c r="G187" s="31"/>
       <c r="H187" s="28"/>
     </row>
-    <row r="188" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B188" s="25"/>
       <c r="C188" s="29"/>
       <c r="D188" s="28"/>
@@ -69560,7 +69602,7 @@
       <c r="G188" s="31"/>
       <c r="H188" s="28"/>
     </row>
-    <row r="189" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B189" s="25"/>
       <c r="C189" s="29"/>
       <c r="D189" s="28"/>
@@ -69569,7 +69611,7 @@
       <c r="G189" s="31"/>
       <c r="H189" s="28"/>
     </row>
-    <row r="190" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B190" s="25"/>
       <c r="C190" s="29"/>
       <c r="D190" s="28"/>
@@ -69578,7 +69620,7 @@
       <c r="G190" s="31"/>
       <c r="H190" s="28"/>
     </row>
-    <row r="191" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B191" s="25"/>
       <c r="C191" s="29"/>
       <c r="D191" s="28"/>
@@ -69587,7 +69629,7 @@
       <c r="G191" s="31"/>
       <c r="H191" s="28"/>
     </row>
-    <row r="192" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B192" s="25"/>
       <c r="C192" s="29"/>
       <c r="D192" s="28"/>
@@ -69596,7 +69638,7 @@
       <c r="G192" s="31"/>
       <c r="H192" s="28"/>
     </row>
-    <row r="193" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B193" s="25"/>
       <c r="C193" s="29"/>
       <c r="D193" s="28"/>
@@ -69605,7 +69647,7 @@
       <c r="G193" s="31"/>
       <c r="H193" s="28"/>
     </row>
-    <row r="194" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B194" s="25"/>
       <c r="C194" s="29"/>
       <c r="D194" s="28"/>
@@ -69614,7 +69656,7 @@
       <c r="G194" s="31"/>
       <c r="H194" s="28"/>
     </row>
-    <row r="195" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B195" s="25"/>
       <c r="C195" s="29"/>
       <c r="D195" s="28"/>
@@ -69623,7 +69665,7 @@
       <c r="G195" s="31"/>
       <c r="H195" s="28"/>
     </row>
-    <row r="196" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B196" s="25"/>
       <c r="C196" s="29"/>
       <c r="D196" s="28"/>
@@ -69632,7 +69674,7 @@
       <c r="G196" s="31"/>
       <c r="H196" s="28"/>
     </row>
-    <row r="197" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B197" s="25"/>
       <c r="C197" s="29"/>
       <c r="D197" s="28"/>
@@ -69641,7 +69683,7 @@
       <c r="G197" s="31"/>
       <c r="H197" s="28"/>
     </row>
-    <row r="198" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B198" s="25"/>
       <c r="C198" s="29"/>
       <c r="D198" s="28"/>
@@ -69650,7 +69692,7 @@
       <c r="G198" s="31"/>
       <c r="H198" s="28"/>
     </row>
-    <row r="199" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B199" s="25"/>
       <c r="C199" s="29"/>
       <c r="D199" s="28"/>
@@ -69659,7 +69701,7 @@
       <c r="G199" s="31"/>
       <c r="H199" s="28"/>
     </row>
-    <row r="200" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B200" s="25"/>
       <c r="C200" s="29"/>
       <c r="D200" s="28"/>
@@ -69668,7 +69710,7 @@
       <c r="G200" s="31"/>
       <c r="H200" s="28"/>
     </row>
-    <row r="201" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B201" s="25"/>
       <c r="C201" s="29"/>
       <c r="D201" s="28"/>
@@ -69677,7 +69719,7 @@
       <c r="G201" s="31"/>
       <c r="H201" s="28"/>
     </row>
-    <row r="202" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B202" s="25"/>
       <c r="C202" s="29"/>
       <c r="D202" s="28"/>
@@ -69686,7 +69728,7 @@
       <c r="G202" s="31"/>
       <c r="H202" s="28"/>
     </row>
-    <row r="203" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B203" s="25"/>
       <c r="C203" s="29"/>
       <c r="D203" s="28"/>
@@ -69695,7 +69737,7 @@
       <c r="G203" s="31"/>
       <c r="H203" s="28"/>
     </row>
-    <row r="204" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B204" s="25"/>
       <c r="C204" s="29"/>
       <c r="D204" s="28"/>
@@ -69704,7 +69746,7 @@
       <c r="G204" s="31"/>
       <c r="H204" s="28"/>
     </row>
-    <row r="205" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B205" s="25"/>
       <c r="C205" s="29"/>
       <c r="D205" s="28"/>
@@ -69713,7 +69755,7 @@
       <c r="G205" s="31"/>
       <c r="H205" s="28"/>
     </row>
-    <row r="206" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B206" s="25"/>
       <c r="C206" s="29"/>
       <c r="D206" s="28"/>
@@ -69722,7 +69764,7 @@
       <c r="G206" s="31"/>
       <c r="H206" s="28"/>
     </row>
-    <row r="207" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B207" s="25"/>
       <c r="C207" s="29"/>
       <c r="D207" s="28"/>
@@ -69731,7 +69773,7 @@
       <c r="G207" s="31"/>
       <c r="H207" s="28"/>
     </row>
-    <row r="208" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B208" s="25"/>
       <c r="C208" s="29"/>
       <c r="D208" s="28"/>
@@ -69740,7 +69782,7 @@
       <c r="G208" s="31"/>
       <c r="H208" s="28"/>
     </row>
-    <row r="209" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B209" s="25"/>
       <c r="C209" s="29"/>
       <c r="D209" s="28"/>
@@ -69749,7 +69791,7 @@
       <c r="G209" s="31"/>
       <c r="H209" s="28"/>
     </row>
-    <row r="210" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B210" s="25"/>
       <c r="C210" s="29"/>
       <c r="D210" s="28"/>
@@ -69758,7 +69800,7 @@
       <c r="G210" s="31"/>
       <c r="H210" s="28"/>
     </row>
-    <row r="211" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B211" s="25"/>
       <c r="C211" s="29"/>
       <c r="D211" s="28"/>
@@ -69767,7 +69809,7 @@
       <c r="G211" s="31"/>
       <c r="H211" s="28"/>
     </row>
-    <row r="212" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B212" s="25"/>
       <c r="C212" s="29"/>
       <c r="D212" s="28"/>
@@ -69776,7 +69818,7 @@
       <c r="G212" s="31"/>
       <c r="H212" s="28"/>
     </row>
-    <row r="213" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B213" s="25"/>
       <c r="C213" s="29"/>
       <c r="D213" s="28"/>
@@ -69785,7 +69827,7 @@
       <c r="G213" s="31"/>
       <c r="H213" s="28"/>
     </row>
-    <row r="214" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B214" s="25"/>
       <c r="C214" s="29"/>
       <c r="D214" s="28"/>
@@ -69794,7 +69836,7 @@
       <c r="G214" s="31"/>
       <c r="H214" s="28"/>
     </row>
-    <row r="215" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B215" s="25"/>
       <c r="C215" s="29"/>
       <c r="D215" s="28"/>
@@ -69803,7 +69845,7 @@
       <c r="G215" s="31"/>
       <c r="H215" s="28"/>
     </row>
-    <row r="216" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B216" s="25"/>
       <c r="C216" s="29"/>
       <c r="D216" s="28"/>
@@ -69812,7 +69854,7 @@
       <c r="G216" s="31"/>
       <c r="H216" s="28"/>
     </row>
-    <row r="217" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B217" s="25"/>
       <c r="C217" s="29"/>
       <c r="D217" s="28"/>
@@ -69821,7 +69863,7 @@
       <c r="G217" s="31"/>
       <c r="H217" s="28"/>
     </row>
-    <row r="218" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B218" s="25"/>
       <c r="C218" s="29"/>
       <c r="D218" s="28"/>
@@ -69830,7 +69872,7 @@
       <c r="G218" s="31"/>
       <c r="H218" s="28"/>
     </row>
-    <row r="219" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B219" s="25"/>
       <c r="C219" s="29"/>
       <c r="D219" s="28"/>
@@ -69839,7 +69881,7 @@
       <c r="G219" s="31"/>
       <c r="H219" s="28"/>
     </row>
-    <row r="220" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B220" s="25"/>
       <c r="C220" s="29"/>
       <c r="D220" s="28"/>
@@ -69848,7 +69890,7 @@
       <c r="G220" s="31"/>
       <c r="H220" s="28"/>
     </row>
-    <row r="221" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B221" s="25"/>
       <c r="C221" s="29"/>
       <c r="D221" s="28"/>
@@ -69857,7 +69899,7 @@
       <c r="G221" s="31"/>
       <c r="H221" s="28"/>
     </row>
-    <row r="222" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B222" s="25"/>
       <c r="C222" s="29"/>
       <c r="D222" s="28"/>
@@ -69866,7 +69908,7 @@
       <c r="G222" s="31"/>
       <c r="H222" s="28"/>
     </row>
-    <row r="223" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B223" s="25"/>
       <c r="C223" s="29"/>
       <c r="D223" s="28"/>
@@ -69875,7 +69917,7 @@
       <c r="G223" s="31"/>
       <c r="H223" s="28"/>
     </row>
-    <row r="224" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B224" s="25"/>
       <c r="C224" s="29"/>
       <c r="D224" s="28"/>
@@ -69884,7 +69926,7 @@
       <c r="G224" s="31"/>
       <c r="H224" s="28"/>
     </row>
-    <row r="225" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B225" s="25"/>
       <c r="C225" s="29"/>
       <c r="D225" s="28"/>
@@ -69893,7 +69935,7 @@
       <c r="G225" s="31"/>
       <c r="H225" s="28"/>
     </row>
-    <row r="226" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B226" s="25"/>
       <c r="C226" s="29"/>
       <c r="D226" s="28"/>
@@ -69902,7 +69944,7 @@
       <c r="G226" s="31"/>
       <c r="H226" s="28"/>
     </row>
-    <row r="227" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B227" s="25"/>
       <c r="C227" s="29"/>
       <c r="D227" s="28"/>
@@ -69911,7 +69953,7 @@
       <c r="G227" s="31"/>
       <c r="H227" s="28"/>
     </row>
-    <row r="228" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B228" s="25"/>
       <c r="C228" s="29"/>
       <c r="D228" s="28"/>
@@ -69920,7 +69962,7 @@
       <c r="G228" s="31"/>
       <c r="H228" s="28"/>
     </row>
-    <row r="229" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B229" s="25"/>
       <c r="C229" s="29"/>
       <c r="D229" s="28"/>
@@ -69929,7 +69971,7 @@
       <c r="G229" s="31"/>
       <c r="H229" s="28"/>
     </row>
-    <row r="230" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B230" s="25"/>
       <c r="C230" s="29"/>
       <c r="D230" s="28"/>
@@ -69938,7 +69980,7 @@
       <c r="G230" s="31"/>
       <c r="H230" s="28"/>
     </row>
-    <row r="231" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B231" s="25"/>
       <c r="C231" s="29"/>
       <c r="D231" s="28"/>
@@ -69947,7 +69989,7 @@
       <c r="G231" s="31"/>
       <c r="H231" s="28"/>
     </row>
-    <row r="232" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B232" s="25"/>
       <c r="C232" s="29"/>
       <c r="D232" s="28"/>
@@ -69956,7 +69998,7 @@
       <c r="G232" s="31"/>
       <c r="H232" s="28"/>
     </row>
-    <row r="233" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B233" s="25"/>
       <c r="C233" s="29"/>
       <c r="D233" s="28"/>
@@ -69965,7 +70007,7 @@
       <c r="G233" s="31"/>
       <c r="H233" s="28"/>
     </row>
-    <row r="234" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B234" s="25"/>
       <c r="C234" s="29"/>
       <c r="D234" s="28"/>
@@ -69974,7 +70016,7 @@
       <c r="G234" s="31"/>
       <c r="H234" s="28"/>
     </row>
-    <row r="235" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B235" s="25"/>
       <c r="C235" s="29"/>
       <c r="D235" s="28"/>
@@ -69983,7 +70025,7 @@
       <c r="G235" s="31"/>
       <c r="H235" s="28"/>
     </row>
-    <row r="236" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B236" s="25"/>
       <c r="C236" s="29"/>
       <c r="D236" s="28"/>
@@ -69992,7 +70034,7 @@
       <c r="G236" s="31"/>
       <c r="H236" s="28"/>
     </row>
-    <row r="237" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B237" s="25"/>
       <c r="C237" s="29"/>
       <c r="D237" s="28"/>
@@ -70001,7 +70043,7 @@
       <c r="G237" s="31"/>
       <c r="H237" s="28"/>
     </row>
-    <row r="238" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B238" s="25"/>
       <c r="C238" s="29"/>
       <c r="D238" s="28"/>
@@ -70010,7 +70052,7 @@
       <c r="G238" s="31"/>
       <c r="H238" s="28"/>
     </row>
-    <row r="239" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B239" s="25"/>
       <c r="C239" s="29"/>
       <c r="D239" s="28"/>
@@ -70019,7 +70061,7 @@
       <c r="G239" s="31"/>
       <c r="H239" s="28"/>
     </row>
-    <row r="240" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B240" s="25"/>
       <c r="C240" s="29"/>
       <c r="D240" s="28"/>
@@ -70028,7 +70070,7 @@
       <c r="G240" s="31"/>
       <c r="H240" s="28"/>
     </row>
-    <row r="241" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B241" s="25"/>
       <c r="C241" s="29"/>
       <c r="D241" s="28"/>
@@ -70037,7 +70079,7 @@
       <c r="G241" s="31"/>
       <c r="H241" s="28"/>
     </row>
-    <row r="242" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B242" s="25"/>
       <c r="C242" s="29"/>
       <c r="D242" s="28"/>
@@ -70046,7 +70088,7 @@
       <c r="G242" s="31"/>
       <c r="H242" s="28"/>
     </row>
-    <row r="243" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B243" s="25"/>
       <c r="C243" s="29"/>
       <c r="D243" s="28"/>
@@ -70055,7 +70097,7 @@
       <c r="G243" s="31"/>
       <c r="H243" s="28"/>
     </row>
-    <row r="244" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B244" s="25"/>
       <c r="C244" s="29"/>
       <c r="D244" s="28"/>
@@ -70064,7 +70106,7 @@
       <c r="G244" s="31"/>
       <c r="H244" s="28"/>
     </row>
-    <row r="245" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B245" s="25"/>
       <c r="C245" s="29"/>
       <c r="D245" s="28"/>
@@ -70073,7 +70115,7 @@
       <c r="G245" s="31"/>
       <c r="H245" s="28"/>
     </row>
-    <row r="246" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B246" s="25"/>
       <c r="C246" s="29"/>
       <c r="D246" s="28"/>
@@ -70082,7 +70124,7 @@
       <c r="G246" s="31"/>
       <c r="H246" s="28"/>
     </row>
-    <row r="247" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B247" s="25"/>
       <c r="C247" s="29"/>
       <c r="D247" s="28"/>
@@ -70091,7 +70133,7 @@
       <c r="G247" s="31"/>
       <c r="H247" s="28"/>
     </row>
-    <row r="248" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B248" s="25"/>
       <c r="C248" s="29"/>
       <c r="D248" s="28"/>
@@ -70100,7 +70142,7 @@
       <c r="G248" s="31"/>
       <c r="H248" s="28"/>
     </row>
-    <row r="249" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B249" s="25"/>
       <c r="C249" s="29"/>
       <c r="D249" s="28"/>
@@ -70109,7 +70151,7 @@
       <c r="G249" s="31"/>
       <c r="H249" s="28"/>
     </row>
-    <row r="250" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B250" s="25"/>
       <c r="C250" s="29"/>
       <c r="D250" s="28"/>
@@ -70118,7 +70160,7 @@
       <c r="G250" s="31"/>
       <c r="H250" s="28"/>
     </row>
-    <row r="251" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B251" s="25"/>
       <c r="C251" s="29"/>
       <c r="D251" s="28"/>
@@ -70127,7 +70169,7 @@
       <c r="G251" s="31"/>
       <c r="H251" s="28"/>
     </row>
-    <row r="252" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B252" s="25"/>
       <c r="C252" s="29"/>
       <c r="D252" s="28"/>
@@ -70136,7 +70178,7 @@
       <c r="G252" s="31"/>
       <c r="H252" s="28"/>
     </row>
-    <row r="253" spans="2:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B253" s="25"/>
       <c r="C253" s="29"/>
       <c r="D253" s="28"/>
@@ -70146,13 +70188,7 @@
       <c r="H253" s="28"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L253" xr:uid="{EACFE543-FF2B-0B4A-AC58-432810FDE959}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="N"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L253" xr:uid="{EACFE543-FF2B-0B4A-AC58-432810FDE959}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
